--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC1ACB2-BBEE-4861-BF4A-7BBF6A395159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F80ACD-A0BE-4D41-AD48-491CDF667316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{7A3F6830-CDDC-4BD6-9DB9-E70917F562BA}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{DDABEE53-8415-4B60-8DAA-76C5DBFE148E}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
     <sheet name="Objectifs par module" sheetId="2" r:id="rId2"/>
-    <sheet name="Cycle EOD Ventes (reel)" sheetId="3" r:id="rId3"/>
-    <sheet name="Scenario 50 traitements" sheetId="4" r:id="rId4"/>
-    <sheet name="Parite Control-M" sheetId="5" r:id="rId5"/>
+    <sheet name="Taxonomie complete" sheetId="3" r:id="rId3"/>
+    <sheet name="Cycles reels construits" sheetId="4" r:id="rId4"/>
+    <sheet name="Scenario 50 traitements" sheetId="5" r:id="rId5"/>
+    <sheet name="Parite Control-M" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Objectifs par module'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Scenario 50 traitements'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenario 50 traitements'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Taxonomie complete'!$A$3:$E$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,15 +44,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="449">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
   <si>
-    <t>Ce classeur illustre, module par module, l'objectif metier reel poursuivi une fois un module Odoo active, et le cycle operatoire (EOD/EOM/TFJ/ON_DEMAND) qui le fait tourner en tache de fond - exactement comme le montre une session Control-M reelle (plusieurs chaines de jobs actives simultanement, chacune avec son propre calendrier).</t>
-  </si>
-  <si>
-    <t>STATUT reel (jamais survendu) : la colonne 'Statut' de la feuille 'Objectifs par module' distingue ce qui est CONSTRUIT ET VERIFIE (CRM, Ventes avec son cycle EOD complet, Achat) de ce qui reste A CONSTRUIRE sur le meme patron deja prouve. Voir docs/CONVENTION_NOMMAGE.md et docs/JOURNAL_TECHNIQUE.md dans le depot pour le detail technique complet de chaque decision.</t>
+    <t>Ce classeur illustre, module par module, l'objectif metier reel poursuivi une fois un module Odoo active, et le cycle operatoire qui le fait tourner en tache de fond - taxonomie bancaire complete (JOUR/NRT, TFJ, EOD, EOW, EOM, EOQ, EOY, CUTOFF, REPLAY, PURGE, SIMULATION, REALTIME, ON_DEMAND, voir la feuille 'Taxonomie complete'), exactement comme le montre une session Control-M reelle (plusieurs chaines de jobs actives simultanement, chacune avec son propre calendrier).</t>
+  </si>
+  <si>
+    <t>STATUT reel (jamais survendu) : la colonne 'Statut' de la feuille 'Objectifs par module' distingue ce qui est CONSTRUIT ET VERIFIE de ce qui reste A CONSTRUIRE sur le meme patron deja prouve. 5 cycles reels construits a ce jour, un par type (TFJ, EOD, CUTOFF, JOUR, PURGE) - voir la feuille 'Cycles reels construits'. Voir docs/CONVENTION_NOMMAGE.md et docs/JOURNAL_TECHNIQUE.md dans le depot pour le detail technique complet de chaque decision.</t>
   </si>
   <si>
     <t>Le moteur d'execution reel (orchestrator.sh) lance desormais tous les jobs prets d'une meme vague en parallele (MAX_PARALLEL_JOBS=6 par defaut, jamais un par un comme WAZ_ELK_FACTORY) - la feuille 'Scenario 50 traitements' simule ce comportement REEL (meme algorithme que le code, pas une illustration inventee) : environ 50 traitements reels lances, 6 demarrent simultanement, chaque emplacement se libere individuellement des qu'UN job finit.</t>
@@ -89,13 +91,13 @@
     <t>Installation et disponibilite de l'infrastructure Odoo complete</t>
   </si>
   <si>
-    <t>ON_DEMAND (deploiement)</t>
-  </si>
-  <si>
-    <t>Verification finale de bout en bout en parallele des modules</t>
-  </si>
-  <si>
-    <t>20 jobs BLD + ECFRVER (parallele)</t>
+    <t>ON_DEMAND (deploiement) + PURGE (mensuel)</t>
+  </si>
+  <si>
+    <t>Verification finale en parallele des modules - archivage a froid des fichiers arc/ &gt;90j</t>
+  </si>
+  <si>
+    <t>20 jobs BLD + ECFRVER (parallele) + ECFCPRG1 (PURGE</t>
   </si>
   <si>
     <t>CT</t>
@@ -128,582 +130,846 @@
     <t>Agenda partage et gestion des rendez-vous</t>
   </si>
   <si>
+    <t>JOUR/NRT</t>
+  </si>
+  <si>
+    <t>Envoi des rappels de rendez-vous du jour (toutes les heures)</t>
+  </si>
+  <si>
+    <t>ECFBCLAC/ECFBCLDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>Discuss</t>
+  </si>
+  <si>
+    <t>Messagerie interne et notifications entre utilisateurs</t>
+  </si>
+  <si>
+    <t>ON_DEMAND</t>
+  </si>
+  <si>
+    <t>Purge des messages archives anciens</t>
+  </si>
+  <si>
+    <t>ECFBDSAC/ECFBDSDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Construit (Tier1 fichier)</t>
+  </si>
+  <si>
+    <t>Suivi des pistes et opportunites commerciales</t>
+  </si>
+  <si>
     <t>TFJ</t>
   </si>
   <si>
-    <t>Envoi des rappels de rendez-vous du jour</t>
-  </si>
-  <si>
-    <t>ECFBCLAC/ECFBCLDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>DS</t>
-  </si>
-  <si>
-    <t>Discuss</t>
-  </si>
-  <si>
-    <t>Messagerie interne et notifications entre utilisateurs</t>
-  </si>
-  <si>
-    <t>ON_DEMAND</t>
-  </si>
-  <si>
-    <t>Purge des messages archives anciens</t>
-  </si>
-  <si>
-    <t>ECFBDSAC/ECFBDSDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Construit (Tier1 fichier)</t>
-  </si>
-  <si>
-    <t>Suivi des pistes et opportunites commerciales</t>
+    <t>Relance automatique des pistes sans activite depuis 7 jours</t>
+  </si>
+  <si>
+    <t>5 jobs Tier1 (ECFRCRCL/CO/MV/WO/LO)</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t>Ventes</t>
+  </si>
+  <si>
+    <t>Construit (Tier1 + TFJ + JOUR reels)</t>
+  </si>
+  <si>
+    <t>Devis commandes et facturation client</t>
+  </si>
+  <si>
+    <t>TFJ (CONSTRUIT ET VERIFIE) + JOUR (CONSTRUIT)</t>
+  </si>
+  <si>
+    <t>TFJ : detection devis en attente (5j) - annulation devis perimes (30j) - rapport CA du jour. JOUR : suivi des devis envoyes sans reponse &gt;2h (8h-18h)</t>
+  </si>
+  <si>
+    <t>3 jobs Tier1 + cycle TFJ complet (ECFCVTRL/NT/RP) + ECFJVTSV (JOUR)</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Comptabilite</t>
+  </si>
+  <si>
+    <t>Construit (marqueur EOD reel)</t>
+  </si>
+  <si>
+    <t>Facturation et comptabilite de base</t>
+  </si>
+  <si>
+    <t>EOD (CONSTRUIT ET VERIFIE) + EOM</t>
+  </si>
+  <si>
+    <t>EOD : bascule quotidienne de la date valeur comptable J-&gt;J+1 (23h50). EOM (a construire) : cloture comptable mensuelle</t>
+  </si>
+  <si>
+    <t>ECFBCPAC/ECFBCPDE (activation) + ECFCEOD1 (EOD</t>
+  </si>
+  <si>
+    <t>AH</t>
+  </si>
+  <si>
+    <t>Achat</t>
+  </si>
+  <si>
+    <t>Construit (Tier1 + CUTOFF reel)</t>
+  </si>
+  <si>
+    <t>Commandes et appels d'offres fournisseurs</t>
+  </si>
+  <si>
+    <t>CUTOFF (CONSTRUIT ET VERIFIE) + EOM</t>
+  </si>
+  <si>
+    <t>CUTOFF : bascule J/J+1 des commandes fournisseurs a 15h. EOM (a construire) : reapprovisionnement mensuel base sur les seuils de stock</t>
+  </si>
+  <si>
+    <t>3 jobs Tier1 (ECFRAHPO/CF/RC) + ECFCCUT1 (CUTOFF</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Gestion des stocks et logistique</t>
+  </si>
+  <si>
+    <t>Alerte quotidienne des ruptures et sur-stocks</t>
+  </si>
+  <si>
+    <t>ECFBTAC/ECFBTDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>MR</t>
+  </si>
+  <si>
+    <t>MRP</t>
+  </si>
+  <si>
+    <t>Ordres de fabrication et nomenclatures</t>
+  </si>
+  <si>
+    <t>Lancement des ordres de fabrication planifies (toutes les heures)</t>
+  </si>
+  <si>
+    <t>ECFBMRAC/ECFBMRDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>RP</t>
+  </si>
+  <si>
+    <t>Reparation</t>
+  </si>
+  <si>
+    <t>Ordres de reparation (SAV/atelier)</t>
+  </si>
+  <si>
+    <t>Rapport quotidien des reparations en cours et terminees</t>
+  </si>
+  <si>
+    <t>ECFBRPAC/ECFBRPDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Flotte vehicules</t>
+  </si>
+  <si>
+    <t>Gestion de parc de vehicules</t>
+  </si>
+  <si>
+    <t>Rapport mensuel d'entretien et de disponibilite des vehicules</t>
+  </si>
+  <si>
+    <t>ECFBFLAC/ECFBFLDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>Point de vente</t>
+  </si>
+  <si>
+    <t>Caisse (vente au comptoir)</t>
+  </si>
+  <si>
+    <t>Cloture de caisse quotidienne (rapprochement especes/carte)</t>
+  </si>
+  <si>
+    <t>ECFBPSAC/ECFBPSDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>PR</t>
+  </si>
+  <si>
+    <t>POS Restaurant</t>
+  </si>
+  <si>
+    <t>Extensions caisse pour restauration</t>
+  </si>
+  <si>
+    <t>Cloture de service (midi/soir) avec ventilation par table</t>
+  </si>
+  <si>
+    <t>ECFBPRAC/ECFBPRDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Site web</t>
+  </si>
+  <si>
+    <t>Constructeur de site web vitrine</t>
+  </si>
+  <si>
+    <t>Verification des liens morts et formulaires de contact</t>
+  </si>
+  <si>
+    <t>ECFBIAC/ECFBIDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>eCommerce</t>
+  </si>
+  <si>
+    <t>Boutique en ligne</t>
+  </si>
+  <si>
+    <t>Rapport quotidien des ventes en ligne et paniers abandonnes</t>
+  </si>
+  <si>
+    <t>ECFBECAC/ECFBECDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>Evenements</t>
+  </si>
+  <si>
+    <t>Publication et billetterie d'evenements</t>
+  </si>
+  <si>
+    <t>Rappel des evenements du jour aux inscrits</t>
+  </si>
+  <si>
+    <t>ECFBEVAC/ECFBEVDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>eLearning</t>
+  </si>
+  <si>
+    <t>Plateforme de formation en ligne</t>
+  </si>
+  <si>
+    <t>Rapport mensuel de progression des formations en cours</t>
+  </si>
+  <si>
+    <t>ECFBELAC/ECFBELDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>JW</t>
+  </si>
+  <si>
+    <t>Offres emploi web</t>
+  </si>
+  <si>
+    <t>Offres d'emploi publiees en ligne</t>
+  </si>
+  <si>
+    <t>Depublication automatique des offres pourvues</t>
+  </si>
+  <si>
+    <t>ECFBJWAC/ECFBJWDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>Fiches employes</t>
+  </si>
+  <si>
+    <t>Rapport mensuel des effectifs et anciennete</t>
+  </si>
+  <si>
+    <t>ECFBRHAC/ECFBRHDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>PN</t>
+  </si>
+  <si>
+    <t>Presences</t>
+  </si>
+  <si>
+    <t>Pointage des presences</t>
+  </si>
+  <si>
+    <t>Rapport quotidien des presences et anomalies (retards/absences)</t>
+  </si>
+  <si>
+    <t>ECFBPNAC/ECFBPNDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>Conges</t>
+  </si>
+  <si>
+    <t>Demandes de conges et absences</t>
+  </si>
+  <si>
+    <t>Relance des demandes en attente de validation (toutes les heures)</t>
+  </si>
+  <si>
+    <t>ECFBCGAC/ECFBCGDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>Notes de frais</t>
+  </si>
+  <si>
+    <t>Notes de frais employes</t>
+  </si>
+  <si>
+    <t>Rapport mensuel des depenses par employe et par categorie</t>
+  </si>
+  <si>
+    <t>ECFBNDAC/ECFBNDDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>Recrutement</t>
+  </si>
+  <si>
+    <t>Pipeline de recrutement</t>
+  </si>
+  <si>
+    <t>Relance quotidienne des candidatures en attente d'entretien</t>
+  </si>
+  <si>
+    <t>ECFBRCAC/ECFBRCDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>Competences</t>
+  </si>
+  <si>
+    <t>Competences et CV des employes</t>
+  </si>
+  <si>
+    <t>Rapport mensuel des ecarts de competences par equipe</t>
+  </si>
+  <si>
+    <t>ECFBCMAC/ECFBCMDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>PJ</t>
+  </si>
+  <si>
+    <t>Projets</t>
+  </si>
+  <si>
+    <t>Gestion de projets</t>
+  </si>
+  <si>
+    <t>Rapport quotidien d'avancement des taches et jalons en retard</t>
+  </si>
+  <si>
+    <t>ECFBPJAC/ECFBPJDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>Todo</t>
+  </si>
+  <si>
+    <t>Listes de taches personnelles</t>
+  </si>
+  <si>
+    <t>Rappel des taches du jour non terminees (toutes les heures)</t>
+  </si>
+  <si>
+    <t>ECFBTDAC/ECFBTDDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Suivi de maintenance des equipements</t>
+  </si>
+  <si>
+    <t>Planning de maintenance preventive du mois suivant</t>
+  </si>
+  <si>
+    <t>ECFBMTAC/ECFBMTDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>Sondages</t>
+  </si>
+  <si>
+    <t>Creation et diffusion de sondages</t>
+  </si>
+  <si>
+    <t>Cloture automatique des sondages arrives a echeance</t>
+  </si>
+  <si>
+    <t>ECFBNAC/ECFBNDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>Cantine</t>
+  </si>
+  <si>
+    <t>Commandes de repas internes</t>
+  </si>
+  <si>
+    <t>CUTOFF</t>
+  </si>
+  <si>
+    <t>Cutoff des commandes du jour (11h) avant envoi cuisine</t>
+  </si>
+  <si>
+    <t>ECFBCNAC/ECFBCNDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>LC</t>
+  </si>
+  <si>
+    <t>Live chat</t>
+  </si>
+  <si>
+    <t>Chat en direct sur le site web</t>
+  </si>
+  <si>
+    <t>Rapport hebdomadaire (EOW) des conversations non traitees</t>
+  </si>
+  <si>
+    <t>ECFBLCAC/ECFBLCDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>Email marketing</t>
+  </si>
+  <si>
+    <t>Campagnes email marketing</t>
+  </si>
+  <si>
+    <t>Envoi des campagnes planifiees (toutes les heures)</t>
+  </si>
+  <si>
+    <t>ECFBEMAC/ECFBEMDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>SMS marketing</t>
+  </si>
+  <si>
+    <t>Campagnes SMS marketing</t>
+  </si>
+  <si>
+    <t>Envoi des campagnes SMS planifiees (toutes les heures)</t>
+  </si>
+  <si>
+    <t>ECFBMAC/ECFBMDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>CK</t>
+  </si>
+  <si>
+    <t>Cartes marketing</t>
+  </si>
+  <si>
+    <t>Cartes marketing dynamiques partageables</t>
+  </si>
+  <si>
+    <t>Rapport de partage/engagement des cartes actives</t>
+  </si>
+  <si>
+    <t>ECFBCKAC/ECFBCKDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>RY</t>
+  </si>
+  <si>
+    <t>Recyclage donnees</t>
+  </si>
+  <si>
+    <t>Detection et archivage des donnees perimees</t>
+  </si>
+  <si>
+    <t>Detection mensuelle des donnees perimees (distinct du PURGE systeme deja construit)</t>
+  </si>
+  <si>
+    <t>ECFBRYAC/ECFBRYDE (activation seulement)</t>
+  </si>
+  <si>
+    <t>Taxonomie complete des cycles operatoires (vocabulaire bancaire reel - CBS Amplitude/SAB/Temenos)</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Nature du declenchement</t>
+  </si>
+  <si>
+    <t>Frequence</t>
+  </si>
+  <si>
+    <t>Cas d'usage</t>
+  </si>
+  <si>
+    <t>Statut chez ECF</t>
+  </si>
+  <si>
+    <t>JOUR / NRT</t>
+  </si>
+  <si>
+    <t>Automatique frequence fixe (ex. toutes les heures) ou micro-batch 5-15 min</t>
+  </si>
+  <si>
+    <t>Quotidienne pendant les heures ouvrees</t>
+  </si>
+  <si>
+    <t>Synchronisations d'interfaces sauvegardes a chaud alertes temps reel</t>
+  </si>
+  <si>
+    <t>CONSTRUIT (ECFJVTSV</t>
+  </si>
+  <si>
+    <t>Automatique a la fermeture (guichets/agences)</t>
+  </si>
+  <si>
+    <t>Quotidienne fenetre nocturne</t>
+  </si>
+  <si>
+    <t>Chaine d'orchestration de fin de journee : gel transactions reconciliations soldes</t>
+  </si>
+  <si>
+    <t>CONSTRUIT (ECFCVTRL/NT/RP</t>
   </si>
   <si>
     <t>EOD</t>
   </si>
   <si>
-    <t>Relance automatique des pistes sans activite depuis 7 jours</t>
-  </si>
-  <si>
-    <t>5 jobs Tier1 (ECFRCRCL/CO/MV/WO/LO)</t>
-  </si>
-  <si>
-    <t>VT</t>
-  </si>
-  <si>
-    <t>Ventes</t>
-  </si>
-  <si>
-    <t>Construit (Tier1 + cycle EOD reel)</t>
-  </si>
-  <si>
-    <t>Devis commandes et facturation client</t>
-  </si>
-  <si>
-    <t>EOD (CONSTRUIT ET VERIFIE)</t>
-  </si>
-  <si>
-    <t>Detection devis en attente (5j) - annulation devis perimes (30j) - rapport CA du jour</t>
-  </si>
-  <si>
-    <t>3 jobs Tier1 + cycle EOD complet (ECFCVTRL/NT/RP)</t>
-  </si>
-  <si>
-    <t>CP</t>
-  </si>
-  <si>
-    <t>Comptabilite</t>
-  </si>
-  <si>
-    <t>Facturation et comptabilite de base</t>
-  </si>
-  <si>
-    <t>EOM + TFJ</t>
-  </si>
-  <si>
-    <t>Cloture comptable mensuelle - relance quotidienne des factures impayees &gt;30j</t>
-  </si>
-  <si>
-    <t>ECFBCPAC/ECFBCPDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>AH</t>
-  </si>
-  <si>
-    <t>Achat</t>
-  </si>
-  <si>
-    <t>Commandes et appels d'offres fournisseurs</t>
-  </si>
-  <si>
-    <t>Reapprovisionnement automatique base sur les seuils de stock minimum</t>
-  </si>
-  <si>
-    <t>3 jobs Tier1 (ECFRAHPO/CF/RC)</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>Gestion des stocks et logistique</t>
-  </si>
-  <si>
-    <t>Alerte quotidienne des ruptures et sur-stocks</t>
-  </si>
-  <si>
-    <t>ECFBTAC/ECFBTDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>MR</t>
-  </si>
-  <si>
-    <t>MRP</t>
-  </si>
-  <si>
-    <t>Ordres de fabrication et nomenclatures</t>
-  </si>
-  <si>
-    <t>Lancement des ordres de fabrication planifies du jour</t>
-  </si>
-  <si>
-    <t>ECFBMRAC/ECFBMRDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>RP</t>
-  </si>
-  <si>
-    <t>Reparation</t>
-  </si>
-  <si>
-    <t>Ordres de reparation (SAV/atelier)</t>
-  </si>
-  <si>
-    <t>Rapport quotidien des reparations en cours et terminees</t>
-  </si>
-  <si>
-    <t>ECFBRPAC/ECFBRPDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>FL</t>
-  </si>
-  <si>
-    <t>Flotte vehicules</t>
-  </si>
-  <si>
-    <t>Gestion de parc de vehicules</t>
-  </si>
-  <si>
-    <t>Rapport mensuel d'entretien et de disponibilite des vehicules</t>
-  </si>
-  <si>
-    <t>ECFBFLAC/ECFBFLDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>PS</t>
-  </si>
-  <si>
-    <t>Point de vente</t>
-  </si>
-  <si>
-    <t>Caisse (vente au comptoir)</t>
-  </si>
-  <si>
-    <t>Cloture de caisse quotidienne (rapprochement especes/carte)</t>
-  </si>
-  <si>
-    <t>ECFBPSAC/ECFBPSDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>POS Restaurant</t>
-  </si>
-  <si>
-    <t>Extensions caisse pour restauration</t>
-  </si>
-  <si>
-    <t>Cloture de service (midi/soir) avec ventilation par table</t>
-  </si>
-  <si>
-    <t>ECFBPRAC/ECFBPRDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>Site web</t>
-  </si>
-  <si>
-    <t>Constructeur de site web vitrine</t>
-  </si>
-  <si>
-    <t>Verification des liens morts et formulaires de contact</t>
-  </si>
-  <si>
-    <t>ECFBIAC/ECFBIDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>eCommerce</t>
-  </si>
-  <si>
-    <t>Boutique en ligne</t>
-  </si>
-  <si>
-    <t>Rapport quotidien des ventes en ligne et paniers abandonnes</t>
-  </si>
-  <si>
-    <t>ECFBECAC/ECFBECDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>Evenements</t>
-  </si>
-  <si>
-    <t>Publication et billetterie d'evenements</t>
-  </si>
-  <si>
-    <t>Rappel des evenements du jour aux inscrits</t>
-  </si>
-  <si>
-    <t>ECFBEVAC/ECFBEVDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>EL</t>
-  </si>
-  <si>
-    <t>eLearning</t>
-  </si>
-  <si>
-    <t>Plateforme de formation en ligne</t>
-  </si>
-  <si>
-    <t>Rapport mensuel de progression des formations en cours</t>
-  </si>
-  <si>
-    <t>ECFBELAC/ECFBELDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>JW</t>
-  </si>
-  <si>
-    <t>Offres emploi web</t>
-  </si>
-  <si>
-    <t>Offres d'emploi publiees en ligne</t>
-  </si>
-  <si>
-    <t>Depublication automatique des offres pourvues</t>
-  </si>
-  <si>
-    <t>ECFBJWAC/ECFBJWDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>RH</t>
-  </si>
-  <si>
-    <t>Fiches employes</t>
-  </si>
-  <si>
-    <t>Rapport mensuel des effectifs et anciennete</t>
-  </si>
-  <si>
-    <t>ECFBRHAC/ECFBRHDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>PN</t>
-  </si>
-  <si>
-    <t>Presences</t>
-  </si>
-  <si>
-    <t>Pointage des presences</t>
-  </si>
-  <si>
-    <t>Rapport quotidien des presences et anomalies (retards/absences)</t>
-  </si>
-  <si>
-    <t>ECFBPNAC/ECFBPNDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>CG</t>
-  </si>
-  <si>
-    <t>Conges</t>
-  </si>
-  <si>
-    <t>Demandes de conges et absences</t>
-  </si>
-  <si>
-    <t>Relance quotidienne des demandes en attente de validation</t>
-  </si>
-  <si>
-    <t>ECFBCGAC/ECFBCGDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>ND</t>
-  </si>
-  <si>
-    <t>Notes de frais</t>
-  </si>
-  <si>
-    <t>Notes de frais employes</t>
-  </si>
-  <si>
-    <t>Rapport mensuel des depenses par employe et par categorie</t>
-  </si>
-  <si>
-    <t>ECFBNDAC/ECFBNDDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>RC</t>
-  </si>
-  <si>
-    <t>Recrutement</t>
-  </si>
-  <si>
-    <t>Pipeline de recrutement</t>
-  </si>
-  <si>
-    <t>Relance quotidienne des candidatures en attente d'entretien</t>
-  </si>
-  <si>
-    <t>ECFBRCAC/ECFBRCDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>CM</t>
-  </si>
-  <si>
-    <t>Competences</t>
-  </si>
-  <si>
-    <t>Competences et CV des employes</t>
-  </si>
-  <si>
-    <t>Rapport mensuel des ecarts de competences par equipe</t>
-  </si>
-  <si>
-    <t>ECFBCMAC/ECFBCMDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>PJ</t>
-  </si>
-  <si>
-    <t>Projets</t>
-  </si>
-  <si>
-    <t>Gestion de projets</t>
-  </si>
-  <si>
-    <t>Rapport quotidien d'avancement des taches et jalons en retard</t>
-  </si>
-  <si>
-    <t>ECFBPJAC/ECFBPJDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>TD</t>
-  </si>
-  <si>
-    <t>Todo</t>
-  </si>
-  <si>
-    <t>Listes de taches personnelles</t>
-  </si>
-  <si>
-    <t>Rappel des taches du jour non terminees</t>
-  </si>
-  <si>
-    <t>ECFBTDAC/ECFBTDDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>Maintenance</t>
-  </si>
-  <si>
-    <t>Suivi de maintenance des equipements</t>
-  </si>
-  <si>
-    <t>Planning de maintenance preventive du mois suivant</t>
-  </si>
-  <si>
-    <t>ECFBMTAC/ECFBMTDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>SN</t>
-  </si>
-  <si>
-    <t>Sondages</t>
-  </si>
-  <si>
-    <t>Creation et diffusion de sondages</t>
-  </si>
-  <si>
-    <t>Cloture automatique des sondages arrives a echeance</t>
-  </si>
-  <si>
-    <t>ECFBNAC/ECFBNDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>Cantine</t>
-  </si>
-  <si>
-    <t>Commandes de repas internes</t>
-  </si>
-  <si>
-    <t>Cloture des commandes du jour avant envoi cuisine</t>
-  </si>
-  <si>
-    <t>ECFBCNAC/ECFBCNDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>LC</t>
-  </si>
-  <si>
-    <t>Live chat</t>
-  </si>
-  <si>
-    <t>Chat en direct sur le site web</t>
-  </si>
-  <si>
-    <t>Rapport hebdomadaire des conversations non traitees</t>
-  </si>
-  <si>
-    <t>ECFBLCAC/ECFBLCDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>Email marketing</t>
-  </si>
-  <si>
-    <t>Campagnes email marketing</t>
-  </si>
-  <si>
-    <t>Envoi des campagnes planifiees du jour</t>
-  </si>
-  <si>
-    <t>ECFBEMAC/ECFBEMDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>SMS marketing</t>
-  </si>
-  <si>
-    <t>Campagnes SMS marketing</t>
-  </si>
-  <si>
-    <t>Envoi des campagnes SMS planifiees du jour</t>
-  </si>
-  <si>
-    <t>ECFBMAC/ECFBMDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>CK</t>
-  </si>
-  <si>
-    <t>Cartes marketing</t>
-  </si>
-  <si>
-    <t>Cartes marketing dynamiques partageables</t>
-  </si>
-  <si>
-    <t>Rapport de partage/engagement des cartes actives</t>
-  </si>
-  <si>
-    <t>ECFBCKAC/ECFBCKDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>RY</t>
-  </si>
-  <si>
-    <t>Recyclage donnees</t>
-  </si>
-  <si>
-    <t>Detection et archivage des donnees perimees</t>
-  </si>
-  <si>
-    <t>Purge mensuelle des donnees perimees detectees</t>
-  </si>
-  <si>
-    <t>ECFBRYAC/ECFBRYDE (activation seulement)</t>
-  </si>
-  <si>
-    <t>Cycle EOD Ventes - seul cycle calendaire CONSTRUIT ET VERIFIE a ce jour</t>
+    <t>Horodate (ex. 23h50)</t>
+  </si>
+  <si>
+    <t>Quotidienne</t>
+  </si>
+  <si>
+    <t>Marqueur logique unique - bascule de la date valeur comptable de J a J+1</t>
+  </si>
+  <si>
+    <t>CONSTRUIT (ECFCEOD1</t>
+  </si>
+  <si>
+    <t>EOW</t>
+  </si>
+  <si>
+    <t>Automatique (vendredi soir/samedi)</t>
+  </si>
+  <si>
+    <t>Hebdomadaire</t>
+  </si>
+  <si>
+    <t>Positions moyennes consolidation des risques hebdomadaires</t>
+  </si>
+  <si>
+    <t>MECANISME PRET (WEEKLY) - aucun exemple construit</t>
+  </si>
+  <si>
+    <t>Calendaire (dernier jour du mois)</t>
+  </si>
+  <si>
+    <t>Mensuelle</t>
+  </si>
+  <si>
+    <t>Paies amortissements arretes comptables rapports reglementaires</t>
+  </si>
+  <si>
+    <t>MECANISME PRET (MONTHLY) - aucun exemple construit</t>
+  </si>
+  <si>
+    <t>EOQ</t>
+  </si>
+  <si>
+    <t>Automatique (fin de trimestre)</t>
+  </si>
+  <si>
+    <t>Trimestrielle</t>
+  </si>
+  <si>
+    <t>Ratios prudentiels reporting reglementaire</t>
+  </si>
+  <si>
+    <t>MECANISME PRET (QUARTERLY) - aucun exemple construit</t>
+  </si>
+  <si>
+    <t>EOY</t>
+  </si>
+  <si>
+    <t>Automatique (31 decembre)</t>
+  </si>
+  <si>
+    <t>Annuelle</t>
+  </si>
+  <si>
+    <t>Bascule d'exercice comptable amortissements annuels etats fiscaux</t>
+  </si>
+  <si>
+    <t>MECANISME PRET (YEARLY) - aucun exemple construit</t>
+  </si>
+  <si>
+    <t>Horaire legal strict (ex. 15h)</t>
+  </si>
+  <si>
+    <t>Heure limite de prise en compte des ordres - bascule automatique en J+1 apres</t>
+  </si>
+  <si>
+    <t>CONSTRUIT (ECFCCUT1</t>
+  </si>
+  <si>
+    <t>REPLAY</t>
+  </si>
+  <si>
+    <t>Exceptionnel manuel ou incident</t>
+  </si>
+  <si>
+    <t>Ponctuelle</t>
+  </si>
+  <si>
+    <t>Rejeu d'une chaine en erreur apres correction d'un bug</t>
+  </si>
+  <si>
+    <t>DEJA COUVERT (bin/rerun_job.sh bin/order_job.sh)</t>
+  </si>
+  <si>
+    <t>PURGE</t>
+  </si>
+  <si>
+    <t>Periodique (depassement de retention)</t>
+  </si>
+  <si>
+    <t>Periodique</t>
+  </si>
+  <si>
+    <t>Nettoyage de tables temporaires archivage a froid</t>
+  </si>
+  <si>
+    <t>CONSTRUIT (ECFCPRG1</t>
+  </si>
+  <si>
+    <t>SIMULATION</t>
+  </si>
+  <si>
+    <t>Sur environnement miroir/sandbox</t>
+  </si>
+  <si>
+    <t>Stress test impact d'une hypothese sur le portefeuille</t>
+  </si>
+  <si>
+    <t>HORS PERIMETRE - necessite un environnement dedie</t>
+  </si>
+  <si>
+    <t>REALTIME</t>
+  </si>
+  <si>
+    <t>Continu evenementiel (Kafka webhooks)</t>
+  </si>
+  <si>
+    <t>Fil de l'eau</t>
+  </si>
+  <si>
+    <t>Anti-fraude transaction autorisation immediate</t>
+  </si>
+  <si>
+    <t>HORS PERIMETRE - architecture evenementielle incompatible avec un ordonnanceur batch</t>
+  </si>
+  <si>
+    <t>Manuel (operateur) ou webhook/API</t>
+  </si>
+  <si>
+    <t>Reexecution d'un batch en erreur export specifique pour audit</t>
+  </si>
+  <si>
+    <t>DEJA COUVERT (jobs Tier1 pilotes par fichier + bin/run_now.sh)</t>
+  </si>
+  <si>
+    <t>5 cycles reels construits et verifies a ce jour - un par type de mecanisme</t>
+  </si>
+  <si>
+    <t>JOB_ID</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>TFJ (0/3)</t>
+  </si>
+  <si>
+    <t>bin/montee_au_plan.sh</t>
+  </si>
+  <si>
+    <t>Montee au plan (New Day)</t>
+  </si>
+  <si>
+    <t>Ouvre la fenetre chaque nuit (00:05)</t>
+  </si>
+  <si>
+    <t>TFJ_VENTES_WINDOW_OPEN</t>
+  </si>
+  <si>
+    <t>TFJ (1/3)</t>
+  </si>
+  <si>
+    <t>ECFCVTRL</t>
+  </si>
+  <si>
+    <t>ECF_VENTE_CYC_RELANCE</t>
+  </si>
+  <si>
+    <t>Detecte les devis en attente depuis plus de 5 jours</t>
+  </si>
+  <si>
+    <t>TFJ_VENTES_RELANCE_OK</t>
+  </si>
+  <si>
+    <t>TFJ (2/3)</t>
+  </si>
+  <si>
+    <t>ECFCVTNT</t>
+  </si>
+  <si>
+    <t>ECF_VENTE_CYC_NETTOYAGE</t>
+  </si>
+  <si>
+    <t>Annule automatiquement les devis perimes depuis plus de 30 jours</t>
+  </si>
+  <si>
+    <t>TFJ_VENTES_NETTOYAGE_OK</t>
+  </si>
+  <si>
+    <t>TFJ (3/3)</t>
+  </si>
+  <si>
+    <t>ECFCVTRP</t>
+  </si>
+  <si>
+    <t>ECF_VENTE_CYC_RAPPORT</t>
+  </si>
+  <si>
+    <t>JOB TERMINAL - rapport de fin de journee (commandes et CA du jour)</t>
+  </si>
+  <si>
+    <t>TFJ_VENTES_TERMINE</t>
+  </si>
+  <si>
+    <t>ECFCEOD1</t>
+  </si>
+  <si>
+    <t>ECF_COMPTA_EOD_BASCULE</t>
+  </si>
+  <si>
+    <t>Marqueur horodate (23h50, minuteur dedie) - bascule la date valeur comptable J-&gt;J+1</t>
+  </si>
+  <si>
+    <t>state/valeur_comptable_courante.txt</t>
+  </si>
+  <si>
+    <t>ECFCCUT1</t>
+  </si>
+  <si>
+    <t>ECF_ACHAT_CUTOFF_ORDRES</t>
+  </si>
+  <si>
+    <t>Marqueur horodate (15h) - fixe J ou J+1 pour les futures commandes fournisseurs</t>
+  </si>
+  <si>
+    <t>state/cutoff_achat_date_valeur.txt</t>
+  </si>
+  <si>
+    <t>ECFJVTSV</t>
+  </si>
+  <si>
+    <t>ECF_VENTE_JOUR_SUIVI</t>
+  </si>
+  <si>
+    <t>Suivi intraday des devis envoyes sans reponse &gt;2h (garde horaire 8h-18h)</t>
+  </si>
+  <si>
+    <t>OUT_COND=NONE, invoque toutes les 15 min</t>
+  </si>
+  <si>
+    <t>ECFCPRG1</t>
+  </si>
+  <si>
+    <t>ECF_SYS_CYC_PURGE</t>
+  </si>
+  <si>
+    <t>Archivage a froid des fichiers arc/ de plus de 90 jours (cadence mensuelle)</t>
+  </si>
+  <si>
+    <t>PURGE_ARC_TERMINE</t>
+  </si>
+  <si>
+    <t>TFJ/EOM/EOW/EOQ/EOY partagent le meme mecanisme (bin/montee_au_plan.sh, CYCLE_WINDOWS, un jalon reel remis a zero par periode). EOD/CUTOFF suivent un patron different : un marqueur horodate unique, son propre minuteur systemd a heure fixe, jamais celui de montee_au_plan.sh. JOUR/NRT n'a besoin d'aucun minuteur dedie : un job Tier 1 classique (OUT_COND=NONE) avec sa propre garde horaire interne, invoque par le minuteur periodique de l'orchestrateur (15 min).</t>
+  </si>
+  <si>
+    <t>Simulation reelle : ~50 traitements sous MAX_PARALLEL_JOBS=6 (meme algorithme que orchestrator.sh)</t>
   </si>
   <si>
     <t>Ordre</t>
   </si>
   <si>
-    <t>JOB_ID</t>
-  </si>
-  <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Sortie produite</t>
-  </si>
-  <si>
-    <t>bin/montee_au_plan.sh</t>
-  </si>
-  <si>
-    <t>Montee au plan (New Day)</t>
-  </si>
-  <si>
-    <t>Ouvre la fenetre du jour (00:05, quotidien)</t>
-  </si>
-  <si>
-    <t>EOD_VENTES_WINDOW_OPEN</t>
-  </si>
-  <si>
-    <t>ECFCVTRL</t>
-  </si>
-  <si>
-    <t>ECF_VENTE_CYC_RELANCE</t>
-  </si>
-  <si>
-    <t>Detecte les devis en attente depuis plus de 5 jours, ecrit un rapport dans /vt/snd</t>
-  </si>
-  <si>
-    <t>EOD_VENTES_RELANCE_OK</t>
-  </si>
-  <si>
-    <t>ECFCVTNT</t>
-  </si>
-  <si>
-    <t>ECF_VENTE_CYC_NETTOYAGE</t>
-  </si>
-  <si>
-    <t>Annule automatiquement les devis perimes depuis plus de 30 jours</t>
-  </si>
-  <si>
-    <t>EOD_VENTES_NETTOYAGE_OK</t>
-  </si>
-  <si>
-    <t>ECFCVTRP</t>
-  </si>
-  <si>
-    <t>ECF_VENTE_CYC_RAPPORT</t>
-  </si>
-  <si>
-    <t>JOB TERMINAL - rapport de fin de journee (commandes et CA du jour)</t>
-  </si>
-  <si>
-    <t>EOD_VENTES_TERMINE</t>
-  </si>
-  <si>
-    <t>Le lendemain, bin/montee_au_plan.sh archive EOD_VENTES_TERMINE (state/plan/history/), l'efface, et rouvre EOD_VENTES_WINDOW_OPEN - la chaine redevient eligible, sans intervention humaine.</t>
-  </si>
-  <si>
-    <t>Simulation reelle : ~50 traitements sous MAX_PARALLEL_JOBS=6 (meme algorithme que orchestrator.sh)</t>
-  </si>
-  <si>
     <t>Service</t>
   </si>
   <si>
@@ -1061,10 +1327,46 @@
     <t>CONSTRUIT - state/history/&lt;JOB_ID&gt;/, bin/view_history.sh</t>
   </si>
   <si>
-    <t>Calendrier (jobs EOD/EOM/TFJ auto-declenches)</t>
-  </si>
-  <si>
-    <t>CONSTRUIT - bin/montee_au_plan.sh, 1 cycle reel (Ventes EOD), 30+ modules restants sur le meme patron</t>
+    <t>Calendrier TFJ/EOM/EOW/EOQ/EOY (chaines auto-declenchees)</t>
+  </si>
+  <si>
+    <t>CONSTRUIT - bin/montee_au_plan.sh (5 cadences), 1 cycle TFJ + 1 cycle PURGE reels</t>
+  </si>
+  <si>
+    <t>EOD/CUTOFF (marqueur horodate, heure fixe)</t>
+  </si>
+  <si>
+    <t>CONSTRUIT - ECFCEOD1 (Comptabilite, 23h50) et ECFCCUT1 (Achat, 15h)</t>
+  </si>
+  <si>
+    <t>JOUR/NRT (intraday, garde horaire interne)</t>
+  </si>
+  <si>
+    <t>CONSTRUIT - ECFJVTSV (Ventes)</t>
+  </si>
+  <si>
+    <t>REPLAY (rejeu apres incident)</t>
+  </si>
+  <si>
+    <t>DEJA COUVERT - bin/rerun_job.sh / bin/order_job.sh</t>
+  </si>
+  <si>
+    <t>PURGE (archivage a froid periodique)</t>
+  </si>
+  <si>
+    <t>CONSTRUIT - ECFCPRG1</t>
+  </si>
+  <si>
+    <t>SIMULATION (stress test sur miroir)</t>
+  </si>
+  <si>
+    <t>A CONSTRUIRE - necessite un environnement miroir/sandbox dedie</t>
+  </si>
+  <si>
+    <t>REALTIME (evenementiel, Kafka/webhooks)</t>
+  </si>
+  <si>
+    <t>HORS PERIMETRE - architecture evenementielle incompatible avec un ordonnanceur batch bash/CSV</t>
   </si>
   <si>
     <t>Montee au plan / New Day (snapshot quotidien)</t>
@@ -1130,7 +1432,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1149,6 +1451,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEDF0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1162,7 +1476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1173,6 +1487,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1501,7 +1823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40EA069E-C37E-4E35-9D07-E3E8FDB1E4FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44B503F-E54F-48F8-B3E8-05AE9262FFDB}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1527,14 +1849,14 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -1545,12 +1867,12 @@
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -1561,14 +1883,14 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1579,12 +1901,12 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -1595,14 +1917,14 @@
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1618,17 +1940,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37157928-76FF-4E37-BD23-CB91E81F6830}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE1AE77-44A1-469E-A35D-801DD77B2B4C}">
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" customWidth="1"/>
     <col min="4" max="4" width="45.77734375" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1"/>
-    <col min="6" max="6" width="45.77734375" customWidth="1"/>
-    <col min="7" max="7" width="35.77734375" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="6" max="6" width="55.77734375" customWidth="1"/>
+    <col min="7" max="7" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1654,7 +1976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1700,7 +2022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>25</v>
       </c>
@@ -1769,7 +2091,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>44</v>
       </c>
@@ -1793,698 +2115,698 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+      <c r="G8" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>28</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="27" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="27" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{37157928-76FF-4E37-BD23-CB91E81F6830}"/>
+  <autoFilter ref="A1:G1" xr:uid="{FDE1AE77-44A1-469E-A35D-801DD77B2B4C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3D4F7A-4BAB-468D-BC40-D440E658C2C9}">
-  <dimension ref="A1:E9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE62E72-034C-49A6-8154-6E7EB4598AA7}">
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="55.77734375" customWidth="1"/>
-    <col min="5" max="5" width="24.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="40.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" customWidth="1"/>
+    <col min="5" max="5" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="A1" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -2494,117 +2816,460 @@
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="A3" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D3" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
+    <row r="4" spans="1:5" ht="93" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="93" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>3</v>
+      <c r="E5" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="106.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="79.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="D11" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>263</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <autoFilter ref="A3:E3" xr:uid="{0DE62E72-034C-49A6-8154-6E7EB4598AA7}"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4400B9-DF3B-4693-9AF8-03147BAE59A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FFCD391-2710-44F2-9FB7-551D10D1FEFA}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="55.77734375" customWidth="1"/>
+    <col min="5" max="5" width="30.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{520B399C-294A-4A60-8313-782D6DB2BE13}">
   <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2618,15 +3283,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="A1" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
@@ -2639,25 +3304,25 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>307</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>221</v>
+        <v>309</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>223</v>
+        <v>311</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="53.4" x14ac:dyDescent="0.3">
@@ -2665,13 +3330,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>225</v>
+        <v>313</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>226</v>
+        <v>314</v>
       </c>
       <c r="E4" s="4">
         <v>45</v>
@@ -2688,13 +3353,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="E5" s="4">
         <v>20</v>
@@ -2711,13 +3376,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>229</v>
+        <v>317</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="E6" s="4">
         <v>30</v>
@@ -2734,13 +3399,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>231</v>
+        <v>319</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>232</v>
+        <v>320</v>
       </c>
       <c r="E7" s="4">
         <v>25</v>
@@ -2757,13 +3422,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>233</v>
+        <v>321</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="E8" s="4">
         <v>40</v>
@@ -2780,13 +3445,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>235</v>
+        <v>323</v>
       </c>
       <c r="E9" s="4">
         <v>35</v>
@@ -2803,13 +3468,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>236</v>
+        <v>324</v>
       </c>
       <c r="E10" s="5">
         <v>20</v>
@@ -2826,13 +3491,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>214</v>
+        <v>285</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>237</v>
+        <v>325</v>
       </c>
       <c r="E11" s="5">
         <v>15</v>
@@ -2849,13 +3514,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="E12" s="5">
         <v>30</v>
@@ -2872,13 +3537,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>240</v>
+        <v>328</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="E13" s="5">
         <v>20</v>
@@ -2895,13 +3560,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="E14" s="5">
         <v>50</v>
@@ -2918,13 +3583,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>244</v>
+        <v>332</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="E15" s="5">
         <v>25</v>
@@ -2941,13 +3606,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>247</v>
+        <v>335</v>
       </c>
       <c r="E16" s="5">
         <v>60</v>
@@ -2964,13 +3629,13 @@
         <v>14</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>249</v>
+        <v>337</v>
       </c>
       <c r="E17" s="5">
         <v>90</v>
@@ -2987,13 +3652,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>250</v>
+        <v>338</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="E18" s="5">
         <v>20</v>
@@ -3010,13 +3675,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>252</v>
+        <v>340</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="E19" s="5">
         <v>35</v>
@@ -3033,13 +3698,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="E20" s="5">
         <v>15</v>
@@ -3056,13 +3721,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>256</v>
+        <v>344</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>257</v>
+        <v>345</v>
       </c>
       <c r="E21" s="5">
         <v>20</v>
@@ -3079,13 +3744,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>258</v>
+        <v>346</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="E22" s="5">
         <v>30</v>
@@ -3102,13 +3767,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>260</v>
+        <v>348</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>261</v>
+        <v>349</v>
       </c>
       <c r="E23" s="5">
         <v>10</v>
@@ -3125,13 +3790,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>263</v>
+        <v>351</v>
       </c>
       <c r="E24" s="5">
         <v>40</v>
@@ -3148,13 +3813,13 @@
         <v>22</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>264</v>
+        <v>352</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>265</v>
+        <v>353</v>
       </c>
       <c r="E25" s="5">
         <v>25</v>
@@ -3171,13 +3836,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>266</v>
+        <v>354</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>267</v>
+        <v>355</v>
       </c>
       <c r="E26" s="5">
         <v>20</v>
@@ -3194,13 +3859,13 @@
         <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>268</v>
+        <v>356</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
       <c r="E27" s="5">
         <v>15</v>
@@ -3217,13 +3882,13 @@
         <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>271</v>
+        <v>359</v>
       </c>
       <c r="E28" s="5">
         <v>30</v>
@@ -3240,13 +3905,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>272</v>
+        <v>360</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>273</v>
+        <v>361</v>
       </c>
       <c r="E29" s="5">
         <v>20</v>
@@ -3263,13 +3928,13 @@
         <v>27</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="E30" s="5">
         <v>35</v>
@@ -3286,13 +3951,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>276</v>
+        <v>364</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="E31" s="5">
         <v>45</v>
@@ -3309,13 +3974,13 @@
         <v>29</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>278</v>
+        <v>366</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>279</v>
+        <v>367</v>
       </c>
       <c r="E32" s="5">
         <v>10</v>
@@ -3332,13 +3997,13 @@
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>280</v>
+        <v>368</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>281</v>
+        <v>369</v>
       </c>
       <c r="E33" s="5">
         <v>30</v>
@@ -3355,13 +4020,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>282</v>
+        <v>370</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>283</v>
+        <v>371</v>
       </c>
       <c r="E34" s="5">
         <v>15</v>
@@ -3378,13 +4043,13 @@
         <v>32</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="E35" s="5">
         <v>10</v>
@@ -3401,13 +4066,13 @@
         <v>33</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>286</v>
+        <v>374</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>287</v>
+        <v>375</v>
       </c>
       <c r="E36" s="5">
         <v>20</v>
@@ -3424,13 +4089,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>288</v>
+        <v>376</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>289</v>
+        <v>377</v>
       </c>
       <c r="E37" s="5">
         <v>60</v>
@@ -3447,13 +4112,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>290</v>
+        <v>378</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>291</v>
+        <v>379</v>
       </c>
       <c r="E38" s="5">
         <v>30</v>
@@ -3470,13 +4135,13 @@
         <v>36</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>293</v>
+        <v>381</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
@@ -3493,13 +4158,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>294</v>
+        <v>382</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>295</v>
+        <v>383</v>
       </c>
       <c r="E40" s="5">
         <v>50</v>
@@ -3516,13 +4181,13 @@
         <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>297</v>
+        <v>385</v>
       </c>
       <c r="E41" s="5">
         <v>40</v>
@@ -3539,13 +4204,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>298</v>
+        <v>386</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>299</v>
+        <v>387</v>
       </c>
       <c r="E42" s="5">
         <v>10</v>
@@ -3562,13 +4227,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>300</v>
+        <v>388</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="E43" s="5">
         <v>20</v>
@@ -3585,13 +4250,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>302</v>
+        <v>390</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>303</v>
+        <v>391</v>
       </c>
       <c r="E44" s="5">
         <v>35</v>
@@ -3608,13 +4273,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>304</v>
+        <v>392</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>305</v>
+        <v>393</v>
       </c>
       <c r="E45" s="5">
         <v>120</v>
@@ -3631,13 +4296,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>306</v>
+        <v>394</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>307</v>
+        <v>395</v>
       </c>
       <c r="E46" s="5">
         <v>15</v>
@@ -3654,13 +4319,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>308</v>
+        <v>396</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>309</v>
+        <v>397</v>
       </c>
       <c r="E47" s="5">
         <v>10</v>
@@ -3677,13 +4342,13 @@
         <v>45</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>310</v>
+        <v>398</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>311</v>
+        <v>399</v>
       </c>
       <c r="E48" s="5">
         <v>10</v>
@@ -3700,13 +4365,13 @@
         <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>312</v>
+        <v>400</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>313</v>
+        <v>401</v>
       </c>
       <c r="E49" s="5">
         <v>25</v>
@@ -3723,13 +4388,13 @@
         <v>47</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>314</v>
+        <v>402</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="E50" s="5">
         <v>10</v>
@@ -3746,13 +4411,13 @@
         <v>48</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="E51" s="5">
         <v>20</v>
@@ -3769,13 +4434,13 @@
         <v>49</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>318</v>
+        <v>406</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>319</v>
+        <v>407</v>
       </c>
       <c r="E52" s="5">
         <v>35</v>
@@ -3792,13 +4457,13 @@
         <v>50</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>320</v>
+        <v>408</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>321</v>
+        <v>409</v>
       </c>
       <c r="E53" s="5">
         <v>45</v>
@@ -3815,13 +4480,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>323</v>
+        <v>411</v>
       </c>
       <c r="E54" s="5">
         <v>30</v>
@@ -3834,18 +4499,18 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
+      <c r="A56" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{5C4400B9-DF3B-4693-9AF8-03147BAE59A2}"/>
+  <autoFilter ref="A3:G3" xr:uid="{520B399C-294A-4A60-8313-782D6DB2BE13}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A56:G56"/>
@@ -3854,109 +4519,157 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2779DD9-7244-4588-8575-FB9548F3D43C}">
-  <dimension ref="A1:B12"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1A2ADCF-A946-4A47-B45D-055F07B86754}">
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.77734375" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="48.77734375" customWidth="1"/>
+    <col min="2" max="2" width="75.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>325</v>
+        <v>413</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>326</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="93" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>327</v>
+        <v>415</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>328</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>329</v>
+        <v>417</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>330</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="93" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>331</v>
+        <v>419</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>332</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="93" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>333</v>
+        <v>421</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>334</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>335</v>
+        <v>423</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>336</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>337</v>
+        <v>425</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="27" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>339</v>
+        <v>427</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>340</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>341</v>
+        <v>429</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="27" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>344</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>346</v>
+      <c r="A11" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>348</v>
+      <c r="A12" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="27" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="27" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,22 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F80ACD-A0BE-4D41-AD48-491CDF667316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B03D445-62C5-4B33-8C8C-D1DD7B16770B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{DDABEE53-8415-4B60-8DAA-76C5DBFE148E}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{6461E050-9495-4CF8-B8D4-17FCEB676545}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
     <sheet name="Objectifs par module" sheetId="2" r:id="rId2"/>
-    <sheet name="Taxonomie complete" sheetId="3" r:id="rId3"/>
-    <sheet name="Cycles reels construits" sheetId="4" r:id="rId4"/>
-    <sheet name="Scenario 50 traitements" sheetId="5" r:id="rId5"/>
-    <sheet name="Parite Control-M" sheetId="6" r:id="rId6"/>
+    <sheet name="Catalogue des operations" sheetId="6" r:id="rId3"/>
+    <sheet name="Taxonomie complete" sheetId="3" r:id="rId4"/>
+    <sheet name="Cycles reels construits" sheetId="4" r:id="rId5"/>
+    <sheet name="Exploitation MCO - efficacite" sheetId="7" r:id="rId6"/>
+    <sheet name="Scenario 50 traitements" sheetId="5" r:id="rId7"/>
+    <sheet name="Parite Control-M" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Catalogue des operations'!$A$3:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Objectifs par module'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenario 50 traitements'!$A$3:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Taxonomie complete'!$A$3:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Scenario 50 traitements'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Taxonomie complete'!$A$3:$E$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="621">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -1285,6 +1288,525 @@
     <t>Lignes en vert : les 6 traitements qui demarrent EXACTEMENT au meme instant (T+0) - la premiere vague. Chaque ligne suivante demarre des qu'UN emplacement se libere (pas le lot entier) - c'est le comportement reel verifie par harnais de simulation (voir docs/JOURNAL_TECHNIQUE.md, entree Phase A).</t>
   </si>
   <si>
+    <t>Catalogue des operations reelles possibles sur Odoo 19 Community - dimension bancaire (conformite, cycles, flux externes)</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>Type de traitement</t>
+  </si>
+  <si>
+    <t>Jobs estimes</t>
+  </si>
+  <si>
+    <t>Architecture (lineaire/parallele)</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Deploiement complet de l'infrastructure</t>
+  </si>
+  <si>
+    <t>Lineaire strict (chaque etape depend de la precedente)</t>
+  </si>
+  <si>
+    <t>CONSTRUIT</t>
+  </si>
+  <si>
+    <t>Deja construit - Tier 0 complet</t>
+  </si>
+  <si>
+    <t>Verification de bout en bout</t>
+  </si>
+  <si>
+    <t>Parallele</t>
+  </si>
+  <si>
+    <t>ECFRVER deja construit</t>
+  </si>
+  <si>
+    <t>Archivage a froid des fichiers arc/</t>
+  </si>
+  <si>
+    <t>Lineaire</t>
+  </si>
+  <si>
+    <t>ECFCPRG1 deja construit</t>
+  </si>
+  <si>
+    <t>Archivage legal annuel (conformite 10 ans)</t>
+  </si>
+  <si>
+    <t>Lineaire (selection - verification integrite - scellement - export stockage immuable)</t>
+  </si>
+  <si>
+    <t>A CONSTRUIRE</t>
+  </si>
+  <si>
+    <t>Distinct de PURGE mensuel - retention longue duree</t>
+  </si>
+  <si>
+    <t>Test de charge pre-deploiement</t>
+  </si>
+  <si>
+    <t>Parallele (plusieurs profils de charge simultanes)</t>
+  </si>
+  <si>
+    <t>HORS PERIMETRE</t>
+  </si>
+  <si>
+    <t>Necessite un environnement miroir dedie</t>
+  </si>
+  <si>
+    <t>Import de contacts en masse</t>
+  </si>
+  <si>
+    <t>Lineaire (validation fichier - dedup - import)</t>
+  </si>
+  <si>
+    <t>Meme patron que les jobs Tier1 deja construits ailleurs</t>
+  </si>
+  <si>
+    <t>Detection et fusion des doublons</t>
+  </si>
+  <si>
+    <t>Lineaire (scan - scoring similarite - fusion - rapport)</t>
+  </si>
+  <si>
+    <t>Synchronisation annuaire externe</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>Lineaire (pull - reconciliation)</t>
+  </si>
+  <si>
+    <t>Micro-batch 5-15 min si connecteur externe existant</t>
+  </si>
+  <si>
+    <t>Export annuaire consolide</t>
+  </si>
+  <si>
+    <t>Rappels de rendez-vous du jour</t>
+  </si>
+  <si>
+    <t>Autonome</t>
+  </si>
+  <si>
+    <t>Garde horaire interne comme ECFJVTSV</t>
+  </si>
+  <si>
+    <t>Detection de conflits d'agenda</t>
+  </si>
+  <si>
+    <t>Lineaire (scan - notification)</t>
+  </si>
+  <si>
+    <t>Synchronisation calendrier externe</t>
+  </si>
+  <si>
+    <t>Lineaire (pull - resolution conflits - push)</t>
+  </si>
+  <si>
+    <t>Nettoyage des evenements passes</t>
+  </si>
+  <si>
+    <t>Notification temps reel</t>
+  </si>
+  <si>
+    <t>Evenementiel</t>
+  </si>
+  <si>
+    <t>Architecture Kafka/webhooks - hors perimetre batch bash/CSV</t>
+  </si>
+  <si>
+    <t>Digest quotidien des mentions non lues</t>
+  </si>
+  <si>
+    <t>JOUR</t>
+  </si>
+  <si>
+    <t>Lineaire (extraction - envoi)</t>
+  </si>
+  <si>
+    <t>Purge des messages archives</t>
+  </si>
+  <si>
+    <t>Creation de piste</t>
+  </si>
+  <si>
+    <t>Conversion piste en opportunite</t>
+  </si>
+  <si>
+    <t>Avancement dans le pipeline</t>
+  </si>
+  <si>
+    <t>Marquage gagne/perdu</t>
+  </si>
+  <si>
+    <t>ECFRCRWO + ECFRCRLO</t>
+  </si>
+  <si>
+    <t>Relance des pistes stagnantes (&gt;7j)</t>
+  </si>
+  <si>
+    <t>Lineaire (detection - relance - rapport)</t>
+  </si>
+  <si>
+    <t>Meme patron que le TFJ Ventes deja construit</t>
+  </si>
+  <si>
+    <t>Score de qualification automatique</t>
+  </si>
+  <si>
+    <t>Lineaire (calcul - mise a jour)</t>
+  </si>
+  <si>
+    <t>Lineaire (extraction - KPI - envoi)</t>
+  </si>
+  <si>
+    <t>Creation de devis</t>
+  </si>
+  <si>
+    <t>Confirmation de commande</t>
+  </si>
+  <si>
+    <t>Facturation</t>
+  </si>
+  <si>
+    <t>Cloture quotidienne (relance-nettoyage-rapport)</t>
+  </si>
+  <si>
+    <t>Lineaire strict</t>
+  </si>
+  <si>
+    <t>ECFCVTRL-&gt;NT-&gt;RP</t>
+  </si>
+  <si>
+    <t>Suivi intraday des devis envoyes</t>
+  </si>
+  <si>
+    <t>Cloture commerciale mensuelle (objectifs-commissions)</t>
+  </si>
+  <si>
+    <t>Lineaire (consolidation - calcul commissions - validation - verrouillage - rapport)</t>
+  </si>
+  <si>
+    <t>Consolidation trimestrielle des ventes</t>
+  </si>
+  <si>
+    <t>Marqueur EOD (bascule date valeur)</t>
+  </si>
+  <si>
+    <t>Reconciliation bancaire quotidienne</t>
+  </si>
+  <si>
+    <t>Lineaire (import releve - rapprochement auto - exceptions - validation - rapport)</t>
+  </si>
+  <si>
+    <t>Relance factures impayees</t>
+  </si>
+  <si>
+    <t>Lineaire (detection - relance)</t>
+  </si>
+  <si>
+    <t>Generation de releves de compte PDF volumineux</t>
+  </si>
+  <si>
+    <t>DIFFERE</t>
+  </si>
+  <si>
+    <t>Lineaire (generation - archivage)</t>
+  </si>
+  <si>
+    <t>Traitement lourd decale hors heures de pointe</t>
+  </si>
+  <si>
+    <t>Exports comptables a heures fixes</t>
+  </si>
+  <si>
+    <t>INTRADAY</t>
+  </si>
+  <si>
+    <t>Lineaire (10h-14h-16h - 3 executions independantes)</t>
+  </si>
+  <si>
+    <t>Analogue aux cycles de compensation SEPA a heures fixes</t>
+  </si>
+  <si>
+    <t>Cloture comptable mensuelle</t>
+  </si>
+  <si>
+    <t>Lineaire (verif soldes - lettrage auto - provisions - balance - validation - verrouillage periode - export - notification - archivage)</t>
+  </si>
+  <si>
+    <t>Chaine lourde representative d'une vraie cloture bancaire</t>
+  </si>
+  <si>
+    <t>Declaration TVA et ratios prudentiels</t>
+  </si>
+  <si>
+    <t>Lineaire (extraction - calcul ratios - validation - generation etat - controle - transmission)</t>
+  </si>
+  <si>
+    <t>Travaux de fin d'annee (bascule exercice)</t>
+  </si>
+  <si>
+    <t>Lineaire + parallele (amortissements calcules en parallele par categorie d'actif - puis convergent vers la cloture)</t>
+  </si>
+  <si>
+    <t>Exemple explicite d'une chaine mixte lineaire/parallele a grande echelle</t>
+  </si>
+  <si>
+    <t>Creation de commande fournisseur</t>
+  </si>
+  <si>
+    <t>Marqueur CUTOFF commandes (15h)</t>
+  </si>
+  <si>
+    <t>Reapprovisionnement automatique nocturne</t>
+  </si>
+  <si>
+    <t>Lineaire (analyse seuils - proposition commandes - validation - envoi)</t>
+  </si>
+  <si>
+    <t>Analyse des depenses fournisseurs</t>
+  </si>
+  <si>
+    <t>Alertes de rupture en temps quasi-reel</t>
+  </si>
+  <si>
+    <t>Inventaire tournant et valorisation nocturne</t>
+  </si>
+  <si>
+    <t>Lineaire (comptage - ecarts - valorisation - ajustement - rapport - verrouillage)</t>
+  </si>
+  <si>
+    <t>Inventaire physique mensuel</t>
+  </si>
+  <si>
+    <t>Valorisation trimestrielle pour arrete</t>
+  </si>
+  <si>
+    <t>Lancement des ordres de fabrication planifies</t>
+  </si>
+  <si>
+    <t>Lineaire (10h-14h-16h)</t>
+  </si>
+  <si>
+    <t>Calcul des besoins nets (MRP run) nocturne</t>
+  </si>
+  <si>
+    <t>Rapport de rendement production</t>
+  </si>
+  <si>
+    <t>Notification avancement reparation</t>
+  </si>
+  <si>
+    <t>Rapport quotidien SAV</t>
+  </si>
+  <si>
+    <t>Alerte echeance assurance/controle technique</t>
+  </si>
+  <si>
+    <t>Controle entretien mensuel</t>
+  </si>
+  <si>
+    <t>Cloture de caisse quotidienne</t>
+  </si>
+  <si>
+    <t>Lineaire (comptage - rapprochement - ecarts - validation)</t>
+  </si>
+  <si>
+    <t>Rapport ventes mensuel par point de vente</t>
+  </si>
+  <si>
+    <t>Cloture de service (midi/soir)</t>
+  </si>
+  <si>
+    <t>Verification liens morts et formulaires</t>
+  </si>
+  <si>
+    <t>Rapport ventes en ligne et paniers abandonnes</t>
+  </si>
+  <si>
+    <t>Relance paniers abandonnes</t>
+  </si>
+  <si>
+    <t>Rappel evenements du jour</t>
+  </si>
+  <si>
+    <t>Rapport frequentation mensuel</t>
+  </si>
+  <si>
+    <t>Rapport progression formations</t>
+  </si>
+  <si>
+    <t>Rapport effectifs et anciennete</t>
+  </si>
+  <si>
+    <t>Bilan social annuel</t>
+  </si>
+  <si>
+    <t>Rapport presences et anomalies quotidien</t>
+  </si>
+  <si>
+    <t>Calcul des heures travaillees mensuel (base paie)</t>
+  </si>
+  <si>
+    <t>Lineaire (extraction - calcul - validation - export)</t>
+  </si>
+  <si>
+    <t>Relance des demandes en attente</t>
+  </si>
+  <si>
+    <t>Solde des conges N vers N+1</t>
+  </si>
+  <si>
+    <t>Rapport depenses mensuel et export compta</t>
+  </si>
+  <si>
+    <t>Relance candidatures en attente</t>
+  </si>
+  <si>
+    <t>Rapport ecarts de competences</t>
+  </si>
+  <si>
+    <t>Rapport avancement quotidien</t>
+  </si>
+  <si>
+    <t>Facturation au temps passe mensuelle</t>
+  </si>
+  <si>
+    <t>Rappel des taches du jour</t>
+  </si>
+  <si>
+    <t>Planning de maintenance preventive mensuel</t>
+  </si>
+  <si>
+    <t>Cloture automatique des sondages echus</t>
+  </si>
+  <si>
+    <t>Cutoff des commandes du jour (11h)</t>
+  </si>
+  <si>
+    <t>Rapport hebdomadaire des conversations non traitees</t>
+  </si>
+  <si>
+    <t>Envoi des campagnes planifiees</t>
+  </si>
+  <si>
+    <t>Lineaire (selection - envoi)</t>
+  </si>
+  <si>
+    <t>Rapport de performance des campagnes</t>
+  </si>
+  <si>
+    <t>Envoi des campagnes SMS planifiees</t>
+  </si>
+  <si>
+    <t>Rapport de partage/engagement</t>
+  </si>
+  <si>
+    <t>Detection mensuelle des donnees perimees</t>
+  </si>
+  <si>
+    <t>Distinct du PURGE systeme global (ECFCPRG1) - specifique au module data_recycle</t>
+  </si>
+  <si>
+    <t>TOTAL : 86 operations reelles cataloguees, 228 jobs estimes au total (lineaires + paralleles cumules) - 17 operations deja CONSTRUITES ET VERIFIEES a ce jour, le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE).</t>
+  </si>
+  <si>
+    <t>Maintien en condition operationnelle - preuves d'efficacite reelles</t>
+  </si>
+  <si>
+    <t>Axe</t>
+  </si>
+  <si>
+    <t>Chiffre reel</t>
+  </si>
+  <si>
+    <t>Preuve / mecanisme</t>
+  </si>
+  <si>
+    <t>Parallelisme structurel</t>
+  </si>
+  <si>
+    <t>34 modules independants, plafonnes a MAX_PARALLEL_JOBS=6</t>
+  </si>
+  <si>
+    <t>6 vagues au maximum (34/6 arrondi) au lieu de 34 executions sequentielles - jamais un par un comme WAZ_ELK_FACTORY. Verifie par harnais de simulation (demarrage groupe, liberation individuelle par emplacement).</t>
+  </si>
+  <si>
+    <t>Isolation de panne</t>
+  </si>
+  <si>
+    <t>34/34 modules verifies structurellement independants</t>
+  </si>
+  <si>
+    <t>./bin/verifier_independance_modules.sh - teste avec une fausse dependance injectee, detectee, puis restauree. Un service en echec n'arrete jamais les autres.</t>
+  </si>
+  <si>
+    <t>Tracabilite / audit</t>
+  </si>
+  <si>
+    <t>123 jobs, registre a 7 colonnes</t>
+  </si>
+  <si>
+    <t>TIMESTAMP,JOB_ID,JOB_NAME,RESULT,LOG_FILE,DURATION_SEC,PATH_TOUCHED - chaque execution laisse un log dedie ET une ligne d'audit, jamais melanges.</t>
+  </si>
+  <si>
+    <t>Diagnostic post-incident</t>
+  </si>
+  <si>
+    <t>Aucun grep de log necessaire</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh &lt;JOB_ID&gt; et state/RAPPORT_EXECUTION.txt donnent immediatement le detail d'une execution precise et le bilan complet d'un run.</t>
+  </si>
+  <si>
+    <t>Couverture des cycles calendaires</t>
+  </si>
+  <si>
+    <t>5 des 14 types de la taxonomie construits et verifies</t>
+  </si>
+  <si>
+    <t>JOUR/NRT, TFJ, EOD, CUTOFF, PURGE - EOW/EOM/EOQ/EOY prets structurellement (memes cadences dans bin/montee_au_plan.sh), REPLAY deja couvert par les outils d'exploitation existants.</t>
+  </si>
+  <si>
+    <t>Couverture du catalogue d'operations</t>
+  </si>
+  <si>
+    <t>17 des 86 operations cataloguees deja construites (~20%)</t>
+  </si>
+  <si>
+    <t>228 jobs estimes au total sur l'ensemble du catalogue si tout etait construit - roadmap explicite, jamais presente comme deja fait.</t>
+  </si>
+  <si>
+    <t>Discipline de verification</t>
+  </si>
+  <si>
+    <t>Chaque ajout verifie avant commit, jamais suppose</t>
+  </si>
+  <si>
+    <t>bash -n systematique, verification des colonnes/doublons jobs_table.csv, verifier_independance_modules.sh, tests unitaires isoles pour toute nouvelle logique (cadences calendaires, parallelisme).</t>
+  </si>
+  <si>
+    <t>Vocabulaire d'exploitation reel</t>
+  </si>
+  <si>
+    <t>Hold/Free/Rerun/Order/Kill/Confirm/Delete</t>
+  </si>
+  <si>
+    <t>Memes termes qu'un vrai poste operateur Control-M - aucune paraphrase francaise, recherche immediate par un operateur deja forme.</t>
+  </si>
+  <si>
+    <t>Principe directeur : jamais suppose, toujours verifie. Chaque ligne ci-dessus est verifiable dans le depot (docs/JOURNAL_TECHNIQUE.md donne la date et la preuve de chaque decision).</t>
+  </si>
+  <si>
     <t>Concept Control-M</t>
   </si>
   <si>
@@ -1301,9 +1823,6 @@
   </si>
   <si>
     <t>CONSTRUIT - colonnes IN_COND/OUT_COND, operateur OU (|)</t>
-  </si>
-  <si>
-    <t>Hold/Free/Rerun/Order/Kill/Confirm/Delete</t>
   </si>
   <si>
     <t>CONSTRUIT - bin/hold_job.sh et consorts, vocabulaire reel</t>
@@ -1397,7 +1916,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1430,6 +1949,22 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1476,10 +2011,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1500,10 +2037,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1823,7 +2368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44B503F-E54F-48F8-B3E8-05AE9262FFDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78616FE7-225E-4E78-BE01-750488388E97}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1849,14 +2394,14 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -1867,12 +2412,12 @@
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -1883,14 +2428,14 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1901,12 +2446,12 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -1917,14 +2462,14 @@
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1940,7 +2485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE1AE77-44A1-469E-A35D-801DD77B2B4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27014042-126D-48E0-A9EF-7B95549A77F8}">
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1954,841 +2499,3048 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="66.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="9" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="9" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="9" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="9" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="9" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="9" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="9" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="9" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="9" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="9" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="9" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="9" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="9" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="9" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="9" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="9" t="s">
         <v>199</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{FDE1AE77-44A1-469E-A35D-801DD77B2B4C}"/>
+  <autoFilter ref="A1:G1" xr:uid="{27014042-126D-48E0-A9EF-7B95549A77F8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE62E72-034C-49A6-8154-6E7EB4598AA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348D6ABD-8051-4D2D-A196-5BDB0B5E79AE}">
+  <dimension ref="A1:H91"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="40.77734375" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="45.77734375" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="8" max="8" width="40.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="79.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="8">
+        <v>20</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="106.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="9">
+        <v>4</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="66.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="13">
+        <v>6</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="66.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="9">
+        <v>4</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H10" s="9"/>
+    </row>
+    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="9">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H14" s="9"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H15" s="9"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" s="13">
+        <v>1</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E18" s="9">
+        <v>2</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="9">
+        <v>3</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E25" s="9">
+        <v>2</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="9">
+        <v>3</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="9">
+        <v>5</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" s="9">
+        <v>4</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="9">
+        <v>5</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H35" s="9"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="9">
+        <v>2</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="E37" s="9">
+        <v>2</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="E38" s="9">
+        <v>3</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="9">
+        <v>9</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E40" s="9">
+        <v>6</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H40" s="9"/>
+    </row>
+    <row r="41" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E41" s="9">
+        <v>12</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="9">
+        <v>4</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H46" s="9"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="9">
+        <v>3</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H47" s="9"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E48" s="9">
+        <v>2</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="9">
+        <v>6</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H49" s="9"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="9">
+        <v>5</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H50" s="9"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E51" s="9">
+        <v>3</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H51" s="9"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="E52" s="9">
+        <v>3</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H52" s="9"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="9">
+        <v>4</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H53" s="9"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="9">
+        <v>2</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H54" s="9"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H55" s="9"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="9">
+        <v>2</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H56" s="9"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E57" s="9">
+        <v>1</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H57" s="9"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" s="9">
+        <v>2</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H58" s="9"/>
+    </row>
+    <row r="59" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="9">
+        <v>4</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H59" s="9"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="9">
+        <v>3</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H60" s="9"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="9">
+        <v>3</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H61" s="9"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62" s="9">
+        <v>2</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H62" s="9"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="9">
+        <v>3</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H63" s="9"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" s="9">
+        <v>2</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H64" s="9"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E65" s="9">
+        <v>1</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H65" s="9"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" s="9">
+        <v>2</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H66" s="9"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="9">
+        <v>2</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H67" s="9"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E68" s="9">
+        <v>1</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H68" s="9"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="9">
+        <v>2</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H69" s="9"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E70" s="9">
+        <v>3</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H70" s="9"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" s="9">
+        <v>2</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H71" s="9"/>
+    </row>
+    <row r="72" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" s="9">
+        <v>4</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H72" s="9"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" s="9">
+        <v>1</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H73" s="9"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E74" s="9">
+        <v>2</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H74" s="9"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="9">
+        <v>3</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H75" s="9"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="9">
+        <v>1</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H76" s="9"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="9">
+        <v>2</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H77" s="9"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E78" s="9">
+        <v>2</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H78" s="9"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="9">
+        <v>3</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H79" s="9"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" s="9">
+        <v>1</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H80" s="9"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" s="9">
+        <v>2</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H81" s="9"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82" s="9">
+        <v>1</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H82" s="9"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E83" s="9">
+        <v>1</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H83" s="9"/>
+    </row>
+    <row r="84" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="A84" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E84" s="9">
+        <v>1</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H84" s="9"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" s="9">
+        <v>2</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H85" s="9"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" s="9">
+        <v>2</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H86" s="9"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="9">
+        <v>2</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H87" s="9"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E88" s="9">
+        <v>1</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H88" s="9"/>
+    </row>
+    <row r="89" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A89" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89" s="9">
+        <v>2</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="B91" s="19"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="19"/>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="19"/>
+      <c r="H91" s="19"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H3" xr:uid="{348D6ABD-8051-4D2D-A196-5BDB0B5E79AE}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A91:H91"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2F3472-0384-4FB1-9048-9EDBA4ECF2EA}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2800,261 +5552,261 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="93" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="93" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="8" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="8" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="8" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="12" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="8" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="13" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="13" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="12" t="s">
         <v>263</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{0DE62E72-034C-49A6-8154-6E7EB4598AA7}"/>
+  <autoFilter ref="A3:E3" xr:uid="{CF2F3472-0384-4FB1-9048-9EDBA4ECF2EA}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -3062,8 +5814,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FFCD391-2710-44F2-9FB7-551D10D1FEFA}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABD72BB-8C8A-4680-9DE1-CBBECCF9607A}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3075,189 +5827,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="14" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="27" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3268,8 +6020,146 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{520B399C-294A-4A60-8313-782D6DB2BE13}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAD0442-1356-41B3-B0C4-531EAF7077B3}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.77734375" customWidth="1"/>
+    <col min="2" max="2" width="45.77734375" customWidth="1"/>
+    <col min="3" max="3" width="65.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>583</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:C13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E9E754-02DB-453F-8243-2334DAD22253}">
   <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3283,1234 +6173,1234 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="6">
         <v>45</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="6">
         <v>0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="6">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="6">
         <v>20</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="6">
         <v>30</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="6">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="6">
         <v>25</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="6">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="6">
         <v>40</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="6">
         <v>0</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="6">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="6">
         <v>35</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="6">
         <v>0</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="6">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="7">
         <v>20</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="7">
         <v>20</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="7">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="7">
         <v>15</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="7">
         <v>25</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="7">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="7">
         <v>30</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <v>30</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="7">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="7">
         <v>20</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="7">
         <v>35</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="7">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+      <c r="A14" s="7">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="7">
         <v>50</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>40</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="7">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="A15" s="7">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="7">
         <v>25</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <v>40</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="7">
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="A16" s="7">
         <v>13</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="7">
         <v>60</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="7">
         <v>40</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="7">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="7">
         <v>90</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="7">
         <v>45</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="7">
         <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+      <c r="A18" s="7">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="7">
         <v>20</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
         <v>55</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="7">
         <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="7">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="7">
         <v>35</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="7">
         <v>60</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="7">
         <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="A20" s="7">
         <v>17</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="7">
         <v>15</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="7">
         <v>65</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="7">
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="7">
         <v>18</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="7">
         <v>75</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="7">
         <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="A22" s="7">
         <v>19</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="7">
         <v>30</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="7">
         <v>80</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="7">
         <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="A23" s="7">
         <v>20</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="7">
         <v>10</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="7">
         <v>90</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
+      <c r="A24" s="7">
         <v>21</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="7">
         <v>40</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="7">
         <v>95</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="7">
         <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="A25" s="7">
         <v>22</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="7">
         <v>25</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="7">
         <v>95</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="7">
         <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+      <c r="A26" s="7">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="7">
         <v>20</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="7">
         <v>100</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="7">
         <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="A27" s="7">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="7">
         <v>15</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="7">
         <v>100</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="7">
         <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="A28" s="7">
         <v>25</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="7">
         <v>30</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="7">
         <v>110</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="7">
         <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="A29" s="7">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="7">
         <v>20</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="7">
         <v>115</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="7">
         <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="A30" s="7">
         <v>27</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="7">
         <v>35</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="7">
         <v>120</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="7">
         <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="A31" s="7">
         <v>28</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="7">
         <v>45</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="7">
         <v>120</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="7">
         <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
+      <c r="A32" s="7">
         <v>29</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="7">
         <v>10</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="7">
         <v>135</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="7">
         <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+      <c r="A33" s="7">
         <v>30</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="7">
         <v>30</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="7">
         <v>135</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="7">
         <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+      <c r="A34" s="7">
         <v>31</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="7">
         <v>15</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="7">
         <v>135</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="7">
         <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+      <c r="A35" s="7">
         <v>32</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="7">
         <v>10</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="7">
         <v>140</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="7">
         <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5">
+      <c r="A36" s="7">
         <v>33</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="7">
         <v>20</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="7">
         <v>145</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="7">
         <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="A37" s="7">
         <v>34</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="7">
         <v>60</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="7">
         <v>150</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="7">
         <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="5">
+      <c r="A38" s="7">
         <v>35</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="7">
         <v>30</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="7">
         <v>150</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="7">
         <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+      <c r="A39" s="7">
         <v>36</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="7">
         <v>15</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="7">
         <v>155</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="7">
         <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+      <c r="A40" s="7">
         <v>37</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="7">
         <v>50</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="7">
         <v>165</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="7">
         <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
+      <c r="A41" s="7">
         <v>38</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="7">
         <v>40</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="7">
         <v>165</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="7">
         <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
+      <c r="A42" s="7">
         <v>39</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="7">
         <v>10</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="7">
         <v>165</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="7">
         <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
+      <c r="A43" s="7">
         <v>40</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="7">
         <v>20</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="7">
         <v>170</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="7">
         <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5">
+      <c r="A44" s="7">
         <v>41</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="7">
         <v>35</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="7">
         <v>175</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="7">
         <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
+      <c r="A45" s="7">
         <v>42</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="7">
         <v>120</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="7">
         <v>180</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="7">
         <v>300</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="5">
+      <c r="A46" s="7">
         <v>43</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="7">
         <v>15</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="7">
         <v>190</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="7">
         <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="5">
+      <c r="A47" s="7">
         <v>44</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="7">
         <v>10</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="7">
         <v>205</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="7">
         <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="5">
+      <c r="A48" s="7">
         <v>45</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="7">
         <v>10</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="7">
         <v>205</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="7">
         <v>215</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
+      <c r="A49" s="7">
         <v>46</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="7">
         <v>25</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="7">
         <v>210</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="7">
         <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="5">
+      <c r="A50" s="7">
         <v>47</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="7">
         <v>10</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="7">
         <v>210</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="7">
         <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
+      <c r="A51" s="7">
         <v>48</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="7">
         <v>20</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="7">
         <v>215</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="7">
         <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="5">
+      <c r="A52" s="7">
         <v>49</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="7">
         <v>35</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="7">
         <v>215</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="7">
         <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="5">
+      <c r="A53" s="7">
         <v>50</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="7">
         <v>45</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="7">
         <v>215</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="7">
         <v>260</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="5">
+      <c r="A54" s="7">
         <v>51</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="7">
         <v>30</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="7">
         <v>220</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54" s="7">
         <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{520B399C-294A-4A60-8313-782D6DB2BE13}"/>
+  <autoFilter ref="A3:G3" xr:uid="{85E9E754-02DB-453F-8243-2334DAD22253}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A56:G56"/>
@@ -4519,8 +7409,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1A2ADCF-A946-4A47-B45D-055F07B86754}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39E84D-A09D-4E68-8461-C2CCAB41C53C}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4529,147 +7419,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>414</v>
+      <c r="A1" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="93" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>416</v>
+      <c r="A2" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>418</v>
+      <c r="A3" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="93" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>420</v>
+      <c r="A4" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="93" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>422</v>
+      <c r="A5" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>424</v>
+      <c r="A6" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>426</v>
+      <c r="A7" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>428</v>
+      <c r="A8" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>430</v>
+      <c r="A9" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>432</v>
+      <c r="A10" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>434</v>
+      <c r="A11" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>436</v>
+      <c r="A12" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>438</v>
+      <c r="A13" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="27" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>440</v>
+      <c r="A14" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>442</v>
+      <c r="A15" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="27" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>444</v>
+      <c r="A16" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>446</v>
+      <c r="A17" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>448</v>
+      <c r="A18" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B03D445-62C5-4B33-8C8C-D1DD7B16770B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4F0E46-69BD-4745-B287-05ED0378A664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{6461E050-9495-4CF8-B8D4-17FCEB676545}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{24C1E762-0FA7-4FAE-AD7C-E2742EFFC62A}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Parite Control-M" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Catalogue des operations'!$A$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Catalogue des operations'!$A$3:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Objectifs par module'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Scenario 50 traitements'!$A$3:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Taxonomie complete'!$A$3:$E$3</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="715">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -1294,6 +1294,9 @@
     <t>Operation</t>
   </si>
   <si>
+    <t>Explication metier (langage clair)</t>
+  </si>
+  <si>
     <t>Type de traitement</t>
   </si>
   <si>
@@ -1303,24 +1306,36 @@
     <t>Architecture (lineaire/parallele)</t>
   </si>
   <si>
+    <t>Priorite</t>
+  </si>
+  <si>
     <t>Justification</t>
   </si>
   <si>
     <t>Deploiement complet de l'infrastructure</t>
   </si>
   <si>
+    <t>Installe tout ce qu'il faut (base de donnees - serveur - securite) pour qu'Odoo fonctionne - comme monter les murs et l'electricite avant d'amenager les pieces</t>
+  </si>
+  <si>
     <t>Lineaire strict (chaque etape depend de la precedente)</t>
   </si>
   <si>
     <t>CONSTRUIT</t>
   </si>
   <si>
+    <t>FAIT</t>
+  </si>
+  <si>
     <t>Deja construit - Tier 0 complet</t>
   </si>
   <si>
     <t>Verification de bout en bout</t>
   </si>
   <si>
+    <t>Verifie - comme un vrai client le ferait - que le site est bien accessible et fonctionnel apres l'installation</t>
+  </si>
+  <si>
     <t>Parallele</t>
   </si>
   <si>
@@ -1330,6 +1345,9 @@
     <t>Archivage a froid des fichiers arc/</t>
   </si>
   <si>
+    <t>Range les fichiers deja traites depuis longtemps dans un coin pour ne pas encombrer l'espace de travail quotidien</t>
+  </si>
+  <si>
     <t>Lineaire</t>
   </si>
   <si>
@@ -1339,30 +1357,45 @@
     <t>Archivage legal annuel (conformite 10 ans)</t>
   </si>
   <si>
+    <t>Conserve une copie inalterable des documents anciens (plus de 10 ans) pour pouvoir les produire en cas de controle meme longtemps apres</t>
+  </si>
+  <si>
     <t>Lineaire (selection - verification integrite - scellement - export stockage immuable)</t>
   </si>
   <si>
     <t>A CONSTRUIRE</t>
   </si>
   <si>
+    <t>MOYENNE</t>
+  </si>
+  <si>
     <t>Distinct de PURGE mensuel - retention longue duree</t>
   </si>
   <si>
     <t>Test de charge pre-deploiement</t>
   </si>
   <si>
+    <t>Simule beaucoup d'utilisateurs en meme temps sur une copie du systeme pour verifier qu'il tient la charge avant un vrai lancement</t>
+  </si>
+  <si>
     <t>Parallele (plusieurs profils de charge simultanes)</t>
   </si>
   <si>
     <t>HORS PERIMETRE</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Necessite un environnement miroir dedie</t>
   </si>
   <si>
     <t>Import de contacts en masse</t>
   </si>
   <si>
+    <t>Charge d'un coup une longue liste de clients/fournisseurs (ex. depuis un tableur) plutot que de les saisir un par un</t>
+  </si>
+  <si>
     <t>Lineaire (validation fichier - dedup - import)</t>
   </si>
   <si>
@@ -1372,27 +1405,42 @@
     <t>Detection et fusion des doublons</t>
   </si>
   <si>
+    <t>Repere les fiches en double (meme client saisi deux fois par erreur) et les fusionne en une seule</t>
+  </si>
+  <si>
     <t>Lineaire (scan - scoring similarite - fusion - rapport)</t>
   </si>
   <si>
     <t>Synchronisation annuaire externe</t>
   </si>
   <si>
+    <t>Garde les coordonnees a jour automatiquement avec un annuaire externe (ex. changement d'adresse) sans ressaisie manuelle</t>
+  </si>
+  <si>
     <t>NRT</t>
   </si>
   <si>
     <t>Lineaire (pull - reconciliation)</t>
   </si>
   <si>
+    <t>BASSE</t>
+  </si>
+  <si>
     <t>Micro-batch 5-15 min si connecteur externe existant</t>
   </si>
   <si>
     <t>Export annuaire consolide</t>
   </si>
   <si>
+    <t>Produit une liste complete et propre de tous les contacts prete a etre partagee ou imprimee</t>
+  </si>
+  <si>
     <t>Rappels de rendez-vous du jour</t>
   </si>
   <si>
+    <t>Envoie un rappel avant chaque rendez-vous du jour pour eviter les oublis</t>
+  </si>
+  <si>
     <t>Autonome</t>
   </si>
   <si>
@@ -1402,21 +1450,33 @@
     <t>Detection de conflits d'agenda</t>
   </si>
   <si>
+    <t>Repere si deux rendez-vous ont ete pris au meme creneau par erreur</t>
+  </si>
+  <si>
     <t>Lineaire (scan - notification)</t>
   </si>
   <si>
     <t>Synchronisation calendrier externe</t>
   </si>
   <si>
+    <t>Garde l'agenda Odoo aligne avec un calendrier externe (Google - Outlook) utilise par ailleurs</t>
+  </si>
+  <si>
     <t>Lineaire (pull - resolution conflits - push)</t>
   </si>
   <si>
     <t>Nettoyage des evenements passes</t>
   </si>
   <si>
+    <t>Range les rendez-vous deja passes pour garder un agenda lisible</t>
+  </si>
+  <si>
     <t>Notification temps reel</t>
   </si>
   <si>
+    <t>Alerte immediatement un utilisateur quand quelqu'un le mentionne dans une discussion - hors de portee d'un simple batch</t>
+  </si>
+  <si>
     <t>Evenementiel</t>
   </si>
   <si>
@@ -1426,6 +1486,9 @@
     <t>Digest quotidien des mentions non lues</t>
   </si>
   <si>
+    <t>Envoie un resume une fois par jour de tout ce qu'on a manque pour ceux qui ne regardent pas la messagerie en continu</t>
+  </si>
+  <si>
     <t>JOUR</t>
   </si>
   <si>
@@ -1435,51 +1498,90 @@
     <t>Purge des messages archives</t>
   </si>
   <si>
+    <t>Efface les vieux messages internes pour ne pas alourdir la base indefiniment</t>
+  </si>
+  <si>
     <t>Creation de piste</t>
   </si>
   <si>
+    <t>Un premier contact manifeste un interet sans engagement - on note son nom - son telephone - ce qu'il veut</t>
+  </si>
+  <si>
     <t>Conversion piste en opportunite</t>
   </si>
   <si>
+    <t>Le commercial confirme que c'est du serieux (client reel - besoin reel) - la piste devient un dossier commercial suivi avec un montant potentiel</t>
+  </si>
+  <si>
     <t>Avancement dans le pipeline</t>
   </si>
   <si>
+    <t>L'opportunite progresse par etapes (Nouveau - Devis envoye - Negociation) au fur et a mesure de la vraie discussion avec le client</t>
+  </si>
+  <si>
     <t>Marquage gagne/perdu</t>
   </si>
   <si>
+    <t>A la fin - le client dit oui (Gagne - contrat signe) ou non (Perdu - avec un motif) - le dossier se ferme</t>
+  </si>
+  <si>
     <t>ECFRCRWO + ECFRCRLO</t>
   </si>
   <si>
     <t>Relance des pistes stagnantes (&gt;7j)</t>
   </si>
   <si>
+    <t>Si personne n'a touche un dossier depuis 7 jours il risque de mourir par oubli - on liste ces dossiers pour qu'un commercial les rappelle</t>
+  </si>
+  <si>
     <t>Lineaire (detection - relance - rapport)</t>
   </si>
   <si>
+    <t>HAUTE</t>
+  </si>
+  <si>
     <t>Meme patron que le TFJ Ventes deja construit</t>
   </si>
   <si>
     <t>Score de qualification automatique</t>
   </si>
   <si>
+    <t>Au lieu qu'un humain devine a l'oeil quelles pistes sont prometteuses - un calcul automatique les classe pour dire au commercial laquelle appeler en premier</t>
+  </si>
+  <si>
     <t>Lineaire (calcul - mise a jour)</t>
   </si>
   <si>
+    <t>Un resume chaque semaine pour le responsable commercial : nouvelles pistes - conversions - gagnes/perdus - valeur totale du pipeline</t>
+  </si>
+  <si>
     <t>Lineaire (extraction - KPI - envoi)</t>
   </si>
   <si>
     <t>Creation de devis</t>
   </si>
   <si>
+    <t>Un client demande un prix pour un produit/service - on prepare une offre chiffree</t>
+  </si>
+  <si>
     <t>Confirmation de commande</t>
   </si>
   <si>
+    <t>Le client accepte le devis - ca devient une vraie commande a honorer</t>
+  </si>
+  <si>
     <t>Facturation</t>
   </si>
   <si>
+    <t>Une fois la commande livree/rendue on emet la facture correspondante</t>
+  </si>
+  <si>
     <t>Cloture quotidienne (relance-nettoyage-rapport)</t>
   </si>
   <si>
+    <t>Chaque soir : on relance les devis en attente - on nettoie les vieux devis morts - on fait le bilan de la journee</t>
+  </si>
+  <si>
     <t>Lineaire strict</t>
   </si>
   <si>
@@ -1489,33 +1591,54 @@
     <t>Suivi intraday des devis envoyes</t>
   </si>
   <si>
+    <t>Pendant la journee on surveille si un devis envoye reste sans reponse trop longtemps pour relancer vite pendant que le client y pense encore</t>
+  </si>
+  <si>
     <t>Cloture commerciale mensuelle (objectifs-commissions)</t>
   </si>
   <si>
+    <t>Fin de mois : on calcule qui a atteint ses objectifs - les commissions des commerciaux - et on verrouille les chiffres du mois</t>
+  </si>
+  <si>
     <t>Lineaire (consolidation - calcul commissions - validation - verrouillage - rapport)</t>
   </si>
   <si>
     <t>Consolidation trimestrielle des ventes</t>
   </si>
   <si>
+    <t>Tous les 3 mois on regroupe les chiffres de vente pour une vue d'ensemble sur le trimestre</t>
+  </si>
+  <si>
     <t>Marqueur EOD (bascule date valeur)</t>
   </si>
   <si>
+    <t>Chaque soir a heure fixe on bascule officiellement la date comptable au jour suivant - comme tourner la page du registre</t>
+  </si>
+  <si>
     <t>Reconciliation bancaire quotidienne</t>
   </si>
   <si>
+    <t>On verifie que ce que dit la banque correspond a ce qu'Odoo a enregistre chaque jour pour reperer vite une erreur</t>
+  </si>
+  <si>
     <t>Lineaire (import releve - rapprochement auto - exceptions - validation - rapport)</t>
   </si>
   <si>
     <t>Relance factures impayees</t>
   </si>
   <si>
+    <t>On repere les factures pas encore payees et on relance les clients concernes</t>
+  </si>
+  <si>
     <t>Lineaire (detection - relance)</t>
   </si>
   <si>
     <t>Generation de releves de compte PDF volumineux</t>
   </si>
   <si>
+    <t>On produit les releves de compte en PDF pour les clients - un traitement lourd fait la nuit pour ne pas ralentir la journee</t>
+  </si>
+  <si>
     <t>DIFFERE</t>
   </si>
   <si>
@@ -1528,6 +1651,9 @@
     <t>Exports comptables a heures fixes</t>
   </si>
   <si>
+    <t>Plusieurs fois par jour a heures precises on exporte les ecritures comptables du moment vers un systeme externe</t>
+  </si>
+  <si>
     <t>INTRADAY</t>
   </si>
   <si>
@@ -1540,6 +1666,9 @@
     <t>Cloture comptable mensuelle</t>
   </si>
   <si>
+    <t>Fin de mois : verifier les soldes - rapprocher les paiements - calculer les provisions - produire le bilan - puis verrouiller la periode pour que rien ne puisse plus etre modifie apres coup</t>
+  </si>
+  <si>
     <t>Lineaire (verif soldes - lettrage auto - provisions - balance - validation - verrouillage periode - export - notification - archivage)</t>
   </si>
   <si>
@@ -1549,12 +1678,18 @@
     <t>Declaration TVA et ratios prudentiels</t>
   </si>
   <si>
+    <t>Chaque trimestre on calcule la TVA a declarer et les ratios financiers reglementaires a transmettre</t>
+  </si>
+  <si>
     <t>Lineaire (extraction - calcul ratios - validation - generation etat - controle - transmission)</t>
   </si>
   <si>
     <t>Travaux de fin d'annee (bascule exercice)</t>
   </si>
   <si>
+    <t>Le 31 decembre : on cloture l'annee comptable - on calcule les amortissements de tous les biens de l'entreprise - et on ouvre la nouvelle annee - le plus gros chantier de l'annee</t>
+  </si>
+  <si>
     <t>Lineaire + parallele (amortissements calcules en parallele par categorie d'actif - puis convergent vers la cloture)</t>
   </si>
   <si>
@@ -1564,160 +1699,304 @@
     <t>Creation de commande fournisseur</t>
   </si>
   <si>
+    <t>On passe commande a un fournisseur pour reapprovisionner</t>
+  </si>
+  <si>
+    <t>Le fournisseur confirme qu'il peut livrer - la commande devient ferme</t>
+  </si>
+  <si>
+    <t>La livraison arrive - on l'enregistre - le stock augmente</t>
+  </si>
+  <si>
     <t>Marqueur CUTOFF commandes (15h)</t>
   </si>
   <si>
+    <t>Passe 15h toute nouvelle commande fournisseur est comptee sur la date de valeur du lendemain - une regle d'heure limite</t>
+  </si>
+  <si>
     <t>Reapprovisionnement automatique nocturne</t>
   </si>
   <si>
+    <t>La nuit on regarde quels produits sont sous le seuil minimum de stock et on propose automatiquement les commandes fournisseurs necessaires</t>
+  </si>
+  <si>
     <t>Lineaire (analyse seuils - proposition commandes - validation - envoi)</t>
   </si>
   <si>
     <t>Analyse des depenses fournisseurs</t>
   </si>
   <si>
+    <t>Une fois par mois on regarde combien on a depense chez chaque fournisseur</t>
+  </si>
+  <si>
     <t>Alertes de rupture en temps quasi-reel</t>
   </si>
   <si>
+    <t>On surveille en continu si un produit tombe en rupture de stock pour alerter vite</t>
+  </si>
+  <si>
     <t>Inventaire tournant et valorisation nocturne</t>
   </si>
   <si>
+    <t>Chaque nuit on compte une partie du stock - on repere les ecarts - on recalcule la valeur du stock</t>
+  </si>
+  <si>
     <t>Lineaire (comptage - ecarts - valorisation - ajustement - rapport - verrouillage)</t>
   </si>
   <si>
     <t>Inventaire physique mensuel</t>
   </si>
   <si>
+    <t>Une fois par mois un comptage plus complet du stock reel</t>
+  </si>
+  <si>
     <t>Valorisation trimestrielle pour arrete</t>
   </si>
   <si>
+    <t>Tous les 3 mois on calcule la valeur financiere totale du stock pour les comptes</t>
+  </si>
+  <si>
     <t>Lancement des ordres de fabrication planifies</t>
   </si>
   <si>
+    <t>A des heures fixes dans la journee on lance en production les ordres de fabrication prevus</t>
+  </si>
+  <si>
     <t>Lineaire (10h-14h-16h)</t>
   </si>
   <si>
     <t>Calcul des besoins nets (MRP run) nocturne</t>
   </si>
   <si>
+    <t>La nuit on calcule automatiquement de quels composants on aura besoin selon les commandes a produire</t>
+  </si>
+  <si>
     <t>Rapport de rendement production</t>
   </si>
   <si>
+    <t>Une fois par mois un bilan de combien on a produit et avec quelle efficacite</t>
+  </si>
+  <si>
     <t>Notification avancement reparation</t>
   </si>
   <si>
+    <t>On previent le client quand sa reparation avance (prise en charge - terminee)</t>
+  </si>
+  <si>
     <t>Rapport quotidien SAV</t>
   </si>
   <si>
+    <t>Chaque jour un point sur les reparations en cours et terminees</t>
+  </si>
+  <si>
     <t>Alerte echeance assurance/controle technique</t>
   </si>
   <si>
+    <t>On previent avant qu'une assurance ou un controle technique n'expire</t>
+  </si>
+  <si>
     <t>Controle entretien mensuel</t>
   </si>
   <si>
+    <t>Une fois par mois verifier quels vehicules ont besoin d'entretien</t>
+  </si>
+  <si>
     <t>Cloture de caisse quotidienne</t>
   </si>
   <si>
+    <t>Chaque soir on compte la caisse et on verifie qu'elle correspond a ce qui a ete encaisse dans la journee</t>
+  </si>
+  <si>
     <t>Lineaire (comptage - rapprochement - ecarts - validation)</t>
   </si>
   <si>
     <t>Rapport ventes mensuel par point de vente</t>
   </si>
   <si>
+    <t>Une fois par mois le bilan des ventes par point de vente</t>
+  </si>
+  <si>
     <t>Cloture de service (midi/soir)</t>
   </si>
   <si>
+    <t>A la fin de chaque service on fait les comptes du service par table</t>
+  </si>
+  <si>
     <t>Verification liens morts et formulaires</t>
   </si>
   <si>
+    <t>Une fois par semaine on verifie que le site web n'a pas de liens casses ou de formulaires en panne</t>
+  </si>
+  <si>
     <t>Rapport ventes en ligne et paniers abandonnes</t>
   </si>
   <si>
+    <t>Chaque jour un bilan des ventes du site et des paniers abandonnes en cours de commande</t>
+  </si>
+  <si>
     <t>Relance paniers abandonnes</t>
   </si>
   <si>
+    <t>On relance les clients qui ont rempli un panier en ligne sans finaliser leur achat</t>
+  </si>
+  <si>
     <t>Rappel evenements du jour</t>
   </si>
   <si>
+    <t>On previent les inscrits d'un evenement le jour meme</t>
+  </si>
+  <si>
     <t>Rapport frequentation mensuel</t>
   </si>
   <si>
+    <t>Une fois par mois combien de personnes ont participe aux evenements</t>
+  </si>
+  <si>
     <t>Rapport progression formations</t>
   </si>
   <si>
+    <t>Une fois par mois ou en sont les employes dans leurs formations en cours</t>
+  </si>
+  <si>
+    <t>Retire automatiquement du site les offres d'emploi deja pourvues pour ne pas continuer a recevoir des candidatures inutiles</t>
+  </si>
+  <si>
     <t>Rapport effectifs et anciennete</t>
   </si>
   <si>
+    <t>Une fois par mois combien d'employes - depuis combien de temps</t>
+  </si>
+  <si>
     <t>Bilan social annuel</t>
   </si>
   <si>
+    <t>Une fois par an le bilan complet de l'annee cote ressources humaines</t>
+  </si>
+  <si>
     <t>Rapport presences et anomalies quotidien</t>
   </si>
   <si>
+    <t>Chaque jour qui etait present - en retard - ou absent</t>
+  </si>
+  <si>
     <t>Calcul des heures travaillees mensuel (base paie)</t>
   </si>
   <si>
+    <t>Une fois par mois calcul des heures travaillees de chacun pour preparer la paie</t>
+  </si>
+  <si>
     <t>Lineaire (extraction - calcul - validation - export)</t>
   </si>
   <si>
     <t>Relance des demandes en attente</t>
   </si>
   <si>
+    <t>On relance un responsable qui n'a pas encore valide une demande de conges de son equipe</t>
+  </si>
+  <si>
     <t>Solde des conges N vers N+1</t>
   </si>
   <si>
+    <t>Le 1er janvier on reporte le solde de conges non pris de l'annee precedente</t>
+  </si>
+  <si>
     <t>Rapport depenses mensuel et export compta</t>
   </si>
   <si>
+    <t>Une fois par mois le total des notes de frais par employe pret a etre envoye a la comptabilite</t>
+  </si>
+  <si>
     <t>Relance candidatures en attente</t>
   </si>
   <si>
+    <t>On relance un recruteur qui n'a pas encore traite une candidature recue</t>
+  </si>
+  <si>
     <t>Rapport ecarts de competences</t>
   </si>
   <si>
+    <t>Une fois par mois quelles competences manquent dans chaque equipe par rapport a ce qui est attendu</t>
+  </si>
+  <si>
     <t>Rapport avancement quotidien</t>
   </si>
   <si>
+    <t>Chaque jour ou en sont les taches des projets en cours et lesquelles sont en retard</t>
+  </si>
+  <si>
     <t>Facturation au temps passe mensuelle</t>
   </si>
   <si>
+    <t>Une fois par mois on facture au client le temps reellement passe sur son projet</t>
+  </si>
+  <si>
     <t>Rappel des taches du jour</t>
   </si>
   <si>
+    <t>On rappelle a chacun les taches personnelles prevues aujourd'hui</t>
+  </si>
+  <si>
     <t>Planning de maintenance preventive mensuel</t>
   </si>
   <si>
+    <t>Une fois par mois on prepare le planning d'entretien preventif des equipements pour le mois suivant</t>
+  </si>
+  <si>
     <t>Cloture automatique des sondages echus</t>
   </si>
   <si>
+    <t>Ferme automatiquement les sondages dont la date limite est passee</t>
+  </si>
+  <si>
     <t>Cutoff des commandes du jour (11h)</t>
   </si>
   <si>
+    <t>A 11h les commandes de repas du jour sont figees et transmises a la cuisine - apres c'est trop tard pour changer</t>
+  </si>
+  <si>
     <t>Rapport hebdomadaire des conversations non traitees</t>
   </si>
   <si>
+    <t>Une fois par semaine combien de conversations du chat en direct sont restees sans reponse</t>
+  </si>
+  <si>
     <t>Envoi des campagnes planifiees</t>
   </si>
   <si>
+    <t>Envoie les campagnes email prevues aux heures programmees</t>
+  </si>
+  <si>
     <t>Lineaire (selection - envoi)</t>
   </si>
   <si>
     <t>Rapport de performance des campagnes</t>
   </si>
   <si>
+    <t>Une fois par mois combien de personnes ont ouvert/clique sur les campagnes envoyees</t>
+  </si>
+  <si>
     <t>Envoi des campagnes SMS planifiees</t>
   </si>
   <si>
+    <t>Envoie les campagnes SMS prevues aux heures programmees</t>
+  </si>
+  <si>
     <t>Rapport de partage/engagement</t>
   </si>
   <si>
+    <t>Une fois par semaine combien de personnes ont partage ou interagi avec les cartes marketing</t>
+  </si>
+  <si>
     <t>Detection mensuelle des donnees perimees</t>
   </si>
   <si>
+    <t>Une fois par mois reperage des donnees anciennes qui devraient etre archivees ou supprimees selon les regles de conservation</t>
+  </si>
+  <si>
     <t>Distinct du PURGE systeme global (ECFCPRG1) - specifique au module data_recycle</t>
   </si>
   <si>
-    <t>TOTAL : 86 operations reelles cataloguees, 228 jobs estimes au total (lineaires + paralleles cumules) - 17 operations deja CONSTRUITES ET VERIFIEES a ce jour, le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE).</t>
+    <t>TOTAL : 86 operations reelles cataloguees, 228 jobs estimes au total (lineaires + paralleles cumules) - 17 operations deja CONSTRUITES ET VERIFIEES (vert), 12 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire.</t>
   </si>
   <si>
     <t>Maintien en condition operationnelle - preuves d'efficacite reelles</t>
@@ -1805,6 +2084,9 @@
   </si>
   <si>
     <t>Principe directeur : jamais suppose, toujours verifie. Chaque ligne ci-dessus est verifiable dans le depot (docs/JOURNAL_TECHNIQUE.md donne la date et la preuve de chaque decision).</t>
+  </si>
+  <si>
+    <t>Nombre d'operations</t>
   </si>
   <si>
     <t>Concept Control-M</t>
@@ -1967,7 +2249,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1998,6 +2280,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2011,7 +2299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2037,9 +2325,14 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2070,6 +2363,1128 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Repartition des 86 operations du catalogue par statut</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Exploitation MCO - efficacite'!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CONSTRUIT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-7259-47BA-899B-F6133CBC1B5C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Exploitation MCO - efficacite'!$B$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nombre d'operations</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Exploitation MCO - efficacite'!$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0FBD-4C88-9479-49AB947B1CDD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Exploitation MCO - efficacite'!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A CONSTRUIRE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7259-47BA-899B-F6133CBC1B5C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Exploitation MCO - efficacite'!$B$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nombre d'operations</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Exploitation MCO - efficacite'!$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0FBD-4C88-9479-49AB947B1CDD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Exploitation MCO - efficacite'!$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HORS PERIMETRE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7259-47BA-899B-F6133CBC1B5C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Exploitation MCO - efficacite'!$B$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nombre d'operations</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Exploitation MCO - efficacite'!$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0FBD-4C88-9479-49AB947B1CDD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>325120</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C96F7BDC-CFFD-4196-8AEB-56A921F9AA39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2368,7 +3783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78616FE7-225E-4E78-BE01-750488388E97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF0E9FC-54E2-410D-A12D-D6521D41204C}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2394,14 +3809,14 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -2412,12 +3827,12 @@
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -2428,14 +3843,14 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2446,12 +3861,12 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -2462,14 +3877,14 @@
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2485,7 +3900,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27014042-126D-48E0-A9EF-7B95549A77F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B25803-B33F-425E-AA20-6A385A65C771}">
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3327,39 +4742,43 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{27014042-126D-48E0-A9EF-7B95549A77F8}"/>
+  <autoFilter ref="A1:G1" xr:uid="{92B25803-B33F-425E-AA20-6A385A65C771}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348D6ABD-8051-4D2D-A196-5BDB0B5E79AE}">
-  <dimension ref="A1:H91"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F984AE0-E9A0-40C6-968A-5C6A18A10B31}">
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" customWidth="1"/>
-    <col min="3" max="3" width="40.77734375" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="45.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1"/>
-    <col min="8" max="8" width="40.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" customWidth="1"/>
+    <col min="4" max="4" width="55.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="40.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" customWidth="1"/>
+    <col min="10" max="10" width="35.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -3368,8 +4787,10 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -3389,13 +4810,19 @@
         <v>417</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="79.8" x14ac:dyDescent="0.3">
+      <c r="I3" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="211.8" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
@@ -3403,25 +4830,31 @@
         <v>11</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="8">
+      <c r="F4" s="8">
         <v>20</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>420</v>
-      </c>
       <c r="G4" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -3429,25 +4862,31 @@
         <v>11</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="8">
+      <c r="F5" s="8">
         <v>1</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="J5" s="8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
@@ -3455,25 +4894,31 @@
         <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="E6" s="8">
+      <c r="F6" s="8">
         <v>1</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>427</v>
-      </c>
       <c r="G6" s="8" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="106.2" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
@@ -3481,25 +4926,31 @@
         <v>11</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E7" s="9">
+      <c r="F7" s="9">
         <v>4</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>430</v>
-      </c>
       <c r="G7" s="9" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="66.599999999999994" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>12</v>
       </c>
@@ -3507,25 +4958,31 @@
         <v>11</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D8" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E8" s="13">
+      <c r="F8" s="13">
         <v>6</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>434</v>
-      </c>
       <c r="G8" s="13" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="66.599999999999994" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>19</v>
       </c>
@@ -3533,25 +4990,31 @@
         <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="9">
+      <c r="F9" s="9">
         <v>3</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J9" s="9" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -3559,23 +5022,29 @@
         <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="9">
+      <c r="F10" s="9">
         <v>4</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>441</v>
-      </c>
       <c r="G10" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
@@ -3583,25 +5052,31 @@
         <v>18</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="E11" s="9">
+        <v>455</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="F11" s="9">
         <v>2</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>444</v>
-      </c>
       <c r="G11" s="9" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
@@ -3609,23 +5084,29 @@
         <v>18</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="9">
+      <c r="F12" s="9">
         <v>2</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G12" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>26</v>
       </c>
@@ -3633,25 +5114,31 @@
         <v>25</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="9">
+      <c r="F13" s="9">
         <v>1</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G13" s="9" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
@@ -3659,23 +5146,29 @@
         <v>25</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="9">
+      <c r="F14" s="9">
         <v>2</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>451</v>
-      </c>
       <c r="G14" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>468</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
@@ -3683,23 +5176,29 @@
         <v>25</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="E15" s="9">
+        <v>470</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="F15" s="9">
         <v>3</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>453</v>
-      </c>
       <c r="G15" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>471</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>26</v>
       </c>
@@ -3707,23 +5206,29 @@
         <v>25</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="9">
+      <c r="F16" s="9">
         <v>1</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G16" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>32</v>
       </c>
@@ -3731,25 +5236,31 @@
         <v>31</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="D17" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="E17" s="13">
+      <c r="F17" s="13">
         <v>1</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>456</v>
-      </c>
       <c r="G17" s="13" t="s">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>32</v>
       </c>
@@ -3757,23 +5268,29 @@
         <v>31</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="F18" s="9">
+        <v>2</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E18" s="9">
-        <v>2</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -3781,23 +5298,29 @@
         <v>31</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="9">
+      <c r="F19" s="9">
         <v>1</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G19" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
@@ -3805,25 +5328,31 @@
         <v>37</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="D20" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="8">
+      <c r="F20" s="8">
         <v>1</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G20" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H20" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
@@ -3831,25 +5360,31 @@
         <v>37</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="8">
+      <c r="F21" s="8">
         <v>1</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G21" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H21" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
@@ -3857,25 +5392,31 @@
         <v>37</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="8">
+        <v>1</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>421</v>
-      </c>
       <c r="H22" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
@@ -3883,51 +5424,63 @@
         <v>37</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="D23" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="8">
+      <c r="F23" s="8">
         <v>2</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G23" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="C24" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="E24" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="9">
+      <c r="F24" s="16">
         <v>3</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G24" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>38</v>
       </c>
@@ -3935,23 +5488,29 @@
         <v>37</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="E25" s="9">
+        <v>499</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="F25" s="9">
         <v>2</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>471</v>
-      </c>
       <c r="G25" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>38</v>
       </c>
@@ -3962,20 +5521,26 @@
         <v>411</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E26" s="9">
+      <c r="F26" s="9">
         <v>3</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>472</v>
-      </c>
       <c r="G26" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>45</v>
       </c>
@@ -3983,25 +5548,31 @@
         <v>44</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="8">
+      <c r="F27" s="8">
         <v>1</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G27" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H27" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>45</v>
       </c>
@@ -4009,25 +5580,31 @@
         <v>44</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="8">
+      <c r="F28" s="8">
         <v>1</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G28" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>45</v>
       </c>
@@ -4035,25 +5612,31 @@
         <v>44</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="D29" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="8">
+      <c r="F29" s="8">
         <v>1</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G29" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H29" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>45</v>
       </c>
@@ -4061,25 +5644,31 @@
         <v>44</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="8">
+      <c r="F30" s="8">
         <v>3</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>477</v>
-      </c>
       <c r="G30" s="8" t="s">
-        <v>421</v>
+        <v>511</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>45</v>
       </c>
@@ -4087,49 +5676,61 @@
         <v>44</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="D31" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="8">
+      <c r="F31" s="8">
         <v>1</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G31" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H31" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A32" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="D32" s="9" t="s">
+      <c r="C32" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="E32" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="9">
+      <c r="F32" s="16">
         <v>5</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G32" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J32" s="16"/>
+    </row>
+    <row r="33" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
@@ -4137,23 +5738,29 @@
         <v>44</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>482</v>
+        <v>518</v>
       </c>
       <c r="D33" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E33" s="9">
+      <c r="F33" s="9">
         <v>4</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G33" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J33" s="9"/>
+    </row>
+    <row r="34" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>52</v>
       </c>
@@ -4161,73 +5768,91 @@
         <v>51</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="D34" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E34" s="8">
+      <c r="F34" s="8">
         <v>1</v>
       </c>
-      <c r="F34" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G34" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H34" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="C35" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="E35" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E35" s="9">
+      <c r="F35" s="16">
         <v>5</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="G35" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J35" s="16"/>
+    </row>
+    <row r="36" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A36" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="D36" s="9" t="s">
+      <c r="C36" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="E36" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E36" s="9">
+      <c r="F36" s="16">
         <v>2</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="G36" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J36" s="16"/>
+    </row>
+    <row r="37" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>52</v>
       </c>
@@ -4235,25 +5860,31 @@
         <v>51</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>488</v>
+        <v>528</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="E37" s="9">
+        <v>529</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="F37" s="9">
         <v>2</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>490</v>
-      </c>
       <c r="G37" s="9" t="s">
-        <v>431</v>
+        <v>531</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>52</v>
       </c>
@@ -4261,75 +5892,93 @@
         <v>51</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="E38" s="9">
+        <v>534</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="F38" s="9">
         <v>3</v>
       </c>
-      <c r="F38" s="9" t="s">
-        <v>494</v>
-      </c>
       <c r="G38" s="9" t="s">
-        <v>431</v>
+        <v>536</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="16">
+        <v>9</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I39" s="16" t="s">
         <v>496</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="9">
-        <v>9</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
+      <c r="J39" s="16" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A40" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="D40" s="9" t="s">
+      <c r="C40" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="E40" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="E40" s="9">
+      <c r="F40" s="16">
         <v>6</v>
       </c>
-      <c r="F40" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="G40" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J40" s="16"/>
+    </row>
+    <row r="41" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>52</v>
       </c>
@@ -4337,25 +5986,31 @@
         <v>51</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>501</v>
+        <v>545</v>
       </c>
       <c r="D41" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E41" s="9">
+      <c r="F41" s="9">
         <v>12</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>502</v>
-      </c>
       <c r="G41" s="9" t="s">
-        <v>431</v>
+        <v>547</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>59</v>
       </c>
@@ -4363,25 +6018,31 @@
         <v>58</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E42" s="8">
+      <c r="F42" s="8">
         <v>1</v>
       </c>
-      <c r="F42" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G42" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H42" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J42" s="8" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>59</v>
       </c>
@@ -4389,25 +6050,31 @@
         <v>58</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="D43" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E43" s="8">
+      <c r="F43" s="8">
         <v>1</v>
       </c>
-      <c r="F43" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G43" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H43" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J43" s="8" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>59</v>
       </c>
@@ -4418,22 +6085,28 @@
         <v>331</v>
       </c>
       <c r="D44" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="8">
+      <c r="F44" s="8">
         <v>1</v>
       </c>
-      <c r="F44" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G44" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H44" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J44" s="8" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>59</v>
       </c>
@@ -4441,49 +6114,61 @@
         <v>58</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>505</v>
+        <v>553</v>
       </c>
       <c r="D45" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E45" s="8">
+      <c r="F45" s="8">
         <v>1</v>
       </c>
-      <c r="F45" s="8" t="s">
-        <v>448</v>
-      </c>
       <c r="G45" s="8" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="H45" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="J45" s="8" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="D46" s="9" t="s">
+      <c r="C46" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="E46" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E46" s="9">
+      <c r="F46" s="16">
         <v>4</v>
       </c>
-      <c r="F46" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G46" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J46" s="16"/>
+    </row>
+    <row r="47" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>59</v>
       </c>
@@ -4491,71 +6176,89 @@
         <v>58</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>508</v>
+        <v>558</v>
       </c>
       <c r="D47" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E47" s="9">
+      <c r="F47" s="9">
         <v>3</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G47" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J47" s="9"/>
+    </row>
+    <row r="48" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A48" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="E48" s="9">
+      <c r="C48" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="F48" s="16">
         <v>2</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
+      <c r="G48" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J48" s="16"/>
+    </row>
+    <row r="49" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A49" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="D49" s="9" t="s">
+      <c r="C49" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="E49" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E49" s="9">
+      <c r="F49" s="16">
         <v>6</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G49" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J49" s="16"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>66</v>
       </c>
@@ -4563,23 +6266,29 @@
         <v>65</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>512</v>
+        <v>565</v>
       </c>
       <c r="D50" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="E50" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E50" s="9">
+      <c r="F50" s="9">
         <v>5</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G50" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J50" s="9"/>
+    </row>
+    <row r="51" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>66</v>
       </c>
@@ -4587,23 +6296,29 @@
         <v>65</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>513</v>
+        <v>567</v>
       </c>
       <c r="D51" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="E51" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E51" s="9">
+      <c r="F51" s="9">
         <v>3</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G51" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J51" s="9"/>
+    </row>
+    <row r="52" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>71</v>
       </c>
@@ -4611,23 +6326,29 @@
         <v>70</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="E52" s="9">
+        <v>570</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="F52" s="9">
         <v>3</v>
       </c>
-      <c r="F52" s="9" t="s">
-        <v>515</v>
-      </c>
       <c r="G52" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <v>571</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J52" s="9"/>
+    </row>
+    <row r="53" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>71</v>
       </c>
@@ -4635,23 +6356,29 @@
         <v>70</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>516</v>
+        <v>572</v>
       </c>
       <c r="D53" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E53" s="9">
+      <c r="F53" s="9">
         <v>4</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G53" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J53" s="9"/>
+    </row>
+    <row r="54" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>71</v>
       </c>
@@ -4659,23 +6386,29 @@
         <v>70</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>517</v>
+        <v>574</v>
       </c>
       <c r="D54" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="E54" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="9">
+      <c r="F54" s="9">
         <v>2</v>
       </c>
-      <c r="F54" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G54" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J54" s="9"/>
+    </row>
+    <row r="55" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>76</v>
       </c>
@@ -4683,23 +6416,29 @@
         <v>75</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>518</v>
+        <v>576</v>
       </c>
       <c r="D55" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E55" s="9">
+      <c r="F55" s="9">
         <v>1</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G55" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H55" s="9"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J55" s="9"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>76</v>
       </c>
@@ -4707,23 +6446,29 @@
         <v>75</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>519</v>
+        <v>578</v>
       </c>
       <c r="D56" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E56" s="9">
+      <c r="F56" s="9">
         <v>2</v>
       </c>
-      <c r="F56" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G56" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H56" s="9"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J56" s="9"/>
+    </row>
+    <row r="57" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>81</v>
       </c>
@@ -4731,23 +6476,29 @@
         <v>80</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E57" s="9">
+        <v>581</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="F57" s="9">
         <v>1</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G57" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H57" s="9"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J57" s="9"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>81</v>
       </c>
@@ -4755,47 +6506,59 @@
         <v>80</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>521</v>
+        <v>582</v>
       </c>
       <c r="D58" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E58" s="9">
+      <c r="F58" s="9">
         <v>2</v>
       </c>
-      <c r="F58" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G58" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H58" s="9"/>
-    </row>
-    <row r="59" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J58" s="9"/>
+    </row>
+    <row r="59" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A59" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="D59" s="9" t="s">
+      <c r="C59" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="E59" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="9">
+      <c r="F59" s="16">
         <v>4</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H59" s="9"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G59" s="16" t="s">
+        <v>586</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J59" s="16"/>
+    </row>
+    <row r="60" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>86</v>
       </c>
@@ -4803,23 +6566,29 @@
         <v>85</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>524</v>
+        <v>587</v>
       </c>
       <c r="D60" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="E60" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E60" s="9">
+      <c r="F60" s="9">
         <v>3</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G60" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H60" s="9"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J60" s="9"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>91</v>
       </c>
@@ -4827,23 +6596,29 @@
         <v>90</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>525</v>
+        <v>589</v>
       </c>
       <c r="D61" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="E61" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="9">
+      <c r="F61" s="9">
         <v>3</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G61" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H61" s="9"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J61" s="9"/>
+    </row>
+    <row r="62" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>96</v>
       </c>
@@ -4851,23 +6626,29 @@
         <v>95</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="D62" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E62" s="9">
+      <c r="F62" s="9">
         <v>2</v>
       </c>
-      <c r="F62" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G62" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H62" s="9"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J62" s="9"/>
+    </row>
+    <row r="63" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>101</v>
       </c>
@@ -4875,23 +6656,29 @@
         <v>100</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>527</v>
+        <v>593</v>
       </c>
       <c r="D63" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E63" s="9">
+      <c r="F63" s="9">
         <v>3</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G63" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H63" s="9"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J63" s="9"/>
+    </row>
+    <row r="64" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>101</v>
       </c>
@@ -4899,23 +6686,29 @@
         <v>100</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>528</v>
+        <v>595</v>
       </c>
       <c r="D64" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="E64" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E64" s="9">
+      <c r="F64" s="9">
         <v>2</v>
       </c>
-      <c r="F64" s="9" t="s">
-        <v>487</v>
-      </c>
       <c r="G64" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H64" s="9"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J64" s="9"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>106</v>
       </c>
@@ -4923,23 +6716,29 @@
         <v>105</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>529</v>
+        <v>597</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E65" s="9">
+        <v>598</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="F65" s="9">
         <v>1</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G65" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H65" s="9"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J65" s="9"/>
+    </row>
+    <row r="66" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>106</v>
       </c>
@@ -4947,23 +6746,29 @@
         <v>105</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>530</v>
+        <v>599</v>
       </c>
       <c r="D66" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="E66" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E66" s="9">
+      <c r="F66" s="9">
         <v>2</v>
       </c>
-      <c r="F66" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G66" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H66" s="9"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J66" s="9"/>
+    </row>
+    <row r="67" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>111</v>
       </c>
@@ -4971,23 +6776,29 @@
         <v>110</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>531</v>
+        <v>601</v>
       </c>
       <c r="D67" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E67" s="9">
+      <c r="F67" s="9">
         <v>2</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G67" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H67" s="9"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J67" s="9"/>
+    </row>
+    <row r="68" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>116</v>
       </c>
@@ -4998,20 +6809,26 @@
         <v>118</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E68" s="9">
+        <v>603</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="F68" s="9">
         <v>1</v>
       </c>
-      <c r="F68" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G68" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H68" s="9"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J68" s="9"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>120</v>
       </c>
@@ -5019,23 +6836,29 @@
         <v>120</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>532</v>
+        <v>604</v>
       </c>
       <c r="D69" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E69" s="9">
+      <c r="F69" s="9">
         <v>2</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G69" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H69" s="9"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J69" s="9"/>
+    </row>
+    <row r="70" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>120</v>
       </c>
@@ -5043,23 +6866,29 @@
         <v>120</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>533</v>
+        <v>606</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="E70" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E70" s="9">
+      <c r="F70" s="9">
         <v>3</v>
       </c>
-      <c r="F70" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G70" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H70" s="9"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J70" s="9"/>
+    </row>
+    <row r="71" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>125</v>
       </c>
@@ -5067,47 +6896,59 @@
         <v>124</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>534</v>
+        <v>608</v>
       </c>
       <c r="D71" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E71" s="9">
+      <c r="F71" s="9">
         <v>2</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G71" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H71" s="9"/>
-    </row>
-    <row r="72" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J71" s="9"/>
+    </row>
+    <row r="72" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A72" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C72" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="D72" s="9" t="s">
+      <c r="C72" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="E72" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E72" s="9">
+      <c r="F72" s="16">
         <v>4</v>
       </c>
-      <c r="F72" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H72" s="9"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G72" s="16" t="s">
+        <v>612</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J72" s="16"/>
+    </row>
+    <row r="73" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>130</v>
       </c>
@@ -5115,23 +6956,29 @@
         <v>129</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
       <c r="D73" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E73" s="9">
+      <c r="F73" s="9">
         <v>1</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G73" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H73" s="9"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J73" s="9"/>
+    </row>
+    <row r="74" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>130</v>
       </c>
@@ -5139,23 +6986,29 @@
         <v>129</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>538</v>
+        <v>615</v>
       </c>
       <c r="D74" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="E74" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E74" s="9">
+      <c r="F74" s="9">
         <v>2</v>
       </c>
-      <c r="F74" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G74" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H74" s="9"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J74" s="9"/>
+    </row>
+    <row r="75" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>135</v>
       </c>
@@ -5163,23 +7016,29 @@
         <v>134</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>539</v>
+        <v>617</v>
       </c>
       <c r="D75" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="E75" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E75" s="9">
+      <c r="F75" s="9">
         <v>3</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G75" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H75" s="9"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J75" s="9"/>
+    </row>
+    <row r="76" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>140</v>
       </c>
@@ -5187,23 +7046,29 @@
         <v>139</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>540</v>
+        <v>619</v>
       </c>
       <c r="D76" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="E76" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E76" s="9">
+      <c r="F76" s="9">
         <v>1</v>
       </c>
-      <c r="F76" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G76" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H76" s="9"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J76" s="9"/>
+    </row>
+    <row r="77" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>145</v>
       </c>
@@ -5211,23 +7076,29 @@
         <v>144</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>541</v>
+        <v>621</v>
       </c>
       <c r="D77" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E77" s="9">
+      <c r="F77" s="9">
         <v>2</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G77" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H77" s="9"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J77" s="9"/>
+    </row>
+    <row r="78" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>150</v>
       </c>
@@ -5235,47 +7106,59 @@
         <v>149</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>542</v>
+        <v>623</v>
       </c>
       <c r="D78" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="E78" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E78" s="9">
+      <c r="F78" s="9">
         <v>2</v>
       </c>
-      <c r="F78" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G78" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H78" s="9"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J78" s="9"/>
+    </row>
+    <row r="79" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="A79" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="D79" s="9" t="s">
+      <c r="C79" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="E79" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E79" s="9">
+      <c r="F79" s="16">
         <v>3</v>
       </c>
-      <c r="F79" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H79" s="9"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G79" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="H79" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="I79" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="J79" s="16"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>155</v>
       </c>
@@ -5283,23 +7166,29 @@
         <v>154</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>544</v>
+        <v>627</v>
       </c>
       <c r="D80" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="E80" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E80" s="9">
+      <c r="F80" s="9">
         <v>1</v>
       </c>
-      <c r="F80" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G80" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H80" s="9"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J80" s="9"/>
+    </row>
+    <row r="81" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>160</v>
       </c>
@@ -5307,23 +7196,29 @@
         <v>159</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>545</v>
+        <v>629</v>
       </c>
       <c r="D81" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E81" s="9">
+      <c r="F81" s="9">
         <v>2</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G81" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H81" s="9"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J81" s="9"/>
+    </row>
+    <row r="82" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>165</v>
       </c>
@@ -5331,23 +7226,29 @@
         <v>164</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>546</v>
+        <v>631</v>
       </c>
       <c r="D82" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="E82" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E82" s="9">
+      <c r="F82" s="9">
         <v>1</v>
       </c>
-      <c r="F82" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G82" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H82" s="9"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J82" s="9"/>
+    </row>
+    <row r="83" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>170</v>
       </c>
@@ -5355,23 +7256,29 @@
         <v>169</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>547</v>
+        <v>633</v>
       </c>
       <c r="D83" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E83" s="9">
+      <c r="F83" s="9">
         <v>1</v>
       </c>
-      <c r="F83" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G83" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H83" s="9"/>
-    </row>
-    <row r="84" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J83" s="9"/>
+    </row>
+    <row r="84" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>176</v>
       </c>
@@ -5379,23 +7286,29 @@
         <v>175</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>548</v>
+        <v>635</v>
       </c>
       <c r="D84" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="E84" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E84" s="9">
+      <c r="F84" s="9">
         <v>1</v>
       </c>
-      <c r="F84" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G84" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H84" s="9"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J84" s="9"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>181</v>
       </c>
@@ -5403,23 +7316,29 @@
         <v>180</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>549</v>
+        <v>637</v>
       </c>
       <c r="D85" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E85" s="9">
+      <c r="F85" s="9">
         <v>2</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>550</v>
-      </c>
       <c r="G85" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H85" s="9"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="J85" s="9"/>
+    </row>
+    <row r="86" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>181</v>
       </c>
@@ -5427,23 +7346,29 @@
         <v>180</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>551</v>
+        <v>640</v>
       </c>
       <c r="D86" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E86" s="9">
+      <c r="F86" s="9">
         <v>2</v>
       </c>
-      <c r="F86" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G86" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H86" s="9"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J86" s="9"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>186</v>
       </c>
@@ -5451,23 +7376,29 @@
         <v>185</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>552</v>
+        <v>642</v>
       </c>
       <c r="D87" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="E87" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E87" s="9">
+      <c r="F87" s="9">
         <v>2</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G87" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H87" s="9"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J87" s="9"/>
+    </row>
+    <row r="88" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>191</v>
       </c>
@@ -5475,23 +7406,29 @@
         <v>190</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>553</v>
+        <v>644</v>
       </c>
       <c r="D88" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="E88" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E88" s="9">
+      <c r="F88" s="9">
         <v>1</v>
       </c>
-      <c r="F88" s="9" t="s">
-        <v>448</v>
-      </c>
       <c r="G88" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H88" s="9"/>
-    </row>
-    <row r="89" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J88" s="9"/>
+    </row>
+    <row r="89" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>196</v>
       </c>
@@ -5499,48 +7436,56 @@
         <v>195</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>554</v>
+        <v>646</v>
       </c>
       <c r="D89" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="E89" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E89" s="9">
+      <c r="F89" s="9">
         <v>2</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="G89" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="18" t="s">
-        <v>556</v>
-      </c>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="19"/>
-      <c r="G91" s="19"/>
-      <c r="H91" s="19"/>
+        <v>438</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="21" t="s">
+        <v>649</v>
+      </c>
+      <c r="B91" s="22"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="22"/>
+      <c r="H91" s="22"/>
+      <c r="I91" s="22"/>
+      <c r="J91" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H3" xr:uid="{348D6ABD-8051-4D2D-A196-5BDB0B5E79AE}"/>
+  <autoFilter ref="A3:J3" xr:uid="{0F984AE0-E9A0-40C6-968A-5C6A18A10B31}"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A91:J91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF2F3472-0384-4FB1-9048-9EDBA4ECF2EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EF07DB-3673-4B0C-8E85-DD1BACD70066}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5552,13 +7497,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -5806,7 +7751,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{CF2F3472-0384-4FB1-9048-9EDBA4ECF2EA}"/>
+  <autoFilter ref="A3:E3" xr:uid="{C0EF07DB-3673-4B0C-8E85-DD1BACD70066}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -5815,7 +7760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABD72BB-8C8A-4680-9DE1-CBBECCF9607A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC6C5D7F-35B2-4AAD-ABE2-9735585FF5B8}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5827,13 +7772,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -6003,13 +7948,13 @@
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="24" t="s">
         <v>305</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6021,8 +7966,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAD0442-1356-41B3-B0C4-531EAF7077B3}">
-  <dimension ref="A1:D13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9773EC07-1A71-43BD-8390-F505E0CA7B12}">
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.77734375" customWidth="1"/>
@@ -6031,12 +7976,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>557</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6045,109 +7990,141 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>558</v>
+        <v>651</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>559</v>
+        <v>652</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>560</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>562</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>563</v>
+        <v>654</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>566</v>
+        <v>657</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>568</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>569</v>
+        <v>660</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>572</v>
+        <v>663</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>575</v>
+        <v>666</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>578</v>
+        <v>669</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>581</v>
+        <v>672</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>673</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>584</v>
+        <v>675</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>585</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="A13" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="B15" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="B16" s="7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6155,11 +8132,12 @@
     <mergeCell ref="A13:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E9E754-02DB-453F-8243-2334DAD22253}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{732DEFA0-AB14-40B1-9D93-7EA4957536DC}">
   <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6173,15 +8151,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -7389,18 +9367,18 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="19" t="s">
+      <c r="A56" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{85E9E754-02DB-453F-8243-2334DAD22253}"/>
+  <autoFilter ref="A3:G3" xr:uid="{732DEFA0-AB14-40B1-9D93-7EA4957536DC}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A56:G56"/>
@@ -7410,7 +9388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39E84D-A09D-4E68-8461-C2CCAB41C53C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C93C0F-A10E-4E79-87EB-36063B012AF1}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7420,146 +9398,146 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>586</v>
+        <v>680</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>587</v>
+        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="93" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>588</v>
+        <v>682</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>589</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>590</v>
+        <v>684</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>591</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="93" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>583</v>
+        <v>676</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>592</v>
+        <v>686</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="93" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>593</v>
+        <v>687</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>594</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>595</v>
+        <v>689</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>596</v>
+        <v>690</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>597</v>
+        <v>691</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>598</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>599</v>
+        <v>693</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>600</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>601</v>
+        <v>695</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>602</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>603</v>
+        <v>697</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>604</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>605</v>
+        <v>699</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>606</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>607</v>
+        <v>701</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>608</v>
+        <v>702</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>609</v>
+        <v>703</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>610</v>
+        <v>704</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>611</v>
+        <v>705</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>612</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>613</v>
+        <v>707</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>614</v>
+        <v>708</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="27" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>615</v>
+        <v>709</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>616</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>617</v>
+        <v>711</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>618</v>
+        <v>712</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>619</v>
+        <v>713</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>620</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8138107C-9D87-4E9C-8B29-C49E44750E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91A7DED7-92AE-444D-9247-EB5D370DAB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{C551928C-355D-43F7-977C-D22A6F84B241}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{1C8EC45E-BD1F-45DD-8D0B-DA7242E61BEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="564">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -928,6 +928,9 @@
     <t>Lineaire (consolidation - calcul commissions - validation - verrouillage - rapport)</t>
   </si>
   <si>
+    <t>ECFCVTEM1 deja construit (version simplifiee : CA et repartition par commercial - sans verrouillage de periode)</t>
+  </si>
+  <si>
     <t>Cloture quotidienne TFJ Ventes (doit avoir tourne chaque jour du mois)</t>
   </si>
   <si>
@@ -961,6 +964,9 @@
     <t>Lineaire (import releve - rapprochement auto - exceptions - validation - rapport)</t>
   </si>
   <si>
+    <t>ECFCCPRB1 deja construit (detection des lignes non rapprochees - pas encore l'import automatique du releve lui-meme)</t>
+  </si>
+  <si>
     <t>Relance factures impayees</t>
   </si>
   <si>
@@ -970,6 +976,9 @@
     <t>Lineaire (detection - relance)</t>
   </si>
   <si>
+    <t>ECFCCPFI1 deja construit (detection et rapport - relance email non automatisee - meme choix que ECFCVTRL cote Ventes)</t>
+  </si>
+  <si>
     <t>Generation de releves de compte PDF volumineux</t>
   </si>
   <si>
@@ -1009,7 +1018,7 @@
     <t>Lineaire (verif soldes - lettrage auto - provisions - balance - validation - verrouillage periode - export - notification - archivage)</t>
   </si>
   <si>
-    <t>Chaine lourde representative d'une vraie cloture bancaire</t>
+    <t>ECFCCPEM1 deja construit (version simplifiee : CA facture/encaisse/balance agee - sans provisions ni verrouillage de periode)</t>
   </si>
   <si>
     <t>Reconciliation bancaire quotidienne + Marqueur EOD (chaque jour du mois)</t>
@@ -1024,6 +1033,9 @@
     <t>Lineaire (extraction - calcul ratios - validation - generation etat - controle - transmission)</t>
   </si>
   <si>
+    <t>ECFCCPEQ1 deja construit (TVA collectee/deductible/nette simplifiee - pas encore les ratios prudentiels)</t>
+  </si>
+  <si>
     <t>Cloture comptable mensuelle (les 3 mois du trimestre)</t>
   </si>
   <si>
@@ -1525,7 +1537,7 @@
     <t>Distinct du PURGE systeme global (ECFCPRG1) - specifique au module data_recycle</t>
   </si>
   <si>
-    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 17 operations deja CONSTRUITES ET VERIFIEES (vert), 13 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
+    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 22 operations deja CONSTRUITES ET VERIFIEES (vert), 8 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
   </si>
   <si>
     <t>Maintien en condition operationnelle - preuves d'efficacite reelles</t>
@@ -1588,7 +1600,7 @@
     <t>Couverture du catalogue d'operations</t>
   </si>
   <si>
-    <t>17 des 88 operations cataloguees deja construites</t>
+    <t>22 des 88 operations cataloguees deja construites</t>
   </si>
   <si>
     <t>233 jobs estimes au total sur l'ensemble du catalogue si tout etait construit - roadmap explicite, jamais presente comme deja fait.</t>
@@ -2082,14 +2094,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>17</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2CC8-4026-803E-2CEC4622D482}"/>
+              <c16:uniqueId val="{00000000-0DA8-451D-8A19-4D353F89230A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2195,14 +2207,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>69</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-2CC8-4026-803E-2CEC4622D482}"/>
+              <c16:uniqueId val="{00000002-0DA8-451D-8A19-4D353F89230A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2315,7 +2327,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-2CC8-4026-803E-2CEC4622D482}"/>
+              <c16:uniqueId val="{00000003-0DA8-451D-8A19-4D353F89230A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2992,7 +3004,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B91864DB-0385-4353-B721-EC56A4533CA5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8CB4A2C-0ACF-4293-980B-DB6D33F055DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3309,7 +3321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82667C35-C0E1-4D6B-B224-A5207098906E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49005E43-6F93-4C86-A4CE-3B9E95856FFA}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3498,7 +3510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D78C55-1DD8-4428-80B7-D978393E723A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE00EBB-670F-4983-9E58-B2E3B1026B64}">
   <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4541,36 +4553,38 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="14">
         <v>5</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="H32" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23" t="s">
+      <c r="H32" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J32" s="14" t="s">
         <v>294</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
@@ -4581,10 +4595,10 @@
         <v>130</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>37</v>
@@ -4603,21 +4617,21 @@
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>22</v>
@@ -4641,93 +4655,97 @@
         <v>192</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A35" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="B35" s="22" t="s">
+    <row r="35" spans="1:11" ht="159" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C35" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="D35" s="23" t="s">
+      <c r="B35" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="D35" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E35" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="14">
         <v>5</v>
       </c>
-      <c r="G35" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="H35" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23" t="s">
+      <c r="G35" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="K35" s="14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A36" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="B36" s="22" t="s">
+    <row r="36" spans="1:11" ht="159" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C36" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="E36" s="23" t="s">
+      <c r="B36" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="14">
         <v>2</v>
       </c>
-      <c r="G36" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23" t="s">
+      <c r="G36" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="K36" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F37" s="15">
         <v>2</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>204</v>
@@ -4736,7 +4754,7 @@
         <v>205</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K37" s="15" t="s">
         <v>192</v>
@@ -4744,25 +4762,25 @@
     </row>
     <row r="38" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F38" s="15">
         <v>3</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>204</v>
@@ -4771,92 +4789,94 @@
         <v>205</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K38" s="15" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="211.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="B39" s="22" t="s">
+      <c r="A39" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C39" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="E39" s="23" t="s">
+      <c r="B39" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="E39" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="14">
         <v>9</v>
       </c>
-      <c r="G39" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J39" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="K39" s="23" t="s">
-        <v>322</v>
+      <c r="G39" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="B40" s="22" t="s">
+      <c r="A40" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C40" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="E40" s="23" t="s">
+      <c r="B40" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="E40" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="14">
         <v>6</v>
       </c>
-      <c r="G40" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="H40" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23" t="s">
-        <v>326</v>
+      <c r="G40" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="225" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>42</v>
@@ -4865,7 +4885,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>204</v>
@@ -4874,24 +4894,24 @@
         <v>205</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>70</v>
@@ -4917,7 +4937,7 @@
     </row>
     <row r="43" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>140</v>
@@ -4926,7 +4946,7 @@
         <v>281</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>70</v>
@@ -4952,7 +4972,7 @@
     </row>
     <row r="44" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>140</v>
@@ -4961,7 +4981,7 @@
         <v>145</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>70</v>
@@ -4987,16 +5007,16 @@
     </row>
     <row r="45" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>47</v>
@@ -5022,16 +5042,16 @@
     </row>
     <row r="46" spans="1:11" ht="172.2" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B46" s="22" t="s">
         <v>140</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E46" s="23" t="s">
         <v>17</v>
@@ -5040,7 +5060,7 @@
         <v>4</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H46" s="23" t="s">
         <v>204</v>
@@ -5055,16 +5075,16 @@
     </row>
     <row r="47" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>140</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>32</v>
@@ -5083,21 +5103,21 @@
       </c>
       <c r="J47" s="15"/>
       <c r="K47" s="15" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B48" s="22" t="s">
         <v>147</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E48" s="23" t="s">
         <v>224</v>
@@ -5121,16 +5141,16 @@
     </row>
     <row r="49" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B49" s="22" t="s">
         <v>147</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E49" s="23" t="s">
         <v>17</v>
@@ -5139,7 +5159,7 @@
         <v>6</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H49" s="23" t="s">
         <v>204</v>
@@ -5154,16 +5174,16 @@
     </row>
     <row r="50" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>32</v>
@@ -5182,21 +5202,21 @@
       </c>
       <c r="J50" s="15"/>
       <c r="K50" s="15" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>37</v>
@@ -5215,30 +5235,30 @@
       </c>
       <c r="J51" s="15"/>
       <c r="K51" s="15" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F52" s="15">
         <v>3</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H52" s="15" t="s">
         <v>204</v>
@@ -5253,16 +5273,16 @@
     </row>
     <row r="53" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>17</v>
@@ -5286,16 +5306,16 @@
     </row>
     <row r="54" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>32</v>
@@ -5319,16 +5339,16 @@
     </row>
     <row r="55" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>107</v>
@@ -5352,16 +5372,16 @@
     </row>
     <row r="56" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>17</v>
@@ -5385,16 +5405,16 @@
     </row>
     <row r="57" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>252</v>
@@ -5418,16 +5438,16 @@
     </row>
     <row r="58" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>32</v>
@@ -5451,16 +5471,16 @@
     </row>
     <row r="59" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B59" s="22" t="s">
         <v>161</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E59" s="23" t="s">
         <v>17</v>
@@ -5469,7 +5489,7 @@
         <v>4</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H59" s="23" t="s">
         <v>204</v>
@@ -5484,16 +5504,16 @@
     </row>
     <row r="60" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>161</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>32</v>
@@ -5517,16 +5537,16 @@
     </row>
     <row r="61" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>164</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>17</v>
@@ -5550,16 +5570,16 @@
     </row>
     <row r="62" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>27</v>
@@ -5583,16 +5603,16 @@
     </row>
     <row r="63" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>17</v>
@@ -5616,16 +5636,16 @@
     </row>
     <row r="64" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>107</v>
@@ -5634,7 +5654,7 @@
         <v>2</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H64" s="15" t="s">
         <v>204</v>
@@ -5649,16 +5669,16 @@
     </row>
     <row r="65" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>252</v>
@@ -5682,16 +5702,16 @@
     </row>
     <row r="66" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>32</v>
@@ -5715,16 +5735,16 @@
     </row>
     <row r="67" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>32</v>
@@ -5748,16 +5768,16 @@
     </row>
     <row r="68" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>252</v>
@@ -5781,16 +5801,16 @@
     </row>
     <row r="69" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>32</v>
@@ -5814,16 +5834,16 @@
     </row>
     <row r="70" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>42</v>
@@ -5842,21 +5862,21 @@
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="277.8" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E71" s="23" t="s">
         <v>17</v>
@@ -5865,7 +5885,7 @@
         <v>2</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H71" s="23" t="s">
         <v>204</v>
@@ -5874,7 +5894,7 @@
         <v>270</v>
       </c>
       <c r="J71" s="23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="K71" s="23" t="s">
         <v>192</v>
@@ -5882,16 +5902,16 @@
     </row>
     <row r="72" spans="1:11" ht="225" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E72" s="15" t="s">
         <v>70</v>
@@ -5900,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H72" s="15" t="s">
         <v>204</v>
@@ -5909,24 +5929,24 @@
         <v>205</v>
       </c>
       <c r="J72" s="15" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E73" s="15" t="s">
         <v>17</v>
@@ -5950,16 +5970,16 @@
     </row>
     <row r="74" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A74" s="22" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E74" s="23" t="s">
         <v>32</v>
@@ -5968,7 +5988,7 @@
         <v>4</v>
       </c>
       <c r="G74" s="23" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="H74" s="23" t="s">
         <v>204</v>
@@ -5978,21 +5998,21 @@
       </c>
       <c r="J74" s="23"/>
       <c r="K74" s="23" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E75" s="15" t="s">
         <v>107</v>
@@ -6016,16 +6036,16 @@
     </row>
     <row r="76" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E76" s="15" t="s">
         <v>42</v>
@@ -6049,16 +6069,16 @@
     </row>
     <row r="77" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E77" s="15" t="s">
         <v>32</v>
@@ -6082,16 +6102,16 @@
     </row>
     <row r="78" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E78" s="15" t="s">
         <v>17</v>
@@ -6115,16 +6135,16 @@
     </row>
     <row r="79" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E79" s="15" t="s">
         <v>32</v>
@@ -6148,16 +6168,16 @@
     </row>
     <row r="80" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E80" s="15" t="s">
         <v>17</v>
@@ -6181,16 +6201,16 @@
     </row>
     <row r="81" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A81" s="22" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E81" s="23" t="s">
         <v>32</v>
@@ -6214,16 +6234,16 @@
     </row>
     <row r="82" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E82" s="15" t="s">
         <v>107</v>
@@ -6247,16 +6267,16 @@
     </row>
     <row r="83" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E83" s="15" t="s">
         <v>32</v>
@@ -6280,16 +6300,16 @@
     </row>
     <row r="84" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E84" s="15" t="s">
         <v>70</v>
@@ -6313,16 +6333,16 @@
     </row>
     <row r="85" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>47</v>
@@ -6346,16 +6366,16 @@
     </row>
     <row r="86" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E86" s="15" t="s">
         <v>27</v>
@@ -6379,16 +6399,16 @@
     </row>
     <row r="87" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E87" s="15" t="s">
         <v>107</v>
@@ -6397,7 +6417,7 @@
         <v>2</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="H87" s="15" t="s">
         <v>204</v>
@@ -6412,16 +6432,16 @@
     </row>
     <row r="88" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E88" s="15" t="s">
         <v>32</v>
@@ -6445,16 +6465,16 @@
     </row>
     <row r="89" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E89" s="15" t="s">
         <v>107</v>
@@ -6478,16 +6498,16 @@
     </row>
     <row r="90" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E90" s="15" t="s">
         <v>27</v>
@@ -6511,16 +6531,16 @@
     </row>
     <row r="91" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E91" s="15" t="s">
         <v>32</v>
@@ -6538,7 +6558,7 @@
         <v>226</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="K91" s="15" t="s">
         <v>192</v>
@@ -6546,7 +6566,7 @@
     </row>
     <row r="93" spans="1:11" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="21" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -6560,7 +6580,7 @@
       <c r="K93" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{66D78C55-1DD8-4428-80B7-D978393E723A}"/>
+  <autoFilter ref="A3:K3" xr:uid="{CDE00EBB-670F-4983-9E58-B2E3B1026B64}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A93:K93"/>
@@ -6570,7 +6590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3320E27B-962F-476C-99E3-6E9F568D33FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E01783F-2C0A-4160-A5B8-C3AEC1586AD7}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6836,7 +6856,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{3320E27B-962F-476C-99E3-6E9F568D33FD}"/>
+  <autoFilter ref="A3:E3" xr:uid="{5E01783F-2C0A-4160-A5B8-C3AEC1586AD7}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -6845,7 +6865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E09837FE-036D-4FB3-BAA5-EC4087018752}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB71E9C-31E0-4DC6-BFCA-3BEE75F95328}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7051,7 +7071,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A49328-CDC9-45AE-A439-B26F90F8A78A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751F6249-8DC4-4EF8-9465-E8BFDF814697}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7062,7 +7082,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -7075,106 +7095,106 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -7184,7 +7204,7 @@
         <v>180</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -7192,7 +7212,7 @@
         <v>189</v>
       </c>
       <c r="B15" s="9">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -7200,7 +7220,7 @@
         <v>204</v>
       </c>
       <c r="B16" s="9">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -7213,153 +7233,153 @@
     </row>
     <row r="28" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -7374,7 +7394,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A95DC96-FAC5-4233-862B-9887027141F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A5DB6D1-7BF2-44D1-B601-A2507581CBEE}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7902,7 +7922,7 @@
       <c r="G25" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{4A95DC96-FAC5-4233-862B-9887027141F4}"/>
+  <autoFilter ref="A3:G3" xr:uid="{7A5DB6D1-7BF2-44D1-B601-A2507581CBEE}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A25:G25"/>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91A7DED7-92AE-444D-9247-EB5D370DAB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBE692D2-1A3C-4593-8F2F-7F5C371C80A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{1C8EC45E-BD1F-45DD-8D0B-DA7242E61BEC}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{AC01D72F-FA82-4C2B-9D77-A0F2D6368433}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="569">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -856,10 +856,7 @@
     <t>Lineaire (detection - relance - rapport)</t>
   </si>
   <si>
-    <t>HAUTE</t>
-  </si>
-  <si>
-    <t>Meme patron que le TFJ Ventes deja construit</t>
+    <t>ECFCCRRL1 deja construit (meme patron que le TFJ Ventes)</t>
   </si>
   <si>
     <t>Score de qualification automatique</t>
@@ -1084,6 +1081,9 @@
     <t>Lineaire (analyse seuils - proposition commandes - validation - envoi)</t>
   </si>
   <si>
+    <t>ECFCAHRA1 deja construit (version simplifiee : liste de proposition - aucune commande fournisseur creee automatiquement)</t>
+  </si>
+  <si>
     <t>Analyse des depenses fournisseurs</t>
   </si>
   <si>
@@ -1102,15 +1102,21 @@
     <t>On surveille en continu si un produit tombe en rupture de stock pour alerter vite</t>
   </si>
   <si>
-    <t>Inventaire tournant et valorisation nocturne</t>
-  </si>
-  <si>
-    <t>Chaque nuit on compte une partie du stock - on repere les ecarts - on recalcule la valeur du stock</t>
+    <t>ECFJSTRU deja construit</t>
+  </si>
+  <si>
+    <t>Valorisation nocturne du stock</t>
+  </si>
+  <si>
+    <t>Chaque nuit on recalcule la valeur du stock disponible a partir du cout standard de chaque produit</t>
   </si>
   <si>
     <t>Lineaire (comptage - ecarts - valorisation - ajustement - rapport - verrouillage)</t>
   </si>
   <si>
+    <t>ECFCSTIN1 deja construit (version simplifiee : valorisation seule - PAS de comptage physique tournant - impossible sans materiel de terrain)</t>
+  </si>
+  <si>
     <t>Inventaire physique mensuel</t>
   </si>
   <si>
@@ -1195,6 +1201,9 @@
     <t>Lineaire (comptage - rapprochement - ecarts - validation)</t>
   </si>
   <si>
+    <t>ECFCPSCX1 deja construit (rapport de synthese par session - le rapprochement especes/carte physique reste fait par Odoo lui-meme a la fermeture de session)</t>
+  </si>
+  <si>
     <t>Rapport ventes mensuel par point de vente</t>
   </si>
   <si>
@@ -1303,7 +1312,7 @@
     <t>Lineaire (detection - alerte)</t>
   </si>
   <si>
-    <t>Champ hr.contract.date_end reel en Community - la paie calculee reste Enterprise mais pas la donnee de date</t>
+    <t>ECFCRHFC1 deja construit</t>
   </si>
   <si>
     <t>Processus de sortie (offboarding)</t>
@@ -1342,6 +1351,9 @@
     <t>Lineaire (extraction - calcul - validation - export)</t>
   </si>
   <si>
+    <t>ECFCPNHM1 deja construit (a partir des pointages hr.attendance reels)</t>
+  </si>
+  <si>
     <t>Rapport presences et anomalies quotidien (chaque jour du mois)</t>
   </si>
   <si>
@@ -1417,6 +1429,9 @@
     <t>Une fois par mois on facture au client le temps reellement passe sur son projet</t>
   </si>
   <si>
+    <t>ECFCPJFA1 deja construit (base chiffree consolidee - aucune facture generee automatiquement)</t>
+  </si>
+  <si>
     <t>Todo</t>
   </si>
   <si>
@@ -1537,7 +1552,7 @@
     <t>Distinct du PURGE systeme global (ECFCPRG1) - specifique au module data_recycle</t>
   </si>
   <si>
-    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 22 operations deja CONSTRUITES ET VERIFIEES (vert), 8 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
+    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 30 operations deja CONSTRUITES ET VERIFIEES (vert), 0 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
   </si>
   <si>
     <t>Maintien en condition operationnelle - preuves d'efficacite reelles</t>
@@ -1600,7 +1615,7 @@
     <t>Couverture du catalogue d'operations</t>
   </si>
   <si>
-    <t>22 des 88 operations cataloguees deja construites</t>
+    <t>30 des 88 operations cataloguees deja construites</t>
   </si>
   <si>
     <t>233 jobs estimes au total sur l'ensemble du catalogue si tout etait construit - roadmap explicite, jamais presente comme deja fait.</t>
@@ -1801,7 +1816,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1832,12 +1847,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1851,7 +1860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1890,10 +1899,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2094,14 +2099,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0DA8-451D-8A19-4D353F89230A}"/>
+              <c16:uniqueId val="{00000000-698F-4098-94CC-F6FAF4054EF1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2207,14 +2212,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>64</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0DA8-451D-8A19-4D353F89230A}"/>
+              <c16:uniqueId val="{00000002-698F-4098-94CC-F6FAF4054EF1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2327,7 +2332,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-0DA8-451D-8A19-4D353F89230A}"/>
+              <c16:uniqueId val="{00000003-698F-4098-94CC-F6FAF4054EF1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3004,7 +3009,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8CB4A2C-0ACF-4293-980B-DB6D33F055DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6237914F-3A94-40F9-A3AA-C989152A98E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3321,7 +3326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49005E43-6F93-4C86-A4CE-3B9E95856FFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE704001-D6E5-4994-8B51-DCCD02BA09C9}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3510,7 +3515,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE00EBB-670F-4983-9E58-B2E3B1026B64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{212957B2-3366-4C00-BC1C-7A7F483E834E}">
   <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4277,37 +4282,37 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="172.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="14">
         <v>3</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="H24" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I24" s="23" t="s">
+      <c r="H24" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="J24" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="K24" s="23" t="s">
+      <c r="K24" s="14" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4319,10 +4324,10 @@
         <v>125</v>
       </c>
       <c r="C25" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>272</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>273</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>224</v>
@@ -4331,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>204</v>
@@ -4352,10 +4357,10 @@
         <v>125</v>
       </c>
       <c r="C26" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>275</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>276</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>27</v>
@@ -4364,7 +4369,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>204</v>
@@ -4379,16 +4384,16 @@
     </row>
     <row r="27" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C27" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D27" s="14" t="s">
         <v>279</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>280</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>70</v>
@@ -4414,16 +4419,16 @@
     </row>
     <row r="28" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C28" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>281</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>282</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>70</v>
@@ -4449,16 +4454,16 @@
     </row>
     <row r="29" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C29" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>283</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>284</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>70</v>
@@ -4484,16 +4489,16 @@
     </row>
     <row r="30" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C30" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>285</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>286</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>17</v>
@@ -4502,7 +4507,7 @@
         <v>3</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>189</v>
@@ -4511,7 +4516,7 @@
         <v>190</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>192</v>
@@ -4519,16 +4524,16 @@
     </row>
     <row r="31" spans="1:11" ht="185.4" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C31" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>289</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>290</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>107</v>
@@ -4554,16 +4559,16 @@
     </row>
     <row r="32" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C32" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="14" t="s">
         <v>291</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>292</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>32</v>
@@ -4572,7 +4577,7 @@
         <v>5</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H32" s="14" t="s">
         <v>189</v>
@@ -4581,24 +4586,24 @@
         <v>190</v>
       </c>
       <c r="J32" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="K32" s="14" t="s">
         <v>294</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>130</v>
       </c>
       <c r="C33" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>296</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>297</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>37</v>
@@ -4617,21 +4622,21 @@
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="C34" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="D34" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>302</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>22</v>
@@ -4657,16 +4662,16 @@
     </row>
     <row r="35" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>300</v>
-      </c>
       <c r="C35" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D35" s="14" t="s">
         <v>303</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>304</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>17</v>
@@ -4675,7 +4680,7 @@
         <v>5</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H35" s="14" t="s">
         <v>189</v>
@@ -4684,7 +4689,7 @@
         <v>190</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K35" s="14" t="s">
         <v>192</v>
@@ -4692,16 +4697,16 @@
     </row>
     <row r="36" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B36" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>300</v>
-      </c>
       <c r="C36" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>307</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>308</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>17</v>
@@ -4710,7 +4715,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H36" s="14" t="s">
         <v>189</v>
@@ -4719,7 +4724,7 @@
         <v>190</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>192</v>
@@ -4727,25 +4732,25 @@
     </row>
     <row r="37" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>300</v>
-      </c>
       <c r="C37" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="E37" s="15" t="s">
         <v>312</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>313</v>
       </c>
       <c r="F37" s="15">
         <v>2</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>204</v>
@@ -4754,7 +4759,7 @@
         <v>205</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K37" s="15" t="s">
         <v>192</v>
@@ -4762,25 +4767,25 @@
     </row>
     <row r="38" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>300</v>
-      </c>
       <c r="C38" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="E38" s="15" t="s">
         <v>317</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>318</v>
       </c>
       <c r="F38" s="15">
         <v>3</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>204</v>
@@ -4789,7 +4794,7 @@
         <v>205</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K38" s="15" t="s">
         <v>192</v>
@@ -4797,16 +4802,16 @@
     </row>
     <row r="39" spans="1:11" ht="211.8" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>300</v>
-      </c>
       <c r="C39" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>321</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>322</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>32</v>
@@ -4815,7 +4820,7 @@
         <v>9</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H39" s="14" t="s">
         <v>189</v>
@@ -4824,24 +4829,24 @@
         <v>190</v>
       </c>
       <c r="J39" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="K39" s="14" t="s">
         <v>324</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B40" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>300</v>
-      </c>
       <c r="C40" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="D40" s="14" t="s">
         <v>326</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>327</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>37</v>
@@ -4850,7 +4855,7 @@
         <v>6</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H40" s="14" t="s">
         <v>189</v>
@@ -4859,24 +4864,24 @@
         <v>190</v>
       </c>
       <c r="J40" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="K40" s="14" t="s">
         <v>329</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="225" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>300</v>
-      </c>
       <c r="C41" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>331</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>332</v>
       </c>
       <c r="E41" s="15" t="s">
         <v>42</v>
@@ -4885,7 +4890,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H41" s="15" t="s">
         <v>204</v>
@@ -4894,24 +4899,24 @@
         <v>205</v>
       </c>
       <c r="J41" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="K41" s="15" t="s">
         <v>334</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C42" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="D42" s="14" t="s">
         <v>337</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>338</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>70</v>
@@ -4937,16 +4942,16 @@
     </row>
     <row r="43" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>70</v>
@@ -4972,7 +4977,7 @@
     </row>
     <row r="44" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>140</v>
@@ -4981,7 +4986,7 @@
         <v>145</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>70</v>
@@ -5007,16 +5012,16 @@
     </row>
     <row r="45" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C45" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>341</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>342</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>47</v>
@@ -5041,41 +5046,43 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="172.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="B46" s="22" t="s">
+      <c r="A46" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="D46" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="E46" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="14">
+        <v>4</v>
+      </c>
+      <c r="G46" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="E46" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="23">
-        <v>4</v>
-      </c>
-      <c r="G46" s="23" t="s">
+      <c r="H46" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J46" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="H46" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I46" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23" t="s">
+      <c r="K46" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>140</v>
@@ -5107,68 +5114,72 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="D48" s="23" t="s">
+      <c r="D48" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="E48" s="23" t="s">
+      <c r="E48" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="14">
         <v>2</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="G48" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="H48" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I48" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23" t="s">
+      <c r="H48" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="K48" s="14" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="22" t="s">
+    <row r="49" spans="1:11" ht="185.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="D49" s="23" t="s">
+      <c r="C49" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="D49" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="E49" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="14">
         <v>6</v>
       </c>
-      <c r="G49" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="H49" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23" t="s">
+      <c r="G49" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="K49" s="14" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5180,10 +5191,10 @@
         <v>147</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>32</v>
@@ -5202,7 +5213,7 @@
       </c>
       <c r="J50" s="15"/>
       <c r="K50" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
@@ -5213,10 +5224,10 @@
         <v>147</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>37</v>
@@ -5235,30 +5246,30 @@
       </c>
       <c r="J51" s="15"/>
       <c r="K51" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F52" s="15">
         <v>3</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H52" s="15" t="s">
         <v>204</v>
@@ -5273,16 +5284,16 @@
     </row>
     <row r="53" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>17</v>
@@ -5306,16 +5317,16 @@
     </row>
     <row r="54" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>32</v>
@@ -5339,16 +5350,16 @@
     </row>
     <row r="55" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>107</v>
@@ -5372,16 +5383,16 @@
     </row>
     <row r="56" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>17</v>
@@ -5405,16 +5416,16 @@
     </row>
     <row r="57" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>252</v>
@@ -5438,16 +5449,16 @@
     </row>
     <row r="58" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>32</v>
@@ -5469,51 +5480,53 @@
         <v>192</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="B59" s="22" t="s">
+    <row r="59" spans="1:11" ht="198.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B59" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C59" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="E59" s="23" t="s">
+      <c r="C59" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="E59" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F59" s="23">
+      <c r="F59" s="14">
         <v>4</v>
       </c>
-      <c r="G59" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="H59" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I59" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23" t="s">
+      <c r="G59" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J59" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="K59" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>161</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>32</v>
@@ -5537,16 +5550,16 @@
     </row>
     <row r="61" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>164</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E61" s="15" t="s">
         <v>17</v>
@@ -5570,16 +5583,16 @@
     </row>
     <row r="62" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>27</v>
@@ -5603,16 +5616,16 @@
     </row>
     <row r="63" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>17</v>
@@ -5636,16 +5649,16 @@
     </row>
     <row r="64" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>107</v>
@@ -5654,7 +5667,7 @@
         <v>2</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H64" s="15" t="s">
         <v>204</v>
@@ -5669,16 +5682,16 @@
     </row>
     <row r="65" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>252</v>
@@ -5702,16 +5715,16 @@
     </row>
     <row r="66" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>32</v>
@@ -5735,16 +5748,16 @@
     </row>
     <row r="67" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>32</v>
@@ -5768,16 +5781,16 @@
     </row>
     <row r="68" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>252</v>
@@ -5801,16 +5814,16 @@
     </row>
     <row r="69" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>32</v>
@@ -5834,16 +5847,16 @@
     </row>
     <row r="70" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>42</v>
@@ -5862,56 +5875,56 @@
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="277.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="C71" s="23" t="s">
-        <v>416</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>417</v>
-      </c>
-      <c r="E71" s="23" t="s">
+      <c r="A71" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E71" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F71" s="23">
+      <c r="F71" s="14">
         <v>2</v>
       </c>
-      <c r="G71" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="H71" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I71" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J71" s="23" t="s">
-        <v>419</v>
-      </c>
-      <c r="K71" s="23" t="s">
+      <c r="G71" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="K71" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="225" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E72" s="15" t="s">
         <v>70</v>
@@ -5920,7 +5933,7 @@
         <v>3</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="H72" s="15" t="s">
         <v>204</v>
@@ -5929,24 +5942,24 @@
         <v>205</v>
       </c>
       <c r="J72" s="15" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E73" s="15" t="s">
         <v>17</v>
@@ -5969,50 +5982,52 @@
       </c>
     </row>
     <row r="74" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A74" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="B74" s="22" t="s">
-        <v>426</v>
-      </c>
-      <c r="C74" s="23" t="s">
+      <c r="A74" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="B74" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="D74" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="E74" s="23" t="s">
+      <c r="C74" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E74" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F74" s="23">
+      <c r="F74" s="14">
         <v>4</v>
       </c>
-      <c r="G74" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="H74" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I74" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J74" s="23"/>
-      <c r="K74" s="23" t="s">
-        <v>432</v>
+      <c r="G74" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E75" s="15" t="s">
         <v>107</v>
@@ -6036,16 +6051,16 @@
     </row>
     <row r="76" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E76" s="15" t="s">
         <v>42</v>
@@ -6069,16 +6084,16 @@
     </row>
     <row r="77" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E77" s="15" t="s">
         <v>32</v>
@@ -6102,16 +6117,16 @@
     </row>
     <row r="78" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E78" s="15" t="s">
         <v>17</v>
@@ -6135,16 +6150,16 @@
     </row>
     <row r="79" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E79" s="15" t="s">
         <v>32</v>
@@ -6168,16 +6183,16 @@
     </row>
     <row r="80" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E80" s="15" t="s">
         <v>17</v>
@@ -6199,51 +6214,53 @@
         <v>192</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A81" s="22" t="s">
-        <v>451</v>
-      </c>
-      <c r="B81" s="22" t="s">
-        <v>452</v>
-      </c>
-      <c r="C81" s="23" t="s">
+    <row r="81" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="D81" s="23" t="s">
+      <c r="B81" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="E81" s="23" t="s">
+      <c r="C81" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="E81" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F81" s="23">
+      <c r="F81" s="14">
         <v>3</v>
       </c>
-      <c r="G81" s="23" t="s">
+      <c r="G81" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="H81" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="I81" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="J81" s="23"/>
-      <c r="K81" s="23" t="s">
+      <c r="H81" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="K81" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E82" s="15" t="s">
         <v>107</v>
@@ -6267,16 +6284,16 @@
     </row>
     <row r="83" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E83" s="15" t="s">
         <v>32</v>
@@ -6300,16 +6317,16 @@
     </row>
     <row r="84" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="E84" s="15" t="s">
         <v>70</v>
@@ -6333,16 +6350,16 @@
     </row>
     <row r="85" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>47</v>
@@ -6366,16 +6383,16 @@
     </row>
     <row r="86" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E86" s="15" t="s">
         <v>27</v>
@@ -6399,16 +6416,16 @@
     </row>
     <row r="87" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E87" s="15" t="s">
         <v>107</v>
@@ -6417,7 +6434,7 @@
         <v>2</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="H87" s="15" t="s">
         <v>204</v>
@@ -6432,16 +6449,16 @@
     </row>
     <row r="88" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E88" s="15" t="s">
         <v>32</v>
@@ -6465,16 +6482,16 @@
     </row>
     <row r="89" spans="1:11" ht="93" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E89" s="15" t="s">
         <v>107</v>
@@ -6498,16 +6515,16 @@
     </row>
     <row r="90" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E90" s="15" t="s">
         <v>27</v>
@@ -6531,16 +6548,16 @@
     </row>
     <row r="91" spans="1:11" ht="159" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E91" s="15" t="s">
         <v>32</v>
@@ -6558,7 +6575,7 @@
         <v>226</v>
       </c>
       <c r="J91" s="15" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="K91" s="15" t="s">
         <v>192</v>
@@ -6566,7 +6583,7 @@
     </row>
     <row r="93" spans="1:11" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="21" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -6580,7 +6597,7 @@
       <c r="K93" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{CDE00EBB-670F-4983-9E58-B2E3B1026B64}"/>
+  <autoFilter ref="A3:K3" xr:uid="{212957B2-3366-4C00-BC1C-7A7F483E834E}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A93:K93"/>
@@ -6590,7 +6607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E01783F-2C0A-4160-A5B8-C3AEC1586AD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937856B8-291B-4ACD-B2C9-46CFAF4660FE}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6856,7 +6873,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{5E01783F-2C0A-4160-A5B8-C3AEC1586AD7}"/>
+  <autoFilter ref="A3:E3" xr:uid="{937856B8-291B-4ACD-B2C9-46CFAF4660FE}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -6865,7 +6882,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB71E9C-31E0-4DC6-BFCA-3BEE75F95328}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF327DC-5CE6-4792-8200-F73E7EDB480B}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7071,7 +7088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751F6249-8DC4-4EF8-9465-E8BFDF814697}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C61CA53-3AC6-45C8-86E2-BC529700CCD4}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7082,11 +7099,11 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
-      <c r="D1" s="24"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -7095,116 +7112,116 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>504</v>
+        <v>507</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>506</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>507</v>
+        <v>510</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>509</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>510</v>
+        <v>513</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>512</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>513</v>
+        <v>516</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>515</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>516</v>
+        <v>519</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>518</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>519</v>
+        <v>522</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>521</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>522</v>
+        <v>525</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>524</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>525</v>
+        <v>528</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>527</v>
+      <c r="B14" s="24" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -7212,7 +7229,7 @@
         <v>189</v>
       </c>
       <c r="B15" s="9">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -7220,7 +7237,7 @@
         <v>204</v>
       </c>
       <c r="B16" s="9">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -7233,153 +7250,153 @@
     </row>
     <row r="28" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -7394,7 +7411,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A5DB6D1-7BF2-44D1-B601-A2507581CBEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF3F253D-849E-4527-9BA7-B951D8E7521D}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7922,7 +7939,7 @@
       <c r="G25" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{7A5DB6D1-7BF2-44D1-B601-A2507581CBEE}"/>
+  <autoFilter ref="A3:G3" xr:uid="{FF3F253D-849E-4527-9BA7-B951D8E7521D}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A25:G25"/>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBE692D2-1A3C-4593-8F2F-7F5C371C80A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C30B0E-B21A-4E5F-B9B6-82117F53497E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{AC01D72F-FA82-4C2B-9D77-A0F2D6368433}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{C843DDEC-7FC3-42E3-8056-764180141529}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="589">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -565,7 +565,7 @@
     <t>Extrait de 20 lignes sur la simulation complete (~50 traitements, documentee integralement dans docs/JOURNAL_TECHNIQUE.md). Lignes en vert : les 6 traitements qui demarrent EXACTEMENT au meme instant (T+0) - la premiere vague. Chaque ligne suivante demarre des qu'UN emplacement se libere (pas le lot entier) - c'est le comportement reel verifie par harnais de simulation.</t>
   </si>
   <si>
-    <t>Catalogue des operations reelles possibles sur Odoo 19 Community - dimension bancaire (conformite, cycles, flux externes)</t>
+    <t>Catalogue des operations reelles possibles sur Odoo 19 Community - dimension bancaire (conformite, cycles, flux externes) - groupe par module, cliquez sur le -/+ dans la marge</t>
   </si>
   <si>
     <t>Module</t>
@@ -601,6 +601,9 @@
     <t>Systeme</t>
   </si>
   <si>
+    <t>5 operation(s) - 3 construite(s) - 32 jobs estimes</t>
+  </si>
+  <si>
     <t>SYS</t>
   </si>
   <si>
@@ -688,6 +691,9 @@
     <t>Contacts</t>
   </si>
   <si>
+    <t>4 operation(s) - 0 construite(s) - 11 jobs estimes</t>
+  </si>
+  <si>
     <t>CT</t>
   </si>
   <si>
@@ -739,6 +745,9 @@
     <t>Calendrier</t>
   </si>
   <si>
+    <t>4 operation(s) - 0 construite(s) - 7 jobs estimes</t>
+  </si>
+  <si>
     <t>CL</t>
   </si>
   <si>
@@ -781,6 +790,9 @@
     <t>Discuss</t>
   </si>
   <si>
+    <t>3 operation(s) - 0 construite(s) - 4 jobs estimes</t>
+  </si>
+  <si>
     <t>DS</t>
   </si>
   <si>
@@ -817,6 +829,9 @@
     <t>CRM</t>
   </si>
   <si>
+    <t>7 operation(s) - 5 construite(s) - 13 jobs estimes</t>
+  </si>
+  <si>
     <t>Creation de piste</t>
   </si>
   <si>
@@ -880,6 +895,9 @@
     <t>Ventes</t>
   </si>
   <si>
+    <t>7 operation(s) - 6 construite(s) - 16 jobs estimes</t>
+  </si>
+  <si>
     <t>Creation de devis</t>
   </si>
   <si>
@@ -943,6 +961,9 @@
     <t>Comptabilite</t>
   </si>
   <si>
+    <t>8 operation(s) - 5 construite(s) - 40 jobs estimes</t>
+  </si>
+  <si>
     <t>CP</t>
   </si>
   <si>
@@ -1054,6 +1075,9 @@
     <t>Achat</t>
   </si>
   <si>
+    <t>6 operation(s) - 5 construite(s) - 11 jobs estimes</t>
+  </si>
+  <si>
     <t>Creation de commande fournisseur</t>
   </si>
   <si>
@@ -1096,6 +1120,9 @@
     <t>Stock</t>
   </si>
   <si>
+    <t>4 operation(s) - 2 construite(s) - 16 jobs estimes</t>
+  </si>
+  <si>
     <t>Alertes de rupture en temps quasi-reel</t>
   </si>
   <si>
@@ -1138,6 +1165,9 @@
     <t>MRP</t>
   </si>
   <si>
+    <t>3 operation(s) - 0 construite(s) - 9 jobs estimes</t>
+  </si>
+  <si>
     <t>Lancement des ordres de fabrication planifies</t>
   </si>
   <si>
@@ -1162,6 +1192,9 @@
     <t>Reparation</t>
   </si>
   <si>
+    <t>2 operation(s) - 0 construite(s) - 3 jobs estimes</t>
+  </si>
+  <si>
     <t>Notification avancement reparation</t>
   </si>
   <si>
@@ -1192,6 +1225,9 @@
     <t>Point de vente</t>
   </si>
   <si>
+    <t>2 operation(s) - 1 construite(s) - 7 jobs estimes</t>
+  </si>
+  <si>
     <t>Cloture de caisse quotidienne</t>
   </si>
   <si>
@@ -1213,6 +1249,9 @@
     <t>POS Restaurant</t>
   </si>
   <si>
+    <t>1 operation(s) - 0 construite(s) - 3 jobs estimes</t>
+  </si>
+  <si>
     <t>Cloture de service (midi/soir)</t>
   </si>
   <si>
@@ -1222,6 +1261,9 @@
     <t>Site web</t>
   </si>
   <si>
+    <t>1 operation(s) - 0 construite(s) - 2 jobs estimes</t>
+  </si>
+  <si>
     <t>SI</t>
   </si>
   <si>
@@ -1234,6 +1276,9 @@
     <t>eCommerce</t>
   </si>
   <si>
+    <t>2 operation(s) - 0 construite(s) - 5 jobs estimes</t>
+  </si>
+  <si>
     <t>Rapport ventes en ligne et paniers abandonnes</t>
   </si>
   <si>
@@ -1276,6 +1321,9 @@
     <t>Offres emploi web</t>
   </si>
   <si>
+    <t>1 operation(s) - 0 construite(s) - 1 jobs estimes</t>
+  </si>
+  <si>
     <t>JW</t>
   </si>
   <si>
@@ -1288,6 +1336,9 @@
     <t>RH</t>
   </si>
   <si>
+    <t>4 operation(s) - 1 construite(s) - 10 jobs estimes</t>
+  </si>
+  <si>
     <t>Rapport effectifs et anciennete</t>
   </si>
   <si>
@@ -1333,6 +1384,9 @@
     <t>Presences</t>
   </si>
   <si>
+    <t>2 operation(s) - 1 construite(s) - 6 jobs estimes</t>
+  </si>
+  <si>
     <t>PN</t>
   </si>
   <si>
@@ -1414,6 +1468,9 @@
     <t>Projets</t>
   </si>
   <si>
+    <t>2 operation(s) - 1 construite(s) - 5 jobs estimes</t>
+  </si>
+  <si>
     <t>PJ</t>
   </si>
   <si>
@@ -1493,6 +1550,9 @@
   </si>
   <si>
     <t>Email marketing</t>
+  </si>
+  <si>
+    <t>2 operation(s) - 0 construite(s) - 4 jobs estimes</t>
   </si>
   <si>
     <t>EM</t>
@@ -1757,7 +1817,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1809,6 +1869,20 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFDCDCE6"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1816,7 +1890,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1847,6 +1921,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3C1E5A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1860,7 +1940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1901,7 +1981,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2106,7 +2194,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-698F-4098-94CC-F6FAF4054EF1}"/>
+              <c16:uniqueId val="{00000000-288E-4214-86DE-4CAF5592C1BF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2219,7 +2307,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-698F-4098-94CC-F6FAF4054EF1}"/>
+              <c16:uniqueId val="{00000002-288E-4214-86DE-4CAF5592C1BF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2332,7 +2420,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-698F-4098-94CC-F6FAF4054EF1}"/>
+              <c16:uniqueId val="{00000003-288E-4214-86DE-4CAF5592C1BF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3009,7 +3097,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6237914F-3A94-40F9-A3AA-C989152A98E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8719C1A-B0B3-4789-8A08-500876D46068}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3326,7 +3414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE704001-D6E5-4994-8B51-DCCD02BA09C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C70B66-E20C-4DC8-9E1E-71C29153BD0A}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3515,9 +3603,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{212957B2-3366-4C00-BC1C-7A7F483E834E}">
-  <dimension ref="A1:K93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7ADAC8F-C4B3-41C5-9D53-D92AC1084FA5}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:K128"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="2" width="8.77734375" customWidth="1"/>
@@ -3595,531 +3686,481 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="211.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="14">
-        <v>20</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" spans="1:11" ht="211.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>184</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="14">
+        <v>20</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="14">
-        <v>1</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" ht="132.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>184</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="F6" s="14">
         <v>1</v>
       </c>
       <c r="G6" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I6" s="14" t="s">
+      <c r="E7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="14">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H7" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="198.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="I7" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="198.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="B8" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="D8" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F8" s="15">
         <v>4</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="H7" s="15" t="s">
+      <c r="G8" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="H8" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="I8" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="J8" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="D8" s="17" t="s">
+      <c r="B9" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="D9" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F9" s="17">
         <v>6</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="H8" s="17" t="s">
+      <c r="G9" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="H9" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="I9" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="K8" s="17" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="J9" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="K9" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="C11" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F11" s="15">
         <v>3</v>
       </c>
-      <c r="G9" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="G11" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="H11" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J9" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="I11" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="B12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F12" s="15">
         <v>4</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I10" s="15" t="s">
+      <c r="G12" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="H12" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="F11" s="15">
-        <v>2</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="15">
-        <v>2</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="I12" s="15" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="93" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F13" s="15">
+        <v>2</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="D14" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" s="15">
-        <v>1</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>237</v>
-      </c>
       <c r="E14" s="15" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="F14" s="15">
         <v>2</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+    </row>
+    <row r="16" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="F16" s="15">
         <v>1</v>
       </c>
       <c r="G16" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="H16" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I16" s="15" t="s">
+      <c r="C17" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="15">
+        <v>2</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="132.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="F18" s="15">
+        <v>3</v>
+      </c>
+      <c r="G18" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F18" s="15">
-        <v>2</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>253</v>
-      </c>
       <c r="H18" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>254</v>
-      </c>
       <c r="D19" s="15" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>32</v>
@@ -4128,272 +4169,236 @@
         <v>1</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="25" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+    </row>
+    <row r="21" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="17">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+    </row>
+    <row r="25" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="C25" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="E25" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F25" s="14">
         <v>1</v>
       </c>
-      <c r="G20" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="14" t="s">
+      <c r="G25" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="I25" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K20" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="185.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="K25" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="185.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="D21" s="14" t="s">
+      <c r="C26" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="14">
+        <v>1</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="14">
-        <v>1</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="B27" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="14">
-        <v>2</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J23" s="14" t="s">
+      <c r="C27" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="K23" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="172.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>267</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="14">
-        <v>3</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="185.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="F25" s="15">
-        <v>2</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="172.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="15">
-        <v>3</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>279</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>70</v>
@@ -4402,1898 +4407,1704 @@
         <v>1</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>129</v>
+        <v>268</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="93" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="132.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>70</v>
       </c>
       <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="172.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="14">
+        <v>3</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="185.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F30" s="15">
+        <v>2</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="172.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="15">
+        <v>3</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+    </row>
+    <row r="33" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I28" s="14" t="s">
+      <c r="G33" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H33" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J28" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="I33" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="E29" s="14" t="s">
+      <c r="C34" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E34" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="185.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="14">
-        <v>5</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="15">
-        <v>4</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I33" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="F34" s="14">
         <v>1</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I34" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="14">
+        <v>1</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H35" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J34" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="14">
-        <v>5</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>189</v>
-      </c>
       <c r="I35" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>305</v>
+        <v>134</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="159" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>299</v>
+        <v>130</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>17</v>
       </c>
       <c r="F36" s="14">
+        <v>3</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="185.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="14">
+        <v>1</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" s="14">
+        <v>5</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" s="15">
+        <v>4</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+    </row>
+    <row r="41" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="14">
+        <v>1</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="14">
+        <v>5</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="14">
         <v>2</v>
       </c>
-      <c r="G36" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I36" s="14" t="s">
+      <c r="G43" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="H43" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J36" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="F37" s="15">
+      <c r="I43" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="132.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="F44" s="15">
         <v>2</v>
       </c>
-      <c r="G37" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I37" s="15" t="s">
+      <c r="G44" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="H44" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J37" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>315</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="F38" s="15">
+      <c r="I44" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="F45" s="15">
         <v>3</v>
       </c>
-      <c r="G38" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I38" s="15" t="s">
+      <c r="G45" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="H45" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J38" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="211.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="E39" s="14" t="s">
+      <c r="I45" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="211.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="E46" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F46" s="14">
         <v>9</v>
       </c>
-      <c r="G39" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="H39" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I39" s="14" t="s">
+      <c r="G46" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="H46" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J39" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="132.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="E40" s="14" t="s">
+      <c r="I46" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="132.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="E47" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F40" s="14">
+      <c r="F47" s="14">
         <v>6</v>
       </c>
-      <c r="G40" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I40" s="14" t="s">
+      <c r="G47" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="H47" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J40" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="225" x14ac:dyDescent="0.3">
-      <c r="A41" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="E41" s="15" t="s">
+      <c r="I47" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="225" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="E48" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F48" s="15">
         <v>12</v>
       </c>
-      <c r="G41" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I41" s="15" t="s">
+      <c r="G48" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="H48" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J41" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="B42" s="11" t="s">
+      <c r="I48" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="B49" s="22"/>
+      <c r="C49" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+    </row>
+    <row r="50" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="E42" s="14" t="s">
+      <c r="C50" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="E50" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F42" s="14">
+      <c r="F50" s="14">
         <v>1</v>
       </c>
-      <c r="G42" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I42" s="14" t="s">
+      <c r="G50" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H50" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J42" s="14" t="s">
+      <c r="I50" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J50" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="K42" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="B43" s="11" t="s">
+      <c r="K50" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="E43" s="14" t="s">
+      <c r="C51" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="E51" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F43" s="14">
+      <c r="F51" s="14">
         <v>1</v>
       </c>
-      <c r="G43" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I43" s="14" t="s">
+      <c r="G51" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H51" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J43" s="14" t="s">
+      <c r="I51" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J51" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="K43" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="B44" s="11" t="s">
+      <c r="K51" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C52" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D44" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="E44" s="14" t="s">
+      <c r="D52" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F44" s="14">
+      <c r="F52" s="14">
         <v>1</v>
       </c>
-      <c r="G44" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I44" s="14" t="s">
+      <c r="G52" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H52" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J44" s="14" t="s">
+      <c r="I52" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J52" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="K44" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="B45" s="11" t="s">
+      <c r="K52" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B53" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="E45" s="14" t="s">
+      <c r="C53" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="E53" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F45" s="14">
+      <c r="F53" s="14">
         <v>1</v>
       </c>
-      <c r="G45" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I45" s="14" t="s">
+      <c r="G53" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H53" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J45" s="14" t="s">
+      <c r="I53" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J53" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="K45" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="172.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="B46" s="11" t="s">
+      <c r="K53" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="172.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B54" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C54" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="14">
+        <v>4</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="D46" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="14">
-        <v>4</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A47" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="B47" s="9" t="s">
+      <c r="B55" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="E47" s="15" t="s">
+      <c r="C55" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="E55" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F55" s="15">
         <v>3</v>
       </c>
-      <c r="G47" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I47" s="15" t="s">
+      <c r="G55" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="F48" s="14">
-        <v>2</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="185.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" s="14">
-        <v>6</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J49" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="K49" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" s="15">
-        <v>5</v>
-      </c>
-      <c r="G50" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F51" s="15">
-        <v>3</v>
-      </c>
-      <c r="G51" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="F52" s="15">
-        <v>3</v>
-      </c>
-      <c r="G52" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A53" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="15">
-        <v>4</v>
-      </c>
-      <c r="G53" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H53" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" s="15">
-        <v>2</v>
-      </c>
-      <c r="G54" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H54" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I54" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F55" s="15">
-        <v>1</v>
-      </c>
-      <c r="G55" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H55" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="I55" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J55" s="15"/>
       <c r="K55" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>375</v>
-      </c>
-      <c r="E56" s="15" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="B56" s="22"/>
+      <c r="C56" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+    </row>
+    <row r="57" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F57" s="14">
+        <v>2</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="185.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="E58" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F56" s="15">
-        <v>2</v>
-      </c>
-      <c r="G56" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H56" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I56" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F57" s="15">
-        <v>1</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H57" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I57" s="15" t="s">
+      <c r="F58" s="14">
+        <v>6</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" s="15">
+        <v>5</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H59" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F58" s="15">
-        <v>2</v>
-      </c>
-      <c r="G58" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H58" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="198.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>383</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F59" s="14">
-        <v>4</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J59" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="K59" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
+      <c r="I59" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F60" s="15">
         <v>3</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I60" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J60" s="15"/>
       <c r="K60" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A61" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="15">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="B61" s="22"/>
+      <c r="C61" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="23"/>
+    </row>
+    <row r="62" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="F62" s="15">
         <v>3</v>
       </c>
-      <c r="G61" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H61" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I61" s="15" t="s">
+      <c r="G62" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="H62" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="E62" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F62" s="15">
-        <v>2</v>
-      </c>
-      <c r="G62" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H62" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="I62" s="15" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J62" s="15"/>
       <c r="K62" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>17</v>
       </c>
       <c r="F63" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H63" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J63" s="15"/>
       <c r="K63" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="F64" s="15">
         <v>2</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>308</v>
+        <v>200</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I64" s="15" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="J64" s="15"/>
       <c r="K64" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A65" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F65" s="15">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="B65" s="22"/>
+      <c r="C65" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="23"/>
+      <c r="I65" s="23"/>
+      <c r="J65" s="23"/>
+      <c r="K65" s="23"/>
+    </row>
+    <row r="66" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F66" s="15">
         <v>1</v>
       </c>
-      <c r="G65" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A66" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F66" s="15">
-        <v>2</v>
-      </c>
       <c r="G66" s="15" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I66" s="15" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J66" s="15"/>
       <c r="K66" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="93" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>406</v>
+        <v>155</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F67" s="15">
         <v>2</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J67" s="15"/>
       <c r="K67" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A68" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="E68" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F68" s="15">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="B68" s="22"/>
+      <c r="C68" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="D68" s="23"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="23"/>
+    </row>
+    <row r="69" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F69" s="15">
         <v>1</v>
       </c>
-      <c r="G68" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H68" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I68" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A69" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="E69" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F69" s="15">
-        <v>2</v>
-      </c>
       <c r="G69" s="15" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J69" s="15"/>
       <c r="K69" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>413</v>
+        <v>158</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F70" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="277.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="E71" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="B71" s="22"/>
+      <c r="C71" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
+      <c r="I71" s="23"/>
+      <c r="J71" s="23"/>
+      <c r="K71" s="23"/>
+    </row>
+    <row r="72" spans="1:11" ht="198.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="E72" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F71" s="14">
-        <v>2</v>
-      </c>
-      <c r="G71" s="14" t="s">
-        <v>421</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I71" s="14" t="s">
+      <c r="F72" s="14">
+        <v>4</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="H72" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="J71" s="14" t="s">
-        <v>422</v>
-      </c>
-      <c r="K71" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="225" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="E72" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F72" s="15">
+      <c r="I72" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" s="15">
         <v>3</v>
       </c>
-      <c r="G72" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="H72" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I72" s="15" t="s">
+      <c r="G73" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H73" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J72" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="K72" s="15" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="66.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A73" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F73" s="15">
-        <v>2</v>
-      </c>
-      <c r="G73" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="I73" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J73" s="15"/>
       <c r="K73" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A74" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>429</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F74" s="14">
-        <v>4</v>
-      </c>
-      <c r="G74" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="H74" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I74" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J74" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="K74" s="14" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="24" t="s">
+        <v>400</v>
+      </c>
+      <c r="B74" s="22"/>
+      <c r="C74" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+      <c r="K74" s="23"/>
+    </row>
+    <row r="75" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>438</v>
+        <v>164</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="F75" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" s="15" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J75" s="15"/>
       <c r="K75" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A76" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E76" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F76" s="15">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="B76" s="22"/>
+      <c r="C76" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="23"/>
+      <c r="K76" s="23"/>
+    </row>
+    <row r="77" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="15">
         <v>2</v>
       </c>
-      <c r="G76" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H76" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I76" s="15" t="s">
+      <c r="G77" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H77" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="E77" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F77" s="15">
-        <v>3</v>
-      </c>
-      <c r="G77" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H77" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="I77" s="15" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="J77" s="15"/>
       <c r="K77" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="E78" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="B78" s="22"/>
+      <c r="C78" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="D78" s="23"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
+      <c r="K78" s="23"/>
+    </row>
+    <row r="79" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="E79" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F78" s="15">
-        <v>1</v>
-      </c>
-      <c r="G78" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H78" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I78" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="E79" s="15" t="s">
-        <v>32</v>
-      </c>
       <c r="F79" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J79" s="15"/>
       <c r="K79" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>455</v>
+        <v>409</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>456</v>
+        <v>167</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>458</v>
+        <v>414</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="F80" s="15">
         <v>2</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>199</v>
+        <v>315</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I80" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J80" s="15"/>
       <c r="K80" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A81" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>456</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F81" s="14">
-        <v>3</v>
-      </c>
-      <c r="G81" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="H81" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I81" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="J81" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="K81" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="79.8" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="B81" s="22"/>
+      <c r="C81" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="D81" s="23"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="23"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="23"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="23"/>
+      <c r="K81" s="23"/>
+    </row>
+    <row r="82" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>463</v>
+        <v>170</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>465</v>
+        <v>417</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="F82" s="15">
         <v>1</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I82" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J82" s="15"/>
       <c r="K82" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>467</v>
+        <v>170</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>468</v>
+        <v>418</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>469</v>
+        <v>419</v>
       </c>
       <c r="E83" s="15" t="s">
         <v>32</v>
@@ -6302,312 +6113,1222 @@
         <v>2</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J83" s="15"/>
       <c r="K83" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A84" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="E84" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F84" s="15">
-        <v>1</v>
-      </c>
-      <c r="G84" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H84" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I84" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J84" s="15"/>
-      <c r="K84" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="145.80000000000001" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="B84" s="22"/>
+      <c r="C84" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="D84" s="23"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="23"/>
+      <c r="G84" s="23"/>
+      <c r="H84" s="23"/>
+      <c r="I84" s="23"/>
+      <c r="J84" s="23"/>
+      <c r="K84" s="23"/>
+    </row>
+    <row r="85" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>474</v>
+        <v>420</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>476</v>
+        <v>422</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>477</v>
+        <v>423</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F85" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="H85" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I85" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J85" s="15"/>
       <c r="K85" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F86" s="15">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="B86" s="22"/>
+      <c r="C86" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="23"/>
+      <c r="J86" s="23"/>
+      <c r="K86" s="23"/>
+    </row>
+    <row r="87" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F87" s="15">
         <v>1</v>
       </c>
-      <c r="G86" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="H86" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I86" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J86" s="15"/>
-      <c r="K86" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A87" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="C87" s="15" t="s">
-        <v>484</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="E87" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="F87" s="15">
-        <v>2</v>
-      </c>
       <c r="G87" s="15" t="s">
-        <v>486</v>
+        <v>237</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I87" s="15" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="J87" s="15"/>
       <c r="K87" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>487</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>488</v>
-      </c>
-      <c r="E88" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="B88" s="22"/>
+      <c r="C88" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="23"/>
+      <c r="K88" s="23"/>
+    </row>
+    <row r="89" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="E89" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="F88" s="15">
-        <v>2</v>
-      </c>
-      <c r="G88" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H88" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I88" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J88" s="15"/>
-      <c r="K88" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="93" x14ac:dyDescent="0.3">
-      <c r="A89" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="C89" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>492</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>107</v>
       </c>
       <c r="F89" s="15">
         <v>2</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H89" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I89" s="15" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J89" s="15"/>
       <c r="K89" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="119.4" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
-        <v>493</v>
+        <v>429</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>494</v>
+        <v>429</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>495</v>
+        <v>433</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>496</v>
+        <v>434</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F90" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="H90" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I90" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J90" s="15"/>
       <c r="K90" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="159" x14ac:dyDescent="0.3">
-      <c r="A91" s="9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="277.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="14">
+        <v>2</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I91" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J91" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="K91" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="225" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F92" s="15">
+        <v>3</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="H92" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I92" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="K92" s="15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="B93" s="22"/>
+      <c r="C93" s="25" t="s">
+        <v>446</v>
+      </c>
+      <c r="D93" s="23"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="23"/>
+      <c r="J93" s="23"/>
+      <c r="K93" s="23"/>
+    </row>
+    <row r="94" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="15">
+        <v>2</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I94" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F95" s="14">
+        <v>4</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I95" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="K95" s="14" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="B96" s="22"/>
+      <c r="C96" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="D96" s="23"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="23"/>
+      <c r="I96" s="23"/>
+      <c r="J96" s="23"/>
+      <c r="K96" s="23"/>
+    </row>
+    <row r="97" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F97" s="15">
+        <v>1</v>
+      </c>
+      <c r="G97" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I97" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" s="15">
+        <v>2</v>
+      </c>
+      <c r="G98" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H98" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B99" s="22"/>
+      <c r="C99" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="D99" s="23"/>
+      <c r="E99" s="23"/>
+      <c r="F99" s="23"/>
+      <c r="G99" s="23"/>
+      <c r="H99" s="23"/>
+      <c r="I99" s="23"/>
+      <c r="J99" s="23"/>
+      <c r="K99" s="23"/>
+    </row>
+    <row r="100" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F100" s="15">
+        <v>3</v>
+      </c>
+      <c r="G100" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H100" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I100" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J100" s="15"/>
+      <c r="K100" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="B101" s="22"/>
+      <c r="C101" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="D101" s="23"/>
+      <c r="E101" s="23"/>
+      <c r="F101" s="23"/>
+      <c r="G101" s="23"/>
+      <c r="H101" s="23"/>
+      <c r="I101" s="23"/>
+      <c r="J101" s="23"/>
+      <c r="K101" s="23"/>
+    </row>
+    <row r="102" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F102" s="15">
+        <v>1</v>
+      </c>
+      <c r="G102" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H102" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I102" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J102" s="15"/>
+      <c r="K102" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="B103" s="22"/>
+      <c r="C103" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="D103" s="23"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
+      <c r="G103" s="23"/>
+      <c r="H103" s="23"/>
+      <c r="I103" s="23"/>
+      <c r="J103" s="23"/>
+      <c r="K103" s="23"/>
+    </row>
+    <row r="104" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F104" s="15">
+        <v>2</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H104" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J104" s="15"/>
+      <c r="K104" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="B105" s="22"/>
+      <c r="C105" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="D105" s="23"/>
+      <c r="E105" s="23"/>
+      <c r="F105" s="23"/>
+      <c r="G105" s="23"/>
+      <c r="H105" s="23"/>
+      <c r="I105" s="23"/>
+      <c r="J105" s="23"/>
+      <c r="K105" s="23"/>
+    </row>
+    <row r="106" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" s="15">
+        <v>2</v>
+      </c>
+      <c r="G106" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J106" s="15"/>
+      <c r="K106" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F107" s="14">
+        <v>3</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I107" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J107" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="K107" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="B108" s="22"/>
+      <c r="C108" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="D108" s="23"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
+      <c r="K108" s="23"/>
+    </row>
+    <row r="109" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="E109" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F109" s="15">
+        <v>1</v>
+      </c>
+      <c r="G109" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I109" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J109" s="15"/>
+      <c r="K109" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="B110" s="22"/>
+      <c r="C110" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="D110" s="23"/>
+      <c r="E110" s="23"/>
+      <c r="F110" s="23"/>
+      <c r="G110" s="23"/>
+      <c r="H110" s="23"/>
+      <c r="I110" s="23"/>
+      <c r="J110" s="23"/>
+      <c r="K110" s="23"/>
+    </row>
+    <row r="111" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F111" s="15">
+        <v>2</v>
+      </c>
+      <c r="G111" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I111" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J111" s="15"/>
+      <c r="K111" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="B112" s="22"/>
+      <c r="C112" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="D112" s="23"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="23"/>
+      <c r="G112" s="23"/>
+      <c r="H112" s="23"/>
+      <c r="I112" s="23"/>
+      <c r="J112" s="23"/>
+      <c r="K112" s="23"/>
+    </row>
+    <row r="113" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F113" s="15">
+        <v>1</v>
+      </c>
+      <c r="G113" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H113" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J113" s="15"/>
+      <c r="K113" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="B114" s="22"/>
+      <c r="C114" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="D114" s="23"/>
+      <c r="E114" s="23"/>
+      <c r="F114" s="23"/>
+      <c r="G114" s="23"/>
+      <c r="H114" s="23"/>
+      <c r="I114" s="23"/>
+      <c r="J114" s="23"/>
+      <c r="K114" s="23"/>
+    </row>
+    <row r="115" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F115" s="15">
+        <v>1</v>
+      </c>
+      <c r="G115" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H115" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I115" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J115" s="15"/>
+      <c r="K115" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="24" t="s">
         <v>497</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B116" s="22"/>
+      <c r="C116" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="D116" s="23"/>
+      <c r="E116" s="23"/>
+      <c r="F116" s="23"/>
+      <c r="G116" s="23"/>
+      <c r="H116" s="23"/>
+      <c r="I116" s="23"/>
+      <c r="J116" s="23"/>
+      <c r="K116" s="23"/>
+    </row>
+    <row r="117" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="B117" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C117" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="D91" s="15" t="s">
+      <c r="D117" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="E91" s="15" t="s">
+      <c r="E117" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117" s="15">
+        <v>1</v>
+      </c>
+      <c r="G117" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H117" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I117" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J117" s="15"/>
+      <c r="K117" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="B118" s="22"/>
+      <c r="C118" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="D118" s="23"/>
+      <c r="E118" s="23"/>
+      <c r="F118" s="23"/>
+      <c r="G118" s="23"/>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="23"/>
+      <c r="K118" s="23"/>
+    </row>
+    <row r="119" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="E119" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F119" s="15">
+        <v>2</v>
+      </c>
+      <c r="G119" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="H119" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I119" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J119" s="15"/>
+      <c r="K119" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C120" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="E120" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="F91" s="15">
+      <c r="F120" s="15">
         <v>2</v>
       </c>
-      <c r="G91" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H91" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="I91" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="J91" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="K91" s="15" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="21" t="s">
-        <v>502</v>
-      </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
+      <c r="G120" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H120" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I120" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J120" s="15"/>
+      <c r="K120" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="B121" s="22"/>
+      <c r="C121" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="D121" s="23"/>
+      <c r="E121" s="23"/>
+      <c r="F121" s="23"/>
+      <c r="G121" s="23"/>
+      <c r="H121" s="23"/>
+      <c r="I121" s="23"/>
+      <c r="J121" s="23"/>
+      <c r="K121" s="23"/>
+    </row>
+    <row r="122" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="E122" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F122" s="15">
+        <v>2</v>
+      </c>
+      <c r="G122" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H122" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I122" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J122" s="15"/>
+      <c r="K122" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="B123" s="22"/>
+      <c r="C123" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="D123" s="23"/>
+      <c r="E123" s="23"/>
+      <c r="F123" s="23"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="23"/>
+      <c r="I123" s="23"/>
+      <c r="J123" s="23"/>
+      <c r="K123" s="23"/>
+    </row>
+    <row r="124" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="E124" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F124" s="15">
+        <v>1</v>
+      </c>
+      <c r="G124" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H124" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I124" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J124" s="15"/>
+      <c r="K124" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="B125" s="22"/>
+      <c r="C125" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="D125" s="23"/>
+      <c r="E125" s="23"/>
+      <c r="F125" s="23"/>
+      <c r="G125" s="23"/>
+      <c r="H125" s="23"/>
+      <c r="I125" s="23"/>
+      <c r="J125" s="23"/>
+      <c r="K125" s="23"/>
+    </row>
+    <row r="126" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F126" s="15">
+        <v>2</v>
+      </c>
+      <c r="G126" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H126" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I126" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J126" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="K126" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="21" t="s">
+        <v>522</v>
+      </c>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{212957B2-3366-4C00-BC1C-7A7F483E834E}"/>
-  <mergeCells count="2">
+  <autoFilter ref="A3:K3" xr:uid="{F7ADAC8F-C4B3-41C5-9D53-D92AC1084FA5}"/>
+  <mergeCells count="37">
+    <mergeCell ref="A128:K128"/>
+    <mergeCell ref="C114:K114"/>
+    <mergeCell ref="C116:K116"/>
+    <mergeCell ref="C118:K118"/>
+    <mergeCell ref="C121:K121"/>
+    <mergeCell ref="C123:K123"/>
+    <mergeCell ref="C125:K125"/>
+    <mergeCell ref="C101:K101"/>
+    <mergeCell ref="C103:K103"/>
+    <mergeCell ref="C105:K105"/>
+    <mergeCell ref="C108:K108"/>
+    <mergeCell ref="C110:K110"/>
+    <mergeCell ref="C112:K112"/>
+    <mergeCell ref="C84:K84"/>
+    <mergeCell ref="C86:K86"/>
+    <mergeCell ref="C88:K88"/>
+    <mergeCell ref="C93:K93"/>
+    <mergeCell ref="C96:K96"/>
+    <mergeCell ref="C99:K99"/>
+    <mergeCell ref="C68:K68"/>
+    <mergeCell ref="C71:K71"/>
+    <mergeCell ref="C74:K74"/>
+    <mergeCell ref="C76:K76"/>
+    <mergeCell ref="C78:K78"/>
+    <mergeCell ref="C81:K81"/>
+    <mergeCell ref="C32:K32"/>
+    <mergeCell ref="C40:K40"/>
+    <mergeCell ref="C49:K49"/>
+    <mergeCell ref="C56:K56"/>
+    <mergeCell ref="C61:K61"/>
+    <mergeCell ref="C65:K65"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A93:K93"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C24:K24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937856B8-291B-4ACD-B2C9-46CFAF4660FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1928F7B-93B7-48AB-89F7-193741E7B494}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6873,7 +7594,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{937856B8-291B-4ACD-B2C9-46CFAF4660FE}"/>
+  <autoFilter ref="A3:E3" xr:uid="{E1928F7B-93B7-48AB-89F7-193741E7B494}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -6882,7 +7603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF327DC-5CE6-4792-8200-F73E7EDB480B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454A19A1-4E37-452A-8B0D-2D95EBA82AB0}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7088,7 +7809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C61CA53-3AC6-45C8-86E2-BC529700CCD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE89C8D9-9235-4708-9AEE-C1CF019077B1}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7099,11 +7820,11 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
-      <c r="D1" s="22"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -7112,121 +7833,121 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>508</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>509</v>
+        <v>527</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>511</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>512</v>
+        <v>530</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>531</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>514</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>515</v>
+        <v>533</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>534</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>517</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>518</v>
+        <v>536</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>520</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>521</v>
+        <v>539</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>523</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>524</v>
+        <v>542</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>543</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>526</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>527</v>
+        <v>545</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>546</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>529</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>530</v>
+        <v>548</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>549</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>532</v>
+      <c r="B14" s="28" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B15" s="9">
         <v>30</v>
@@ -7234,7 +7955,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" s="9">
         <v>56</v>
@@ -7242,7 +7963,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B17" s="9">
         <v>2</v>
@@ -7250,153 +7971,153 @@
     </row>
     <row r="28" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -7411,7 +8132,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF3F253D-849E-4527-9BA7-B951D8E7521D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CBCFC4F-1F9E-4F5E-A5C8-CB0CC1652917}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7939,7 +8660,7 @@
       <c r="G25" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{FF3F253D-849E-4527-9BA7-B951D8E7521D}"/>
+  <autoFilter ref="A3:G3" xr:uid="{1CBCFC4F-1F9E-4F5E-A5C8-CB0CC1652917}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A25:G25"/>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C30B0E-B21A-4E5F-B9B6-82117F53497E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74D2DBD9-2160-4AFE-99A1-1A04A938936E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{C843DDEC-7FC3-42E3-8056-764180141529}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{5FF0A2E3-D62D-4FC9-AC61-E6D22B7FCF7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="591">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -760,7 +760,7 @@
     <t>Autonome</t>
   </si>
   <si>
-    <t>Garde horaire interne comme ECFJVTSV</t>
+    <t>Garde horaire interne comme ECFJALRVT1</t>
   </si>
   <si>
     <t>Detection de conflits d'agenda</t>
@@ -871,7 +871,7 @@
     <t>Lineaire (detection - relance - rapport)</t>
   </si>
   <si>
-    <t>ECFCCRRL1 deja construit (meme patron que le TFJ Ventes)</t>
+    <t>ECFCRELCR1 deja construit (meme patron que le TFJ Ventes)</t>
   </si>
   <si>
     <t>Score de qualification automatique</t>
@@ -925,7 +925,7 @@
     <t>Lineaire strict</t>
   </si>
   <si>
-    <t>ECFCVTRL-&gt;NT-&gt;RP</t>
+    <t>ECFCRELVT1 -&gt; ECFCVTNT -&gt; ECFCCLOVT1</t>
   </si>
   <si>
     <t>Suivi intraday des devis envoyes</t>
@@ -934,6 +934,9 @@
     <t>Pendant la journee on surveille si un devis envoye reste sans reponse trop longtemps pour relancer vite pendant que le client y pense encore</t>
   </si>
   <si>
+    <t>ECFJALRVT1</t>
+  </si>
+  <si>
     <t>Cloture commerciale mensuelle (objectifs-commissions)</t>
   </si>
   <si>
@@ -943,7 +946,7 @@
     <t>Lineaire (consolidation - calcul commissions - validation - verrouillage - rapport)</t>
   </si>
   <si>
-    <t>ECFCVTEM1 deja construit (version simplifiee : CA et repartition par commercial - sans verrouillage de periode)</t>
+    <t>ECFCCLOVT2 deja construit (version simplifiee : CA et repartition par commercial - sans verrouillage de periode)</t>
   </si>
   <si>
     <t>Cloture quotidienne TFJ Ventes (doit avoir tourne chaque jour du mois)</t>
@@ -973,6 +976,9 @@
     <t>Chaque soir a heure fixe on bascule officiellement la date comptable au jour suivant - comme tourner la page du registre</t>
   </si>
   <si>
+    <t>ECFCCLOCP1</t>
+  </si>
+  <si>
     <t>Reconciliation bancaire quotidienne</t>
   </si>
   <si>
@@ -994,7 +1000,7 @@
     <t>Lineaire (detection - relance)</t>
   </si>
   <si>
-    <t>ECFCCPFI1 deja construit (detection et rapport - relance email non automatisee - meme choix que ECFCVTRL cote Ventes)</t>
+    <t>ECFCRELCP1 deja construit (detection et rapport - relance email non automatisee - meme choix que ECFCRELVT1 cote Ventes)</t>
   </si>
   <si>
     <t>Generation de releves de compte PDF volumineux</t>
@@ -1036,7 +1042,7 @@
     <t>Lineaire (verif soldes - lettrage auto - provisions - balance - validation - verrouillage periode - export - notification - archivage)</t>
   </si>
   <si>
-    <t>ECFCCPEM1 deja construit (version simplifiee : CA facture/encaisse/balance agee - sans provisions ni verrouillage de periode)</t>
+    <t>ECFCCLOCP2 deja construit (version simplifiee : CA facture/encaisse/balance agee - sans provisions ni verrouillage de periode)</t>
   </si>
   <si>
     <t>Reconciliation bancaire quotidienne + Marqueur EOD (chaque jour du mois)</t>
@@ -1129,7 +1135,7 @@
     <t>On surveille en continu si un produit tombe en rupture de stock pour alerter vite</t>
   </si>
   <si>
-    <t>ECFJSTRU deja construit</t>
+    <t>ECFJALRST1 deja construit</t>
   </si>
   <si>
     <t>Valorisation nocturne du stock</t>
@@ -1237,7 +1243,7 @@
     <t>Lineaire (comptage - rapprochement - ecarts - validation)</t>
   </si>
   <si>
-    <t>ECFCPSCX1 deja construit (rapport de synthese par session - le rapprochement especes/carte physique reste fait par Odoo lui-meme a la fermeture de session)</t>
+    <t>ECFCCLOPS1 deja construit (rapport de synthese par session - le rapprochement especes/carte physique reste fait par Odoo lui-meme a la fermeture de session)</t>
   </si>
   <si>
     <t>Rapport ventes mensuel par point de vente</t>
@@ -1363,7 +1369,7 @@
     <t>Lineaire (detection - alerte)</t>
   </si>
   <si>
-    <t>ECFCRHFC1 deja construit</t>
+    <t>ECFCALRRH1 deja construit</t>
   </si>
   <si>
     <t>Processus de sortie (offboarding)</t>
@@ -2194,7 +2200,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-288E-4214-86DE-4CAF5592C1BF}"/>
+              <c16:uniqueId val="{00000000-BDBB-4559-A8D0-940529E41D84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2307,7 +2313,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-288E-4214-86DE-4CAF5592C1BF}"/>
+              <c16:uniqueId val="{00000002-BDBB-4559-A8D0-940529E41D84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2420,7 +2426,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-288E-4214-86DE-4CAF5592C1BF}"/>
+              <c16:uniqueId val="{00000003-BDBB-4559-A8D0-940529E41D84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3097,7 +3103,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8719C1A-B0B3-4789-8A08-500876D46068}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA5D2A91-2795-4F8F-B812-158618510B19}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3414,7 +3420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C70B66-E20C-4DC8-9E1E-71C29153BD0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA3A266-F89F-4F14-AA83-40942C948E58}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3603,7 +3609,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7ADAC8F-C4B3-41C5-9D53-D92AC1084FA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E15E1F3-362E-4514-B137-131D17BF05EF}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -4744,7 +4750,7 @@
         <v>191</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>108</v>
+        <v>296</v>
       </c>
       <c r="K37" s="14" t="s">
         <v>193</v>
@@ -4758,10 +4764,10 @@
         <v>130</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>32</v>
@@ -4770,7 +4776,7 @@
         <v>5</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H38" s="14" t="s">
         <v>190</v>
@@ -4779,10 +4785,10 @@
         <v>191</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -4793,10 +4799,10 @@
         <v>130</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E39" s="15" t="s">
         <v>37</v>
@@ -4815,16 +4821,16 @@
       </c>
       <c r="J39" s="15"/>
       <c r="K39" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="25" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="23"/>
@@ -4837,16 +4843,16 @@
     </row>
     <row r="41" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>22</v>
@@ -4864,7 +4870,7 @@
         <v>191</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>99</v>
+        <v>310</v>
       </c>
       <c r="K41" s="14" t="s">
         <v>193</v>
@@ -4872,16 +4878,16 @@
     </row>
     <row r="42" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>17</v>
@@ -4890,7 +4896,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H42" s="14" t="s">
         <v>190</v>
@@ -4899,24 +4905,24 @@
         <v>191</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K42" s="14" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="172.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>17</v>
@@ -4925,7 +4931,7 @@
         <v>2</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H43" s="14" t="s">
         <v>190</v>
@@ -4934,7 +4940,7 @@
         <v>191</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K43" s="14" t="s">
         <v>193</v>
@@ -4942,25 +4948,25 @@
     </row>
     <row r="44" spans="1:11" ht="132.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F44" s="15">
         <v>2</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>205</v>
@@ -4969,7 +4975,7 @@
         <v>206</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K44" s="15" t="s">
         <v>193</v>
@@ -4977,25 +4983,25 @@
     </row>
     <row r="45" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F45" s="15">
         <v>3</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>205</v>
@@ -5004,7 +5010,7 @@
         <v>206</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K45" s="15" t="s">
         <v>193</v>
@@ -5012,16 +5018,16 @@
     </row>
     <row r="46" spans="1:11" ht="211.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E46" s="14" t="s">
         <v>32</v>
@@ -5030,7 +5036,7 @@
         <v>9</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H46" s="14" t="s">
         <v>190</v>
@@ -5039,24 +5045,24 @@
         <v>191</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="132.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>37</v>
@@ -5065,7 +5071,7 @@
         <v>6</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>190</v>
@@ -5074,24 +5080,24 @@
         <v>191</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="225" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>42</v>
@@ -5100,7 +5106,7 @@
         <v>12</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H48" s="15" t="s">
         <v>205</v>
@@ -5109,19 +5115,19 @@
         <v>206</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B49" s="22"/>
       <c r="C49" s="25" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="23"/>
@@ -5134,16 +5140,16 @@
     </row>
     <row r="50" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>70</v>
@@ -5169,7 +5175,7 @@
     </row>
     <row r="51" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>140</v>
@@ -5178,7 +5184,7 @@
         <v>286</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>70</v>
@@ -5204,7 +5210,7 @@
     </row>
     <row r="52" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>140</v>
@@ -5213,7 +5219,7 @@
         <v>145</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>70</v>
@@ -5239,16 +5245,16 @@
     </row>
     <row r="53" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>47</v>
@@ -5274,16 +5280,16 @@
     </row>
     <row r="54" spans="1:11" ht="172.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>17</v>
@@ -5292,7 +5298,7 @@
         <v>4</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H54" s="14" t="s">
         <v>190</v>
@@ -5301,7 +5307,7 @@
         <v>191</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K54" s="14" t="s">
         <v>193</v>
@@ -5309,16 +5315,16 @@
     </row>
     <row r="55" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>140</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>32</v>
@@ -5337,16 +5343,16 @@
       </c>
       <c r="J55" s="15"/>
       <c r="K55" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="24" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B56" s="22"/>
       <c r="C56" s="25" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="23"/>
@@ -5359,16 +5365,16 @@
     </row>
     <row r="57" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>147</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>226</v>
@@ -5386,7 +5392,7 @@
         <v>191</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K57" s="14" t="s">
         <v>193</v>
@@ -5394,16 +5400,16 @@
     </row>
     <row r="58" spans="1:11" ht="185.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>147</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>17</v>
@@ -5412,7 +5418,7 @@
         <v>6</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H58" s="14" t="s">
         <v>190</v>
@@ -5421,7 +5427,7 @@
         <v>191</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K58" s="14" t="s">
         <v>193</v>
@@ -5429,16 +5435,16 @@
     </row>
     <row r="59" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>32</v>
@@ -5457,21 +5463,21 @@
       </c>
       <c r="J59" s="15"/>
       <c r="K59" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>37</v>
@@ -5490,16 +5496,16 @@
       </c>
       <c r="J60" s="15"/>
       <c r="K60" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B61" s="22"/>
       <c r="C61" s="25" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D61" s="23"/>
       <c r="E61" s="23"/>
@@ -5512,25 +5518,25 @@
     </row>
     <row r="62" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F62" s="15">
         <v>3</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H62" s="15" t="s">
         <v>205</v>
@@ -5545,16 +5551,16 @@
     </row>
     <row r="63" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>17</v>
@@ -5578,16 +5584,16 @@
     </row>
     <row r="64" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>152</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>32</v>
@@ -5611,11 +5617,11 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B65" s="22"/>
       <c r="C65" s="25" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D65" s="23"/>
       <c r="E65" s="23"/>
@@ -5628,16 +5634,16 @@
     </row>
     <row r="66" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>107</v>
@@ -5661,16 +5667,16 @@
     </row>
     <row r="67" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>155</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>17</v>
@@ -5694,11 +5700,11 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="24" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B68" s="22"/>
       <c r="C68" s="25" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D68" s="23"/>
       <c r="E68" s="23"/>
@@ -5711,16 +5717,16 @@
     </row>
     <row r="69" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E69" s="15" t="s">
         <v>256</v>
@@ -5744,16 +5750,16 @@
     </row>
     <row r="70" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>32</v>
@@ -5777,11 +5783,11 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B71" s="22"/>
       <c r="C71" s="25" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D71" s="23"/>
       <c r="E71" s="23"/>
@@ -5794,16 +5800,16 @@
     </row>
     <row r="72" spans="1:11" ht="198.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>161</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>17</v>
@@ -5812,7 +5818,7 @@
         <v>4</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H72" s="14" t="s">
         <v>190</v>
@@ -5821,7 +5827,7 @@
         <v>191</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K72" s="14" t="s">
         <v>193</v>
@@ -5829,16 +5835,16 @@
     </row>
     <row r="73" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B73" s="9" t="s">
         <v>161</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E73" s="15" t="s">
         <v>32</v>
@@ -5862,11 +5868,11 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B74" s="22"/>
       <c r="C74" s="25" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="23"/>
@@ -5879,16 +5885,16 @@
     </row>
     <row r="75" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B75" s="9" t="s">
         <v>164</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E75" s="15" t="s">
         <v>17</v>
@@ -5912,11 +5918,11 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B76" s="22"/>
       <c r="C76" s="25" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="23"/>
@@ -5929,16 +5935,16 @@
     </row>
     <row r="77" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E77" s="15" t="s">
         <v>27</v>
@@ -5962,11 +5968,11 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B78" s="22"/>
       <c r="C78" s="25" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
@@ -5979,16 +5985,16 @@
     </row>
     <row r="79" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E79" s="15" t="s">
         <v>17</v>
@@ -6012,16 +6018,16 @@
     </row>
     <row r="80" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E80" s="15" t="s">
         <v>107</v>
@@ -6030,7 +6036,7 @@
         <v>2</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H80" s="15" t="s">
         <v>205</v>
@@ -6045,11 +6051,11 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B81" s="22"/>
       <c r="C81" s="25" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D81" s="23"/>
       <c r="E81" s="23"/>
@@ -6062,16 +6068,16 @@
     </row>
     <row r="82" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E82" s="15" t="s">
         <v>256</v>
@@ -6095,16 +6101,16 @@
     </row>
     <row r="83" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E83" s="15" t="s">
         <v>32</v>
@@ -6128,11 +6134,11 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B84" s="22"/>
       <c r="C84" s="25" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
@@ -6145,16 +6151,16 @@
     </row>
     <row r="85" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>32</v>
@@ -6178,11 +6184,11 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B86" s="22"/>
       <c r="C86" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
@@ -6195,16 +6201,16 @@
     </row>
     <row r="87" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E87" s="15" t="s">
         <v>256</v>
@@ -6228,11 +6234,11 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="24" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B88" s="22"/>
       <c r="C88" s="25" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D88" s="23"/>
       <c r="E88" s="23"/>
@@ -6245,16 +6251,16 @@
     </row>
     <row r="89" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E89" s="15" t="s">
         <v>32</v>
@@ -6278,16 +6284,16 @@
     </row>
     <row r="90" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E90" s="15" t="s">
         <v>42</v>
@@ -6306,21 +6312,21 @@
       </c>
       <c r="J90" s="15"/>
       <c r="K90" s="15" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="277.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E91" s="14" t="s">
         <v>17</v>
@@ -6329,7 +6335,7 @@
         <v>2</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H91" s="14" t="s">
         <v>190</v>
@@ -6338,7 +6344,7 @@
         <v>191</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K91" s="14" t="s">
         <v>193</v>
@@ -6346,16 +6352,16 @@
     </row>
     <row r="92" spans="1:11" ht="225" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E92" s="15" t="s">
         <v>70</v>
@@ -6364,7 +6370,7 @@
         <v>3</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H92" s="15" t="s">
         <v>205</v>
@@ -6373,19 +6379,19 @@
         <v>206</v>
       </c>
       <c r="J92" s="15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B93" s="22"/>
       <c r="C93" s="25" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D93" s="23"/>
       <c r="E93" s="23"/>
@@ -6398,16 +6404,16 @@
     </row>
     <row r="94" spans="1:11" ht="66.599999999999994" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E94" s="15" t="s">
         <v>17</v>
@@ -6431,16 +6437,16 @@
     </row>
     <row r="95" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E95" s="14" t="s">
         <v>32</v>
@@ -6449,7 +6455,7 @@
         <v>4</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H95" s="14" t="s">
         <v>190</v>
@@ -6458,19 +6464,19 @@
         <v>191</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B96" s="22"/>
       <c r="C96" s="25" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
@@ -6483,16 +6489,16 @@
     </row>
     <row r="97" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E97" s="15" t="s">
         <v>107</v>
@@ -6516,16 +6522,16 @@
     </row>
     <row r="98" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E98" s="15" t="s">
         <v>42</v>
@@ -6549,11 +6555,11 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B99" s="22"/>
       <c r="C99" s="25" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23"/>
@@ -6566,16 +6572,16 @@
     </row>
     <row r="100" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E100" s="15" t="s">
         <v>32</v>
@@ -6599,11 +6605,11 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B101" s="22"/>
       <c r="C101" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D101" s="23"/>
       <c r="E101" s="23"/>
@@ -6616,16 +6622,16 @@
     </row>
     <row r="102" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E102" s="15" t="s">
         <v>17</v>
@@ -6649,11 +6655,11 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B103" s="22"/>
       <c r="C103" s="25" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D103" s="23"/>
       <c r="E103" s="23"/>
@@ -6666,16 +6672,16 @@
     </row>
     <row r="104" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E104" s="15" t="s">
         <v>32</v>
@@ -6699,11 +6705,11 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="24" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B105" s="22"/>
       <c r="C105" s="25" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D105" s="23"/>
       <c r="E105" s="23"/>
@@ -6716,16 +6722,16 @@
     </row>
     <row r="106" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E106" s="15" t="s">
         <v>17</v>
@@ -6749,16 +6755,16 @@
     </row>
     <row r="107" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>32</v>
@@ -6776,7 +6782,7 @@
         <v>191</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K107" s="14" t="s">
         <v>193</v>
@@ -6784,11 +6790,11 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="24" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B108" s="22"/>
       <c r="C108" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
@@ -6801,16 +6807,16 @@
     </row>
     <row r="109" spans="1:11" ht="79.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E109" s="15" t="s">
         <v>107</v>
@@ -6834,11 +6840,11 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B110" s="22"/>
       <c r="C110" s="25" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D110" s="23"/>
       <c r="E110" s="23"/>
@@ -6851,16 +6857,16 @@
     </row>
     <row r="111" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E111" s="15" t="s">
         <v>32</v>
@@ -6884,11 +6890,11 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="24" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D112" s="23"/>
       <c r="E112" s="23"/>
@@ -6901,16 +6907,16 @@
     </row>
     <row r="113" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A113" s="9" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E113" s="15" t="s">
         <v>70</v>
@@ -6934,11 +6940,11 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="24" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B114" s="22"/>
       <c r="C114" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D114" s="23"/>
       <c r="E114" s="23"/>
@@ -6951,16 +6957,16 @@
     </row>
     <row r="115" spans="1:11" ht="145.80000000000001" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E115" s="15" t="s">
         <v>47</v>
@@ -6984,11 +6990,11 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="24" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B116" s="22"/>
       <c r="C116" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D116" s="23"/>
       <c r="E116" s="23"/>
@@ -7001,16 +7007,16 @@
     </row>
     <row r="117" spans="1:11" ht="106.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A117" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>27</v>
@@ -7034,11 +7040,11 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="24" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B118" s="22"/>
       <c r="C118" s="25" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D118" s="23"/>
       <c r="E118" s="23"/>
@@ -7051,16 +7057,16 @@
     </row>
     <row r="119" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E119" s="15" t="s">
         <v>107</v>
@@ -7069,7 +7075,7 @@
         <v>2</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H119" s="15" t="s">
         <v>205</v>
@@ -7084,16 +7090,16 @@
     </row>
     <row r="120" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A120" s="9" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>32</v>
@@ -7117,11 +7123,11 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B121" s="22"/>
       <c r="C121" s="25" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D121" s="23"/>
       <c r="E121" s="23"/>
@@ -7134,16 +7140,16 @@
     </row>
     <row r="122" spans="1:11" ht="93" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E122" s="15" t="s">
         <v>107</v>
@@ -7167,11 +7173,11 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="24" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B123" s="22"/>
       <c r="C123" s="25" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D123" s="23"/>
       <c r="E123" s="23"/>
@@ -7184,16 +7190,16 @@
     </row>
     <row r="124" spans="1:11" ht="119.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E124" s="15" t="s">
         <v>27</v>
@@ -7217,11 +7223,11 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="24" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B125" s="22"/>
       <c r="C125" s="25" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D125" s="23"/>
       <c r="E125" s="23"/>
@@ -7234,16 +7240,16 @@
     </row>
     <row r="126" spans="1:11" ht="159" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E126" s="15" t="s">
         <v>32</v>
@@ -7261,7 +7267,7 @@
         <v>228</v>
       </c>
       <c r="J126" s="15" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K126" s="15" t="s">
         <v>193</v>
@@ -7269,7 +7275,7 @@
     </row>
     <row r="128" spans="1:11" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="21" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -7283,7 +7289,7 @@
       <c r="K128" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{F7ADAC8F-C4B3-41C5-9D53-D92AC1084FA5}"/>
+  <autoFilter ref="A3:K3" xr:uid="{2E15E1F3-362E-4514-B137-131D17BF05EF}"/>
   <mergeCells count="37">
     <mergeCell ref="A128:K128"/>
     <mergeCell ref="C114:K114"/>
@@ -7328,7 +7334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1928F7B-93B7-48AB-89F7-193741E7B494}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27130E95-0811-4A0B-A01B-CAF6D9C8D224}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7594,7 +7600,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{E1928F7B-93B7-48AB-89F7-193741E7B494}"/>
+  <autoFilter ref="A3:E3" xr:uid="{27130E95-0811-4A0B-A01B-CAF6D9C8D224}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -7603,7 +7609,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454A19A1-4E37-452A-8B0D-2D95EBA82AB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0CE624-02A4-4A49-BA11-9CC2BF6D3829}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7809,7 +7815,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE89C8D9-9235-4708-9AEE-C1CF019077B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C044133-EC9A-474B-9594-6BDAFD92E6A6}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7820,7 +7826,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -7833,106 +7839,106 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -7942,7 +7948,7 @@
         <v>180</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -7971,153 +7977,153 @@
     </row>
     <row r="28" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -8132,7 +8138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CBCFC4F-1F9E-4F5E-A5C8-CB0CC1652917}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98C3FB85-BA0C-4991-974E-308CF7363756}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8660,7 +8666,7 @@
       <c r="G25" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{1CBCFC4F-1F9E-4F5E-A5C8-CB0CC1652917}"/>
+  <autoFilter ref="A3:G3" xr:uid="{98C3FB85-BA0C-4991-974E-308CF7363756}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A25:G25"/>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74D2DBD9-2160-4AFE-99A1-1A04A938936E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AB24D01-363C-4578-A742-ED10BD157361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{5FF0A2E3-D62D-4FC9-AC61-E6D22B7FCF7A}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{03B8B241-4607-456B-A423-362F3C32F81C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
     <sheet name="Catalogue des operations" sheetId="5" r:id="rId2"/>
-    <sheet name="Taxonomie complete" sheetId="2" r:id="rId3"/>
-    <sheet name="Cycles reels construits" sheetId="3" r:id="rId4"/>
-    <sheet name="Exploitation MCO - efficacite" sheetId="6" r:id="rId5"/>
-    <sheet name="Scenario 50 traitements" sheetId="4" r:id="rId6"/>
+    <sheet name="Operations par type traitement" sheetId="6" r:id="rId3"/>
+    <sheet name="Taxonomie complete" sheetId="2" r:id="rId4"/>
+    <sheet name="Cycles reels construits" sheetId="3" r:id="rId5"/>
+    <sheet name="Exploitation MCO - efficacite" sheetId="7" r:id="rId6"/>
+    <sheet name="Scenario 50 traitements" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Catalogue des operations'!$A$3:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Scenario 50 traitements'!$A$3:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Taxonomie complete'!$A$3:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Operations par type traitement'!$A$3:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Scenario 50 traitements'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Taxonomie complete'!$A$3:$E$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="607">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -1619,6 +1621,54 @@
   </si>
   <si>
     <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 30 operations deja CONSTRUITES ET VERIFIEES (vert), 0 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
+  </si>
+  <si>
+    <t>Memes 88 operations, groupees par type de traitement (TFJ/EOM/ON_DEMAND/...) - pour repondre a 'combien d'operations TFJ au total ?'</t>
+  </si>
+  <si>
+    <t>20 operations - 4 construite(s) - 59 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>15 operations - 8 construite(s) - 46 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>14 operations - 11 construite(s) - 38 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>10 operations - 2 construite(s) - 14 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>5 operations - 0 construite(s) - 9 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>4 operations - 0 construite(s) - 5 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>4 operations - 1 construite(s) - 9 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>4 operations - 0 construite(s) - 21 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>3 operations - 1 construite(s) - 13 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>2 operations - 0 construite(s) - 6 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>2 operations - 1 construite(s) - 2 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>1 operation - 0 construite(s) - 2 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>1 operation - 0 construite(s) - 6 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>1 operation - 0 construite(s) - 1 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>1 operation - 1 construite(s) - 1 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t>Maintien en condition operationnelle - preuves d'efficacite reelles</t>
@@ -2200,7 +2250,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BDBB-4559-A8D0-940529E41D84}"/>
+              <c16:uniqueId val="{00000000-1B25-465B-B328-6C6F1E9EC643}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2313,7 +2363,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-BDBB-4559-A8D0-940529E41D84}"/>
+              <c16:uniqueId val="{00000002-1B25-465B-B328-6C6F1E9EC643}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2426,7 +2476,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BDBB-4559-A8D0-940529E41D84}"/>
+              <c16:uniqueId val="{00000003-1B25-465B-B328-6C6F1E9EC643}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3103,7 +3153,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA5D2A91-2795-4F8F-B812-158618510B19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77622F8B-2DE7-4D72-A27C-08C704AAA420}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3420,7 +3470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA3A266-F89F-4F14-AA83-40942C948E58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83412779-CC28-47E7-9A4C-5D35CBDAC71D}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3609,7 +3659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E15E1F3-362E-4514-B137-131D17BF05EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D4FF926-5CAC-497A-8E37-6D37AAC9CEF4}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -7289,7 +7339,7 @@
       <c r="K128" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{2E15E1F3-362E-4514-B137-131D17BF05EF}"/>
+  <autoFilter ref="A3:K3" xr:uid="{6D4FF926-5CAC-497A-8E37-6D37AAC9CEF4}"/>
   <mergeCells count="37">
     <mergeCell ref="A128:K128"/>
     <mergeCell ref="C114:K114"/>
@@ -7334,7 +7384,3374 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27130E95-0811-4A0B-A01B-CAF6D9C8D224}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3B3E0A-BA90-4939-991F-4C9A794F6191}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:K107"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" customWidth="1"/>
+    <col min="4" max="4" width="55.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="40.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" customWidth="1"/>
+    <col min="10" max="10" width="35.77734375" customWidth="1"/>
+    <col min="11" max="11" width="40.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="15">
+        <v>4</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="79.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="15">
+        <v>1</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="15">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="14">
+        <v>5</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="211.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="14">
+        <v>9</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="15">
+        <v>3</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="79.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="15">
+        <v>5</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="15">
+        <v>2</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="79.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="15">
+        <v>2</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="15">
+        <v>3</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="15">
+        <v>2</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="15">
+        <v>2</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="14">
+        <v>4</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="15">
+        <v>3</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="15">
+        <v>2</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="14">
+        <v>3</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="15">
+        <v>2</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+    </row>
+    <row r="26" spans="1:11" ht="172.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="14">
+        <v>3</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="172.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="172.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="14">
+        <v>4</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="185.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="14">
+        <v>6</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="15">
+        <v>4</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="79.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="15">
+        <v>2</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="198.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="14">
+        <v>4</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="15">
+        <v>3</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="15">
+        <v>3</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="277.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="14">
+        <v>2</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="15">
+        <v>2</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="15">
+        <v>1</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="15">
+        <v>2</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+    </row>
+    <row r="42" spans="1:11" ht="211.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="14">
+        <v>20</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" s="15">
+        <v>3</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" s="14">
+        <v>1</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="185.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F45" s="14">
+        <v>1</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" s="14">
+        <v>1</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="132.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" s="14">
+        <v>2</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F48" s="14">
+        <v>1</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F49" s="14">
+        <v>1</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J49" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="14">
+        <v>1</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F51" s="14">
+        <v>1</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F52" s="14">
+        <v>1</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="14">
+        <v>1</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J53" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="225" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F54" s="15">
+        <v>3</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="H54" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" s="15">
+        <v>1</v>
+      </c>
+      <c r="G55" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H55" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I55" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="22"/>
+      <c r="C56" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+    </row>
+    <row r="57" spans="1:11" ht="132.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F57" s="14">
+        <v>1</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F58" s="15">
+        <v>1</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F59" s="15">
+        <v>2</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="185.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F60" s="14">
+        <v>1</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J60" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F61" s="15">
+        <v>1</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F62" s="15">
+        <v>2</v>
+      </c>
+      <c r="G62" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F63" s="15">
+        <v>1</v>
+      </c>
+      <c r="G63" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I63" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="79.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F64" s="15">
+        <v>1</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F65" s="15">
+        <v>2</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I65" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F66" s="15">
+        <v>2</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I66" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B67" s="22"/>
+      <c r="C67" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+      <c r="I67" s="23"/>
+      <c r="J67" s="23"/>
+      <c r="K67" s="23"/>
+    </row>
+    <row r="68" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="15">
+        <v>2</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="172.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="15">
+        <v>3</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I69" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="15">
+        <v>2</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I70" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="15">
+        <v>1</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="15">
+        <v>1</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B73" s="22"/>
+      <c r="C73" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="D73" s="23"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="23"/>
+      <c r="I73" s="23"/>
+      <c r="J73" s="23"/>
+      <c r="K73" s="23"/>
+    </row>
+    <row r="74" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F74" s="15">
+        <v>2</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I74" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F75" s="15">
+        <v>1</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F76" s="15">
+        <v>1</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F77" s="15">
+        <v>1</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I77" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B78" s="22"/>
+      <c r="C78" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="D78" s="23"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
+      <c r="K78" s="23"/>
+    </row>
+    <row r="79" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F79" s="15">
+        <v>2</v>
+      </c>
+      <c r="G79" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H79" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I79" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="K79" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="132.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F80" s="15">
+        <v>3</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I80" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J80" s="15"/>
+      <c r="K80" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="185.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F81" s="15">
+        <v>2</v>
+      </c>
+      <c r="G81" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I81" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="93" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F82" s="14">
+        <v>2</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B83" s="22"/>
+      <c r="C83" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="23"/>
+      <c r="H83" s="23"/>
+      <c r="I83" s="23"/>
+      <c r="J83" s="23"/>
+      <c r="K83" s="23"/>
+    </row>
+    <row r="84" spans="1:11" ht="198.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" s="15">
+        <v>4</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="H84" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I84" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K84" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="225" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" s="15">
+        <v>12</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I85" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="79.8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" s="15">
+        <v>3</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I86" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J86" s="15"/>
+      <c r="K86" s="15" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" s="15">
+        <v>2</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I87" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" s="22"/>
+      <c r="C88" s="25" t="s">
+        <v>534</v>
+      </c>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="23"/>
+      <c r="K88" s="23"/>
+    </row>
+    <row r="89" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" s="15">
+        <v>4</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I89" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J89" s="15"/>
+      <c r="K89" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="132.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90" s="14">
+        <v>6</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I90" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="106.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F91" s="15">
+        <v>3</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H91" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I91" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B92" s="22"/>
+      <c r="C92" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
+      <c r="I92" s="23"/>
+      <c r="J92" s="23"/>
+      <c r="K92" s="23"/>
+    </row>
+    <row r="93" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="F93" s="15">
+        <v>3</v>
+      </c>
+      <c r="G93" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I93" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J93" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="K93" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="119.4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="F94" s="15">
+        <v>3</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I94" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B95" s="22"/>
+      <c r="C95" s="25" t="s">
+        <v>536</v>
+      </c>
+      <c r="D95" s="23"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="23"/>
+      <c r="H95" s="23"/>
+      <c r="I95" s="23"/>
+      <c r="J95" s="23"/>
+      <c r="K95" s="23"/>
+    </row>
+    <row r="96" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F96" s="14">
+        <v>1</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I96" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J96" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="K96" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" s="15">
+        <v>1</v>
+      </c>
+      <c r="G97" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I97" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="B98" s="22"/>
+      <c r="C98" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="D98" s="23"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="23"/>
+      <c r="G98" s="23"/>
+      <c r="H98" s="23"/>
+      <c r="I98" s="23"/>
+      <c r="J98" s="23"/>
+      <c r="K98" s="23"/>
+    </row>
+    <row r="99" spans="1:11" ht="132.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="F99" s="15">
+        <v>2</v>
+      </c>
+      <c r="G99" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="H99" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="I99" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="K99" s="15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B100" s="22"/>
+      <c r="C100" s="25" t="s">
+        <v>538</v>
+      </c>
+      <c r="D100" s="23"/>
+      <c r="E100" s="23"/>
+      <c r="F100" s="23"/>
+      <c r="G100" s="23"/>
+      <c r="H100" s="23"/>
+      <c r="I100" s="23"/>
+      <c r="J100" s="23"/>
+      <c r="K100" s="23"/>
+    </row>
+    <row r="101" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="E101" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F101" s="17">
+        <v>6</v>
+      </c>
+      <c r="G101" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="H101" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="I101" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="J101" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="K101" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102" s="22"/>
+      <c r="C102" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+    </row>
+    <row r="103" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="D103" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="E103" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F103" s="17">
+        <v>1</v>
+      </c>
+      <c r="G103" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H103" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="I103" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="J103" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B104" s="22"/>
+      <c r="C104" s="25" t="s">
+        <v>540</v>
+      </c>
+      <c r="D104" s="23"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="23"/>
+      <c r="G104" s="23"/>
+      <c r="H104" s="23"/>
+      <c r="I104" s="23"/>
+      <c r="J104" s="23"/>
+      <c r="K104" s="23"/>
+    </row>
+    <row r="105" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F105" s="14">
+        <v>1</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I105" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J105" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K105" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="22"/>
+      <c r="C106" s="25" t="s">
+        <v>540</v>
+      </c>
+      <c r="D106" s="23"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="23"/>
+      <c r="G106" s="23"/>
+      <c r="H106" s="23"/>
+      <c r="I106" s="23"/>
+      <c r="J106" s="23"/>
+      <c r="K106" s="23"/>
+    </row>
+    <row r="107" spans="1:11" ht="159" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F107" s="14">
+        <v>1</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I107" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="J107" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="K107" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:K3" xr:uid="{4D3B3E0A-BA90-4939-991F-4C9A794F6191}"/>
+  <mergeCells count="17">
+    <mergeCell ref="C98:K98"/>
+    <mergeCell ref="C100:K100"/>
+    <mergeCell ref="C102:K102"/>
+    <mergeCell ref="C104:K104"/>
+    <mergeCell ref="C106:K106"/>
+    <mergeCell ref="C73:K73"/>
+    <mergeCell ref="C78:K78"/>
+    <mergeCell ref="C83:K83"/>
+    <mergeCell ref="C88:K88"/>
+    <mergeCell ref="C92:K92"/>
+    <mergeCell ref="C95:K95"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="C41:K41"/>
+    <mergeCell ref="C56:K56"/>
+    <mergeCell ref="C67:K67"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EFFE12F-C7B1-4BC5-A174-5F3ED5AFF8E4}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7600,7 +11017,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{27130E95-0811-4A0B-A01B-CAF6D9C8D224}"/>
+  <autoFilter ref="A3:E3" xr:uid="{3EFFE12F-C7B1-4BC5-A174-5F3ED5AFF8E4}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -7608,8 +11025,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0CE624-02A4-4A49-BA11-9CC2BF6D3829}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9103D5F2-0E5E-48DC-B076-0498D1ABAC3E}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7814,8 +11231,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C044133-EC9A-474B-9594-6BDAFD92E6A6}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD161C2-1547-4072-8859-8A842F755591}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7826,7 +11243,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -7839,106 +11256,106 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>537</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>543</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -7948,7 +11365,7 @@
         <v>180</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -7977,153 +11394,153 @@
     </row>
     <row r="28" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>566</v>
+        <v>582</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>584</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>588</v>
+        <v>604</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -8137,8 +11554,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98C3FB85-BA0C-4991-974E-308CF7363756}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67772A58-931E-42F5-8F04-7CACE6B453D1}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8666,7 +12083,7 @@
       <c r="G25" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{98C3FB85-BA0C-4991-974E-308CF7363756}"/>
+  <autoFilter ref="A3:G3" xr:uid="{67772A58-931E-42F5-8F04-7CACE6B453D1}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A25:G25"/>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BAE00C4-5902-4B43-9E9F-01967A832E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34DE7E2-F58C-47CF-BB92-77740D68307E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{BE70FAC4-92D6-4206-B422-8A73B7504C4D}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{064D8D0D-B934-4A2C-A324-93FEC81DD467}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="676">
   <si>
     <t>Tableau de bord des cycles operatoires - ERP_CRM_FACTORY</t>
   </si>
@@ -879,7 +879,7 @@
     <t>CRM</t>
   </si>
   <si>
-    <t>7 operation(s) - 5 construite(s) - 13 jobs estimes</t>
+    <t>7 operation(s) - 7 construite(s) - 13 jobs estimes</t>
   </si>
   <si>
     <t>4 operations</t>
@@ -924,6 +924,9 @@
     <t>Lineaire (extraction - KPI - envoi)</t>
   </si>
   <si>
+    <t>ECFCCLOCR1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
     <t>Score de qualification automatique</t>
   </si>
   <si>
@@ -933,6 +936,9 @@
     <t>Lineaire (calcul - mise a jour)</t>
   </si>
   <si>
+    <t>ECFJSCORCR1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
     <t xml:space="preserve">   TFJ</t>
   </si>
   <si>
@@ -1266,108 +1272,132 @@
     <t>Reparation</t>
   </si>
   <si>
+    <t>2 operation(s) - 2 construite(s) - 3 jobs estimes</t>
+  </si>
+  <si>
+    <t>Rapport quotidien SAV</t>
+  </si>
+  <si>
+    <t>Chaque jour un point sur les reparations en cours et terminees</t>
+  </si>
+  <si>
+    <t>ECFCCLORP1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
+    <t>Notification avancement reparation</t>
+  </si>
+  <si>
+    <t>On previent le client quand sa reparation avance (prise en charge - terminee)</t>
+  </si>
+  <si>
+    <t>ECFJALRRP1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
+    <t>Flotte vehicules</t>
+  </si>
+  <si>
+    <t>Controle entretien mensuel</t>
+  </si>
+  <si>
+    <t>Une fois par mois verifier quels vehicules ont besoin d'entretien</t>
+  </si>
+  <si>
+    <t>ECFCCLOFL1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
+    <t>Alerte echeance assurance/controle technique</t>
+  </si>
+  <si>
+    <t>On previent avant qu'une assurance ou un controle technique n'expire</t>
+  </si>
+  <si>
+    <t>ECFCALRFL1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
+    <t>Point de vente</t>
+  </si>
+  <si>
+    <t>2 operation(s) - 2 construite(s) - 7 jobs estimes</t>
+  </si>
+  <si>
+    <t>Rapport ventes mensuel par point de vente</t>
+  </si>
+  <si>
+    <t>Une fois par mois le bilan des ventes par point de vente</t>
+  </si>
+  <si>
+    <t>ECFCCLOPS2 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
+    <t>Cloture de caisse quotidienne</t>
+  </si>
+  <si>
+    <t>Chaque soir on compte la caisse et on verifie qu'elle correspond a ce qui a ete encaisse dans la journee</t>
+  </si>
+  <si>
+    <t>Lineaire (comptage - rapprochement - ecarts - validation)</t>
+  </si>
+  <si>
+    <t>ECFCCLOPS1 deja construit (rapport de synthese par session - le rapprochement especes/carte physique reste fait par Odoo lui-meme a la fermeture de session)</t>
+  </si>
+  <si>
+    <t>POS Restaurant</t>
+  </si>
+  <si>
+    <t>1 operation(s) - 0 construite(s) - 3 jobs estimes</t>
+  </si>
+  <si>
+    <t>Cloture de service (midi/soir)</t>
+  </si>
+  <si>
+    <t>A la fin de chaque service on fait les comptes du service par table</t>
+  </si>
+  <si>
+    <t>Site web</t>
+  </si>
+  <si>
+    <t>1 operation(s) - 0 construite(s) - 2 jobs estimes</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>Verification liens morts et formulaires</t>
+  </si>
+  <si>
+    <t>Une fois par semaine on verifie que le site web n'a pas de liens casses ou de formulaires en panne</t>
+  </si>
+  <si>
+    <t>eCommerce</t>
+  </si>
+  <si>
+    <t>2 operation(s) - 2 construite(s) - 5 jobs estimes</t>
+  </si>
+  <si>
+    <t>Relance paniers abandonnes</t>
+  </si>
+  <si>
+    <t>On relance les clients qui ont rempli un panier en ligne sans finaliser leur achat</t>
+  </si>
+  <si>
+    <t>ECFJRELEC1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
+    <t>Rapport ventes en ligne et paniers abandonnes</t>
+  </si>
+  <si>
+    <t>Chaque jour un bilan des ventes du site et des paniers abandonnes en cours de commande</t>
+  </si>
+  <si>
+    <t>ECFCCLOEC1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
+    <t>Evenements</t>
+  </si>
+  <si>
     <t>2 operation(s) - 0 construite(s) - 3 jobs estimes</t>
   </si>
   <si>
-    <t>Rapport quotidien SAV</t>
-  </si>
-  <si>
-    <t>Chaque jour un point sur les reparations en cours et terminees</t>
-  </si>
-  <si>
-    <t>Notification avancement reparation</t>
-  </si>
-  <si>
-    <t>On previent le client quand sa reparation avance (prise en charge - terminee)</t>
-  </si>
-  <si>
-    <t>Flotte vehicules</t>
-  </si>
-  <si>
-    <t>Controle entretien mensuel</t>
-  </si>
-  <si>
-    <t>Une fois par mois verifier quels vehicules ont besoin d'entretien</t>
-  </si>
-  <si>
-    <t>Alerte echeance assurance/controle technique</t>
-  </si>
-  <si>
-    <t>On previent avant qu'une assurance ou un controle technique n'expire</t>
-  </si>
-  <si>
-    <t>Point de vente</t>
-  </si>
-  <si>
-    <t>2 operation(s) - 1 construite(s) - 7 jobs estimes</t>
-  </si>
-  <si>
-    <t>Rapport ventes mensuel par point de vente</t>
-  </si>
-  <si>
-    <t>Une fois par mois le bilan des ventes par point de vente</t>
-  </si>
-  <si>
-    <t>Cloture de caisse quotidienne</t>
-  </si>
-  <si>
-    <t>Chaque soir on compte la caisse et on verifie qu'elle correspond a ce qui a ete encaisse dans la journee</t>
-  </si>
-  <si>
-    <t>Lineaire (comptage - rapprochement - ecarts - validation)</t>
-  </si>
-  <si>
-    <t>ECFCCLOPS1 deja construit (rapport de synthese par session - le rapprochement especes/carte physique reste fait par Odoo lui-meme a la fermeture de session)</t>
-  </si>
-  <si>
-    <t>POS Restaurant</t>
-  </si>
-  <si>
-    <t>1 operation(s) - 0 construite(s) - 3 jobs estimes</t>
-  </si>
-  <si>
-    <t>Cloture de service (midi/soir)</t>
-  </si>
-  <si>
-    <t>A la fin de chaque service on fait les comptes du service par table</t>
-  </si>
-  <si>
-    <t>Site web</t>
-  </si>
-  <si>
-    <t>1 operation(s) - 0 construite(s) - 2 jobs estimes</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>Verification liens morts et formulaires</t>
-  </si>
-  <si>
-    <t>Une fois par semaine on verifie que le site web n'a pas de liens casses ou de formulaires en panne</t>
-  </si>
-  <si>
-    <t>eCommerce</t>
-  </si>
-  <si>
-    <t>2 operation(s) - 0 construite(s) - 5 jobs estimes</t>
-  </si>
-  <si>
-    <t>Relance paniers abandonnes</t>
-  </si>
-  <si>
-    <t>On relance les clients qui ont rempli un panier en ligne sans finaliser leur achat</t>
-  </si>
-  <si>
-    <t>Rapport ventes en ligne et paniers abandonnes</t>
-  </si>
-  <si>
-    <t>Chaque jour un bilan des ventes du site et des paniers abandonnes en cours de commande</t>
-  </si>
-  <si>
-    <t>Evenements</t>
-  </si>
-  <si>
     <t>Rapport frequentation mensuel</t>
   </si>
   <si>
@@ -1410,7 +1440,7 @@
     <t>RH</t>
   </si>
   <si>
-    <t>4 operation(s) - 1 construite(s) - 10 jobs estimes</t>
+    <t>4 operation(s) - 4 construite(s) - 10 jobs estimes</t>
   </si>
   <si>
     <t>Alerte fin de contrat (CDD/periode d'essai)</t>
@@ -1434,7 +1464,7 @@
     <t>Lineaire (checklist sequentielle)</t>
   </si>
   <si>
-    <t>Processus standard RH meme sur une version generique</t>
+    <t>ECFRSOFRH1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
   </si>
   <si>
     <t>Alerte fin de contrat (si depart lie a une echeance de contrat)</t>
@@ -1446,12 +1476,18 @@
     <t>Une fois par mois combien d'employes - depuis combien de temps</t>
   </si>
   <si>
+    <t>ECFCCLORH1 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
     <t>Bilan social annuel</t>
   </si>
   <si>
     <t>Une fois par an le bilan complet de l'annee cote ressources humaines</t>
   </si>
   <si>
+    <t>ECFCCLORH2 construit (lot garage auto/parfumerie - 2026-09-05)</t>
+  </si>
+  <si>
     <t>Rapport effectifs et anciennete (les 12 mois de l'annee)</t>
   </si>
   <si>
@@ -1686,13 +1722,13 @@
     <t>Distinct du PURGE systeme global (ECFCPRG1) - specifique au module data_recycle</t>
   </si>
   <si>
-    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 30 operations deja CONSTRUITES ET VERIFIEES (vert), 0 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
+    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 42 operations deja CONSTRUITES ET VERIFIEES (vert), 0 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
   </si>
   <si>
     <t>Memes 88 operations, groupees par type de traitement (TFJ/EOM/ON_DEMAND/...) - pour repondre a 'combien d'operations TFJ au total ?'</t>
   </si>
   <si>
-    <t>20 operations - 4 construite(s) - 59 jobs estimes (deplier pour voir le detail)</t>
+    <t>20 operations - 7 construite(s) - 59 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Presences</t>
@@ -1755,7 +1791,7 @@
     <t xml:space="preserve">   Stock</t>
   </si>
   <si>
-    <t>15 operations - 8 construite(s) - 46 jobs estimes (deplier pour voir le detail)</t>
+    <t>15 operations - 10 construite(s) - 46 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   POS Restaurant</t>
@@ -1773,7 +1809,7 @@
     <t xml:space="preserve">   Reparation</t>
   </si>
   <si>
-    <t>14 operations - 11 construite(s) - 38 jobs estimes (deplier pour voir le detail)</t>
+    <t>14 operations - 12 construite(s) - 38 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Sondages</t>
@@ -1782,7 +1818,7 @@
     <t xml:space="preserve">   Systeme</t>
   </si>
   <si>
-    <t>10 operations - 2 construite(s) - 14 jobs estimes (deplier pour voir le detail)</t>
+    <t>10 operations - 4 construite(s) - 14 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Todo</t>
@@ -1794,7 +1830,7 @@
     <t xml:space="preserve">   SMS marketing</t>
   </si>
   <si>
-    <t>5 operations - 0 construite(s) - 9 jobs estimes (deplier pour voir le detail)</t>
+    <t>5 operations - 1 construite(s) - 9 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Live chat</t>
@@ -1806,16 +1842,16 @@
     <t xml:space="preserve">   Site web</t>
   </si>
   <si>
-    <t>4 operations - 0 construite(s) - 5 jobs estimes (deplier pour voir le detail)</t>
+    <t>4 operations - 1 construite(s) - 5 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Offres emploi web</t>
   </si>
   <si>
-    <t>4 operations - 1 construite(s) - 9 jobs estimes (deplier pour voir le detail)</t>
-  </si>
-  <si>
-    <t>4 operations - 0 construite(s) - 21 jobs estimes (deplier pour voir le detail)</t>
+    <t>4 operations - 2 construite(s) - 9 jobs estimes (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>4 operations - 1 construite(s) - 21 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t>3 operations - 1 construite(s) - 13 jobs estimes (deplier pour voir le detail)</t>
@@ -1902,7 +1938,7 @@
     <t>Couverture du catalogue d'operations</t>
   </si>
   <si>
-    <t>30 des 88 operations cataloguees deja construites</t>
+    <t>42 des 88 operations cataloguees deja construites</t>
   </si>
   <si>
     <t>233 jobs estimes au total sur l'ensemble du catalogue si tout etait construit - roadmap explicite, jamais presente comme deja fait.</t>
@@ -2489,7 +2525,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F224-4569-9031-BD06F7896826}"/>
+              <c16:uniqueId val="{00000000-4674-4831-9E5B-616AD3D5F25B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2503,11 +2539,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1064785664"/>
-        <c:axId val="1064786080"/>
+        <c:axId val="1824259024"/>
+        <c:axId val="1824257360"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1064785664"/>
+        <c:axId val="1824259024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2550,7 +2586,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1064786080"/>
+        <c:crossAx val="1824257360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2558,7 +2594,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1064786080"/>
+        <c:axId val="1824257360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2609,7 +2645,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1064785664"/>
+        <c:crossAx val="1824259024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2789,10 +2825,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>56</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
@@ -2802,7 +2838,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2CFB-4404-BF67-AE7D4BAFF10B}"/>
+              <c16:uniqueId val="{00000000-99AB-439E-AA8C-37E6B2A70287}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2816,11 +2852,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1068414736"/>
-        <c:axId val="1068415984"/>
+        <c:axId val="1824258192"/>
+        <c:axId val="1824256528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1068414736"/>
+        <c:axId val="1824258192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2863,7 +2899,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1068415984"/>
+        <c:crossAx val="1824256528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2871,7 +2907,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1068415984"/>
+        <c:axId val="1824256528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2922,7 +2958,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1068414736"/>
+        <c:crossAx val="1824258192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3154,14 +3190,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6552-4DF5-8325-7EDA0238B789}"/>
+              <c16:uniqueId val="{00000000-C2A8-4F80-A3C9-A4ACEDE64708}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3267,14 +3303,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>56</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-6552-4DF5-8325-7EDA0238B789}"/>
+              <c16:uniqueId val="{00000002-C2A8-4F80-A3C9-A4ACEDE64708}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3387,7 +3423,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-6552-4DF5-8325-7EDA0238B789}"/>
+              <c16:uniqueId val="{00000003-C2A8-4F80-A3C9-A4ACEDE64708}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5150,7 +5186,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A68BBE2-A72F-43B7-8257-A8B9EFC85213}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{782E7328-3997-4BCD-AD86-E6ECF325ABB6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5186,7 +5222,7 @@
         <xdr:cNvPr id="3" name="Graphique 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC12C61E-0A2B-438D-84E8-34204E738501}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F582DC55-42DF-40B5-8CF0-3B347CBABCD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5227,7 +5263,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4034BCD5-C290-46F8-9A0F-96EEE5AB87E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D461C39-1190-4EF7-B005-7CDCFCD8D12A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5544,7 +5580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0F5A3D3-918A-419A-8CF9-4F12F98FF003}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE69E7E-BE29-448B-8BB2-66444206E958}">
   <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5745,7 +5781,7 @@
         <v>26</v>
       </c>
       <c r="E25">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -5759,7 +5795,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -5899,7 +5935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{270345B8-86E3-4F6F-9264-23A9C8034D4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFABEDA-7478-4F8D-8179-8796BA34DADB}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -7043,35 +7079,37 @@
       <c r="K45" s="29"/>
     </row>
     <row r="46" spans="1:11" ht="172.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="16">
         <v>3</v>
       </c>
-      <c r="G46" s="17" t="s">
+      <c r="G46" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="H46" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I46" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17" t="s">
+      <c r="H46" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J46" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="K46" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -7093,41 +7131,43 @@
       <c r="K47" s="29"/>
     </row>
     <row r="48" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C48" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="D48" s="17" t="s">
+      <c r="C48" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="D48" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="E48" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="16">
         <v>2</v>
       </c>
-      <c r="G48" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I48" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17" t="s">
+      <c r="G48" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="K48" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A49" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B49" s="28"/>
       <c r="C49" s="29" t="s">
@@ -7150,10 +7190,10 @@
         <v>136</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E50" s="16" t="s">
         <v>10</v>
@@ -7162,7 +7202,7 @@
         <v>3</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>27</v>
@@ -7171,7 +7211,7 @@
         <v>214</v>
       </c>
       <c r="J50" s="16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>203</v>
@@ -7179,11 +7219,11 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="26" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="25"/>
@@ -7200,7 +7240,7 @@
       </c>
       <c r="B52" s="28"/>
       <c r="C52" s="29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D52" s="29"/>
       <c r="E52" s="29"/>
@@ -7213,16 +7253,16 @@
     </row>
     <row r="53" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E53" s="16" t="s">
         <v>11</v>
@@ -7248,16 +7288,16 @@
     </row>
     <row r="54" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E54" s="16" t="s">
         <v>11</v>
@@ -7283,16 +7323,16 @@
     </row>
     <row r="55" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E55" s="16" t="s">
         <v>11</v>
@@ -7335,16 +7375,16 @@
     </row>
     <row r="57" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E57" s="16" t="s">
         <v>9</v>
@@ -7353,7 +7393,7 @@
         <v>5</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H57" s="16" t="s">
         <v>27</v>
@@ -7362,15 +7402,15 @@
         <v>214</v>
       </c>
       <c r="J57" s="16" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K57" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="58" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A58" s="30" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B58" s="28"/>
       <c r="C58" s="29" t="s">
@@ -7387,16 +7427,16 @@
     </row>
     <row r="59" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>17</v>
@@ -7415,12 +7455,12 @@
       </c>
       <c r="J59" s="17"/>
       <c r="K59" s="17" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A60" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B60" s="28"/>
       <c r="C60" s="29" t="s">
@@ -7437,16 +7477,16 @@
     </row>
     <row r="61" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>10</v>
@@ -7455,7 +7495,7 @@
         <v>3</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H61" s="16" t="s">
         <v>27</v>
@@ -7464,7 +7504,7 @@
         <v>214</v>
       </c>
       <c r="J61" s="16" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K61" s="16" t="s">
         <v>203</v>
@@ -7489,16 +7529,16 @@
     </row>
     <row r="63" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B63" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E63" s="16" t="s">
         <v>12</v>
@@ -7516,7 +7556,7 @@
         <v>214</v>
       </c>
       <c r="J63" s="16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K63" s="16" t="s">
         <v>203</v>
@@ -7524,11 +7564,11 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="26" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B64" s="24"/>
       <c r="C64" s="27" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D64" s="25"/>
       <c r="E64" s="25"/>
@@ -7541,7 +7581,7 @@
     </row>
     <row r="65" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A65" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B65" s="28"/>
       <c r="C65" s="29" t="s">
@@ -7558,16 +7598,16 @@
     </row>
     <row r="66" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E66" s="16" t="s">
         <v>10</v>
@@ -7576,7 +7616,7 @@
         <v>5</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H66" s="16" t="s">
         <v>27</v>
@@ -7585,7 +7625,7 @@
         <v>214</v>
       </c>
       <c r="J66" s="16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K66" s="16" t="s">
         <v>203</v>
@@ -7593,16 +7633,16 @@
     </row>
     <row r="67" spans="1:11" ht="172.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E67" s="16" t="s">
         <v>10</v>
@@ -7611,7 +7651,7 @@
         <v>2</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H67" s="16" t="s">
         <v>27</v>
@@ -7620,7 +7660,7 @@
         <v>214</v>
       </c>
       <c r="J67" s="16" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K67" s="16" t="s">
         <v>203</v>
@@ -7645,16 +7685,16 @@
     </row>
     <row r="69" spans="1:11" ht="211.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E69" s="16" t="s">
         <v>9</v>
@@ -7663,7 +7703,7 @@
         <v>9</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H69" s="16" t="s">
         <v>27</v>
@@ -7672,15 +7712,15 @@
         <v>214</v>
       </c>
       <c r="J69" s="16" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="70" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A70" s="30" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B70" s="28"/>
       <c r="C70" s="29" t="s">
@@ -7697,16 +7737,16 @@
     </row>
     <row r="71" spans="1:11" ht="132.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E71" s="16" t="s">
         <v>17</v>
@@ -7715,7 +7755,7 @@
         <v>6</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H71" s="16" t="s">
         <v>27</v>
@@ -7724,10 +7764,10 @@
         <v>214</v>
       </c>
       <c r="J71" s="16" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
@@ -7749,16 +7789,16 @@
     </row>
     <row r="73" spans="1:11" ht="225" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>16</v>
@@ -7767,7 +7807,7 @@
         <v>12</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>26</v>
@@ -7776,15 +7816,15 @@
         <v>201</v>
       </c>
       <c r="J73" s="17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K73" s="17" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A74" s="30" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B74" s="28"/>
       <c r="C74" s="29" t="s">
@@ -7801,16 +7841,16 @@
     </row>
     <row r="75" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E75" s="16" t="s">
         <v>24</v>
@@ -7828,7 +7868,7 @@
         <v>214</v>
       </c>
       <c r="J75" s="16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K75" s="16" t="s">
         <v>203</v>
@@ -7836,7 +7876,7 @@
     </row>
     <row r="76" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A76" s="30" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B76" s="28"/>
       <c r="C76" s="29" t="s">
@@ -7853,16 +7893,16 @@
     </row>
     <row r="77" spans="1:11" ht="132.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E77" s="17" t="s">
         <v>20</v>
@@ -7871,7 +7911,7 @@
         <v>2</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>26</v>
@@ -7880,7 +7920,7 @@
         <v>201</v>
       </c>
       <c r="J77" s="17" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K77" s="17" t="s">
         <v>203</v>
@@ -7888,7 +7928,7 @@
     </row>
     <row r="78" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A78" s="30" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B78" s="28"/>
       <c r="C78" s="29" t="s">
@@ -7905,16 +7945,16 @@
     </row>
     <row r="79" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E79" s="17" t="s">
         <v>18</v>
@@ -7923,7 +7963,7 @@
         <v>3</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>26</v>
@@ -7932,7 +7972,7 @@
         <v>201</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K79" s="17" t="s">
         <v>203</v>
@@ -7940,11 +7980,11 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="26" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B80" s="24"/>
       <c r="C80" s="27" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D80" s="25"/>
       <c r="E80" s="25"/>
@@ -7961,7 +8001,7 @@
       </c>
       <c r="B81" s="28"/>
       <c r="C81" s="29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D81" s="29"/>
       <c r="E81" s="29"/>
@@ -7974,16 +8014,16 @@
     </row>
     <row r="82" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E82" s="16" t="s">
         <v>11</v>
@@ -8009,16 +8049,16 @@
     </row>
     <row r="83" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B83" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E83" s="16" t="s">
         <v>11</v>
@@ -8044,7 +8084,7 @@
     </row>
     <row r="84" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B84" s="13" t="s">
         <v>151</v>
@@ -8053,7 +8093,7 @@
         <v>156</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E84" s="16" t="s">
         <v>11</v>
@@ -8096,16 +8136,16 @@
     </row>
     <row r="86" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>151</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E86" s="17" t="s">
         <v>9</v>
@@ -8124,12 +8164,12 @@
       </c>
       <c r="J86" s="17"/>
       <c r="K86" s="17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="87" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A87" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B87" s="28"/>
       <c r="C87" s="29" t="s">
@@ -8146,16 +8186,16 @@
     </row>
     <row r="88" spans="1:11" ht="172.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B88" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E88" s="16" t="s">
         <v>10</v>
@@ -8164,7 +8204,7 @@
         <v>4</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H88" s="16" t="s">
         <v>27</v>
@@ -8173,7 +8213,7 @@
         <v>214</v>
       </c>
       <c r="J88" s="16" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K88" s="16" t="s">
         <v>203</v>
@@ -8181,7 +8221,7 @@
     </row>
     <row r="89" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A89" s="30" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B89" s="28"/>
       <c r="C89" s="29" t="s">
@@ -8198,16 +8238,16 @@
     </row>
     <row r="90" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B90" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E90" s="16" t="s">
         <v>19</v>
@@ -8233,11 +8273,11 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="26" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B91" s="24"/>
       <c r="C91" s="27" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D91" s="25"/>
       <c r="E91" s="25"/>
@@ -8267,16 +8307,16 @@
     </row>
     <row r="93" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>158</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E93" s="17" t="s">
         <v>9</v>
@@ -8295,12 +8335,12 @@
       </c>
       <c r="J93" s="17"/>
       <c r="K93" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A94" s="30" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B94" s="28"/>
       <c r="C94" s="29" t="s">
@@ -8317,16 +8357,16 @@
     </row>
     <row r="95" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>158</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E95" s="17" t="s">
         <v>17</v>
@@ -8345,7 +8385,7 @@
       </c>
       <c r="J95" s="17"/>
       <c r="K95" s="17" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="96" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
@@ -8367,16 +8407,16 @@
     </row>
     <row r="97" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B97" s="13" t="s">
         <v>158</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E97" s="16" t="s">
         <v>15</v>
@@ -8394,7 +8434,7 @@
         <v>214</v>
       </c>
       <c r="J97" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K97" s="16" t="s">
         <v>203</v>
@@ -8402,7 +8442,7 @@
     </row>
     <row r="98" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A98" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B98" s="28"/>
       <c r="C98" s="29" t="s">
@@ -8419,16 +8459,16 @@
     </row>
     <row r="99" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B99" s="13" t="s">
         <v>158</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E99" s="16" t="s">
         <v>10</v>
@@ -8437,7 +8477,7 @@
         <v>6</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H99" s="16" t="s">
         <v>27</v>
@@ -8446,7 +8486,7 @@
         <v>214</v>
       </c>
       <c r="J99" s="16" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K99" s="16" t="s">
         <v>203</v>
@@ -8454,11 +8494,11 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="26" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B100" s="24"/>
       <c r="C100" s="27" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D100" s="25"/>
       <c r="E100" s="25"/>
@@ -8488,16 +8528,16 @@
     </row>
     <row r="102" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>163</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E102" s="17" t="s">
         <v>9</v>
@@ -8521,7 +8561,7 @@
     </row>
     <row r="103" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A103" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B103" s="28"/>
       <c r="C103" s="29" t="s">
@@ -8538,16 +8578,16 @@
     </row>
     <row r="104" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>163</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E104" s="17" t="s">
         <v>10</v>
@@ -8571,7 +8611,7 @@
     </row>
     <row r="105" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A105" s="30" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B105" s="28"/>
       <c r="C105" s="29" t="s">
@@ -8588,16 +8628,16 @@
     </row>
     <row r="106" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>163</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E106" s="17" t="s">
         <v>18</v>
@@ -8606,7 +8646,7 @@
         <v>3</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>26</v>
@@ -8621,11 +8661,11 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="26" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B107" s="24"/>
       <c r="C107" s="27" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D107" s="25"/>
       <c r="E107" s="25"/>
@@ -8638,7 +8678,7 @@
     </row>
     <row r="108" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A108" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B108" s="28"/>
       <c r="C108" s="29" t="s">
@@ -8654,35 +8694,37 @@
       <c r="K108" s="29"/>
     </row>
     <row r="109" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A109" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="B109" s="11" t="s">
+      <c r="A109" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B109" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C109" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="D109" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="E109" s="17" t="s">
+      <c r="C109" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="E109" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F109" s="17">
+      <c r="F109" s="16">
         <v>2</v>
       </c>
-      <c r="G109" s="17" t="s">
+      <c r="G109" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H109" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I109" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="J109" s="17"/>
-      <c r="K109" s="17" t="s">
+      <c r="H109" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I109" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J109" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="K109" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -8704,45 +8746,47 @@
       <c r="K110" s="29"/>
     </row>
     <row r="111" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A111" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="B111" s="11" t="s">
+      <c r="A111" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B111" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C111" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="D111" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="E111" s="17" t="s">
+      <c r="C111" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="E111" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F111" s="17">
+      <c r="F111" s="16">
         <v>1</v>
       </c>
-      <c r="G111" s="17" t="s">
+      <c r="G111" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="H111" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I111" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J111" s="17"/>
-      <c r="K111" s="17" t="s">
+      <c r="H111" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I111" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J111" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="K111" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="26" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B112" s="24"/>
       <c r="C112" s="27" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D112" s="25"/>
       <c r="E112" s="25"/>
@@ -8771,35 +8815,37 @@
       <c r="K113" s="29"/>
     </row>
     <row r="114" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A114" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="B114" s="11" t="s">
+      <c r="A114" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="B114" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C114" s="17" t="s">
-        <v>412</v>
-      </c>
-      <c r="D114" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="E114" s="17" t="s">
+      <c r="C114" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E114" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F114" s="17">
+      <c r="F114" s="16">
         <v>2</v>
       </c>
-      <c r="G114" s="17" t="s">
+      <c r="G114" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H114" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I114" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="J114" s="17"/>
-      <c r="K114" s="17" t="s">
+      <c r="H114" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J114" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="K114" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -8821,45 +8867,47 @@
       <c r="K115" s="29"/>
     </row>
     <row r="116" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A116" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="B116" s="11" t="s">
+      <c r="A116" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="B116" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C116" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="D116" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="E116" s="17" t="s">
+      <c r="C116" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="D116" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="E116" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F116" s="17">
+      <c r="F116" s="16">
         <v>1</v>
       </c>
-      <c r="G116" s="17" t="s">
+      <c r="G116" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="H116" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I116" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J116" s="17"/>
-      <c r="K116" s="17" t="s">
+      <c r="H116" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I116" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="K116" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="26" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B117" s="24"/>
       <c r="C117" s="27" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D117" s="25"/>
       <c r="E117" s="25"/>
@@ -8887,42 +8935,44 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A119" s="11" t="s">
-        <v>416</v>
-      </c>
-      <c r="B119" s="11" t="s">
+    <row r="119" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A119" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B119" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C119" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D119" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="E119" s="17" t="s">
+      <c r="C119" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="D119" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E119" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F119" s="17">
+      <c r="F119" s="16">
         <v>3</v>
       </c>
-      <c r="G119" s="17" t="s">
+      <c r="G119" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H119" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I119" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J119" s="17"/>
-      <c r="K119" s="17" t="s">
+      <c r="H119" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I119" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J119" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="K119" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="120" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A120" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B120" s="28"/>
       <c r="C120" s="29" t="s">
@@ -8939,16 +8989,16 @@
     </row>
     <row r="121" spans="1:11" ht="198.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B121" s="13" t="s">
         <v>172</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="E121" s="16" t="s">
         <v>10</v>
@@ -8957,7 +9007,7 @@
         <v>4</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="H121" s="16" t="s">
         <v>27</v>
@@ -8966,7 +9016,7 @@
         <v>214</v>
       </c>
       <c r="J121" s="16" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="K121" s="16" t="s">
         <v>203</v>
@@ -8974,11 +9024,11 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="26" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B122" s="24"/>
       <c r="C122" s="27" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="D122" s="25"/>
       <c r="E122" s="25"/>
@@ -8991,7 +9041,7 @@
     </row>
     <row r="123" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A123" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B123" s="28"/>
       <c r="C123" s="29" t="s">
@@ -9008,16 +9058,16 @@
     </row>
     <row r="124" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>175</v>
       </c>
       <c r="C124" s="17" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E124" s="17" t="s">
         <v>10</v>
@@ -9041,11 +9091,11 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="26" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B125" s="24"/>
       <c r="C125" s="27" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D125" s="25"/>
       <c r="E125" s="25"/>
@@ -9075,16 +9125,16 @@
     </row>
     <row r="127" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A127" s="11" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E127" s="17" t="s">
         <v>13</v>
@@ -9108,11 +9158,11 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="26" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B128" s="24"/>
       <c r="C128" s="27" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D128" s="25"/>
       <c r="E128" s="25"/>
@@ -9141,41 +9191,43 @@
       <c r="K129" s="29"/>
     </row>
     <row r="130" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A130" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="B130" s="11" t="s">
+      <c r="A130" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B130" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C130" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="D130" s="17" t="s">
-        <v>436</v>
-      </c>
-      <c r="E130" s="17" t="s">
+      <c r="C130" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E130" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F130" s="17">
+      <c r="F130" s="16">
         <v>2</v>
       </c>
-      <c r="G130" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="H130" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I130" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J130" s="17"/>
-      <c r="K130" s="17" t="s">
+      <c r="G130" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="H130" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I130" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J130" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="K130" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="131" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A131" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B131" s="28"/>
       <c r="C131" s="29" t="s">
@@ -9191,45 +9243,47 @@
       <c r="K131" s="29"/>
     </row>
     <row r="132" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A132" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="B132" s="11" t="s">
+      <c r="A132" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B132" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C132" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D132" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="E132" s="17" t="s">
+      <c r="C132" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="D132" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E132" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F132" s="17">
+      <c r="F132" s="16">
         <v>3</v>
       </c>
-      <c r="G132" s="17" t="s">
+      <c r="G132" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H132" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I132" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J132" s="17"/>
-      <c r="K132" s="17" t="s">
+      <c r="H132" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I132" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J132" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K132" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="26" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B133" s="24"/>
       <c r="C133" s="27" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="D133" s="25"/>
       <c r="E133" s="25"/>
@@ -9259,16 +9313,16 @@
     </row>
     <row r="135" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A135" s="11" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>181</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="E135" s="17" t="s">
         <v>9</v>
@@ -9309,16 +9363,16 @@
     </row>
     <row r="137" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A137" s="11" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>181</v>
       </c>
       <c r="C137" s="17" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="E137" s="17" t="s">
         <v>14</v>
@@ -9342,11 +9396,11 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="26" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B138" s="24"/>
       <c r="C138" s="27" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D138" s="25"/>
       <c r="E138" s="25"/>
@@ -9376,16 +9430,16 @@
     </row>
     <row r="140" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="E140" s="17" t="s">
         <v>9</v>
@@ -9409,11 +9463,11 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="26" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B141" s="24"/>
       <c r="C141" s="27" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D141" s="25"/>
       <c r="E141" s="25"/>
@@ -9443,16 +9497,16 @@
     </row>
     <row r="143" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E143" s="17" t="s">
         <v>14</v>
@@ -9476,11 +9530,11 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="26" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B144" s="24"/>
       <c r="C144" s="27" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D144" s="25"/>
       <c r="E144" s="25"/>
@@ -9493,7 +9547,7 @@
     </row>
     <row r="145" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A145" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B145" s="28"/>
       <c r="C145" s="29" t="s">
@@ -9510,16 +9564,16 @@
     </row>
     <row r="146" spans="1:11" ht="277.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A146" s="13" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>10</v>
@@ -9528,7 +9582,7 @@
         <v>2</v>
       </c>
       <c r="G146" s="16" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H146" s="16" t="s">
         <v>27</v>
@@ -9537,7 +9591,7 @@
         <v>214</v>
       </c>
       <c r="J146" s="16" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="K146" s="16" t="s">
         <v>203</v>
@@ -9561,38 +9615,38 @@
       <c r="K147" s="29"/>
     </row>
     <row r="148" spans="1:11" ht="225" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A148" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="B148" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="C148" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="D148" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="E148" s="17" t="s">
+      <c r="A148" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="D148" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="E148" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F148" s="17">
+      <c r="F148" s="16">
         <v>3</v>
       </c>
-      <c r="G148" s="17" t="s">
-        <v>461</v>
-      </c>
-      <c r="H148" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I148" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J148" s="17" t="s">
-        <v>462</v>
-      </c>
-      <c r="K148" s="17" t="s">
-        <v>463</v>
+      <c r="G148" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="H148" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I148" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J148" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="K148" s="16" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="149" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
@@ -9613,35 +9667,37 @@
       <c r="K149" s="29"/>
     </row>
     <row r="150" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A150" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="B150" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="C150" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="D150" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="E150" s="17" t="s">
+      <c r="A150" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="D150" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E150" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F150" s="17">
+      <c r="F150" s="16">
         <v>2</v>
       </c>
-      <c r="G150" s="17" t="s">
+      <c r="G150" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H150" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I150" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J150" s="17"/>
-      <c r="K150" s="17" t="s">
+      <c r="H150" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I150" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J150" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="K150" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -9663,45 +9719,47 @@
       <c r="K151" s="29"/>
     </row>
     <row r="152" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A152" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="C152" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="D152" s="17" t="s">
-        <v>467</v>
-      </c>
-      <c r="E152" s="17" t="s">
+      <c r="A152" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="D152" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="E152" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F152" s="17">
+      <c r="F152" s="16">
         <v>3</v>
       </c>
-      <c r="G152" s="17" t="s">
+      <c r="G152" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H152" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I152" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="J152" s="17"/>
-      <c r="K152" s="17" t="s">
-        <v>468</v>
+      <c r="H152" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I152" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J152" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="K152" s="16" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="26" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B153" s="24"/>
       <c r="C153" s="27" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="D153" s="25"/>
       <c r="E153" s="25"/>
@@ -9731,16 +9789,16 @@
     </row>
     <row r="155" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C155" s="16" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D155" s="16" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="E155" s="16" t="s">
         <v>9</v>
@@ -9749,7 +9807,7 @@
         <v>4</v>
       </c>
       <c r="G155" s="16" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="H155" s="16" t="s">
         <v>27</v>
@@ -9758,15 +9816,15 @@
         <v>214</v>
       </c>
       <c r="J155" s="16" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="K155" s="16" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="156" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A156" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B156" s="28"/>
       <c r="C156" s="29" t="s">
@@ -9783,16 +9841,16 @@
     </row>
     <row r="157" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="E157" s="17" t="s">
         <v>10</v>
@@ -9816,11 +9874,11 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="26" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B158" s="24"/>
       <c r="C158" s="27" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="D158" s="25"/>
       <c r="E158" s="25"/>
@@ -9850,16 +9908,16 @@
     </row>
     <row r="160" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A160" s="11" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C160" s="17" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="E160" s="17" t="s">
         <v>16</v>
@@ -9900,16 +9958,16 @@
     </row>
     <row r="162" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A162" s="11" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="E162" s="17" t="s">
         <v>12</v>
@@ -9933,11 +9991,11 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="26" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B163" s="24"/>
       <c r="C163" s="27" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="D163" s="25"/>
       <c r="E163" s="25"/>
@@ -9967,16 +10025,16 @@
     </row>
     <row r="165" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A165" s="11" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C165" s="17" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E165" s="17" t="s">
         <v>9</v>
@@ -10000,11 +10058,11 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="26" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B166" s="24"/>
       <c r="C166" s="27" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D166" s="25"/>
       <c r="E166" s="25"/>
@@ -10017,7 +10075,7 @@
     </row>
     <row r="167" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A167" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B167" s="28"/>
       <c r="C167" s="29" t="s">
@@ -10034,16 +10092,16 @@
     </row>
     <row r="168" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="E168" s="17" t="s">
         <v>10</v>
@@ -10067,11 +10125,11 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="26" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B169" s="24"/>
       <c r="C169" s="27" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D169" s="25"/>
       <c r="E169" s="25"/>
@@ -10101,16 +10159,16 @@
     </row>
     <row r="171" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A171" s="11" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C171" s="17" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="D171" s="17" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="E171" s="17" t="s">
         <v>9</v>
@@ -10134,11 +10192,11 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="26" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B172" s="24"/>
       <c r="C172" s="27" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="D172" s="25"/>
       <c r="E172" s="25"/>
@@ -10168,16 +10226,16 @@
     </row>
     <row r="174" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A174" s="13" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C174" s="16" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="D174" s="16" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E174" s="16" t="s">
         <v>9</v>
@@ -10195,7 +10253,7 @@
         <v>214</v>
       </c>
       <c r="J174" s="16" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="K174" s="16" t="s">
         <v>203</v>
@@ -10203,7 +10261,7 @@
     </row>
     <row r="175" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A175" s="30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B175" s="28"/>
       <c r="C175" s="29" t="s">
@@ -10220,16 +10278,16 @@
     </row>
     <row r="176" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A176" s="11" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C176" s="17" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="E176" s="17" t="s">
         <v>10</v>
@@ -10253,11 +10311,11 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="26" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B177" s="24"/>
       <c r="C177" s="27" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D177" s="25"/>
       <c r="E177" s="25"/>
@@ -10287,16 +10345,16 @@
     </row>
     <row r="179" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A179" s="11" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C179" s="17" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E179" s="17" t="s">
         <v>12</v>
@@ -10320,11 +10378,11 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="26" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B180" s="24"/>
       <c r="C180" s="27" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D180" s="25"/>
       <c r="E180" s="25"/>
@@ -10354,16 +10412,16 @@
     </row>
     <row r="182" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A182" s="11" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C182" s="17" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="E182" s="17" t="s">
         <v>9</v>
@@ -10387,11 +10445,11 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="26" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="B183" s="24"/>
       <c r="C183" s="27" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D183" s="25"/>
       <c r="E183" s="25"/>
@@ -10421,16 +10479,16 @@
     </row>
     <row r="185" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A185" s="11" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C185" s="17" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="D185" s="17" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="E185" s="17" t="s">
         <v>11</v>
@@ -10454,11 +10512,11 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="26" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B186" s="24"/>
       <c r="C186" s="27" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D186" s="25"/>
       <c r="E186" s="25"/>
@@ -10471,7 +10529,7 @@
     </row>
     <row r="187" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A187" s="30" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B187" s="28"/>
       <c r="C187" s="29" t="s">
@@ -10488,16 +10546,16 @@
     </row>
     <row r="188" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A188" s="11" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C188" s="17" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="D188" s="17" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="E188" s="17" t="s">
         <v>19</v>
@@ -10521,11 +10579,11 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="26" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B189" s="24"/>
       <c r="C189" s="27" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D189" s="25"/>
       <c r="E189" s="25"/>
@@ -10555,16 +10613,16 @@
     </row>
     <row r="191" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A191" s="11" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C191" s="17" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="D191" s="17" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="E191" s="17" t="s">
         <v>13</v>
@@ -10588,11 +10646,11 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="26" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B192" s="24"/>
       <c r="C192" s="27" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="D192" s="25"/>
       <c r="E192" s="25"/>
@@ -10622,16 +10680,16 @@
     </row>
     <row r="194" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A194" s="11" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C194" s="17" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D194" s="17" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="E194" s="17" t="s">
         <v>9</v>
@@ -10672,16 +10730,16 @@
     </row>
     <row r="196" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A196" s="11" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C196" s="17" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D196" s="17" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="E196" s="17" t="s">
         <v>12</v>
@@ -10690,7 +10748,7 @@
         <v>2</v>
       </c>
       <c r="G196" s="17" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>26</v>
@@ -10705,11 +10763,11 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="26" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="B197" s="24"/>
       <c r="C197" s="27" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D197" s="25"/>
       <c r="E197" s="25"/>
@@ -10739,16 +10797,16 @@
     </row>
     <row r="199" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A199" s="11" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C199" s="17" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E199" s="17" t="s">
         <v>12</v>
@@ -10772,11 +10830,11 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="26" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="B200" s="24"/>
       <c r="C200" s="27" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D200" s="25"/>
       <c r="E200" s="25"/>
@@ -10806,16 +10864,16 @@
     </row>
     <row r="202" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A202" s="11" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C202" s="17" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="E202" s="17" t="s">
         <v>13</v>
@@ -10839,11 +10897,11 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="26" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="B203" s="24"/>
       <c r="C203" s="27" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D203" s="25"/>
       <c r="E203" s="25"/>
@@ -10873,16 +10931,16 @@
     </row>
     <row r="205" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A205" s="11" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C205" s="17" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="E205" s="17" t="s">
         <v>9</v>
@@ -10900,7 +10958,7 @@
         <v>233</v>
       </c>
       <c r="J205" s="17" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="K205" s="17" t="s">
         <v>203</v>
@@ -10908,7 +10966,7 @@
     </row>
     <row r="207" spans="1:11" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="23" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -10922,7 +10980,7 @@
       <c r="K207" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{270345B8-86E3-4F6F-9264-23A9C8034D4F}"/>
+  <autoFilter ref="A3:K3" xr:uid="{DCFABEDA-7478-4F8D-8179-8796BA34DADB}"/>
   <mergeCells count="116">
     <mergeCell ref="C204:K204"/>
     <mergeCell ref="A207:K207"/>
@@ -11046,7 +11104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F0FA64-2001-4638-8478-D9B38AC2BAC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B080FD3-BC29-448D-836E-817B0276C16E}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -11068,7 +11126,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11135,7 +11193,7 @@
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="27" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="D4" s="25"/>
       <c r="E4" s="25"/>
@@ -11148,7 +11206,7 @@
     </row>
     <row r="5" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="29" t="s">
@@ -11165,16 +11223,16 @@
     </row>
     <row r="6" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>9</v>
@@ -11183,7 +11241,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>27</v>
@@ -11192,15 +11250,15 @@
         <v>214</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A7" s="30" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B7" s="28"/>
       <c r="C7" s="29" t="s">
@@ -11217,16 +11275,16 @@
     </row>
     <row r="8" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>9</v>
@@ -11250,7 +11308,7 @@
     </row>
     <row r="9" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="29" t="s">
@@ -11266,41 +11324,43 @@
       <c r="K9" s="29"/>
     </row>
     <row r="10" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="A10" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <v>2</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17" t="s">
+      <c r="H10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="K10" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="29" t="s">
@@ -11317,16 +11377,16 @@
     </row>
     <row r="12" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>181</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>9</v>
@@ -11350,7 +11410,7 @@
     </row>
     <row r="13" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A13" s="30" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="29" t="s">
@@ -11367,16 +11427,16 @@
     </row>
     <row r="14" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>9</v>
@@ -11400,7 +11460,7 @@
     </row>
     <row r="15" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A15" s="30" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="B15" s="28"/>
       <c r="C15" s="29" t="s">
@@ -11417,16 +11477,16 @@
     </row>
     <row r="16" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>9</v>
@@ -11450,7 +11510,7 @@
     </row>
     <row r="17" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="29" t="s">
@@ -11467,16 +11527,16 @@
     </row>
     <row r="18" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>9</v>
@@ -11494,7 +11554,7 @@
         <v>233</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="K18" s="17" t="s">
         <v>203</v>
@@ -11502,7 +11562,7 @@
     </row>
     <row r="19" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="29" t="s">
@@ -11519,16 +11579,16 @@
     </row>
     <row r="20" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>9</v>
@@ -11552,7 +11612,7 @@
     </row>
     <row r="21" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="29" t="s">
@@ -11569,16 +11629,16 @@
     </row>
     <row r="22" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>9</v>
@@ -11602,7 +11662,7 @@
     </row>
     <row r="23" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A23" s="30" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="29" t="s">
@@ -11619,16 +11679,16 @@
     </row>
     <row r="24" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>9</v>
@@ -11646,7 +11706,7 @@
         <v>214</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>203</v>
@@ -11654,7 +11714,7 @@
     </row>
     <row r="25" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B25" s="28"/>
       <c r="C25" s="29" t="s">
@@ -11671,16 +11731,16 @@
     </row>
     <row r="26" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>9</v>
@@ -11689,7 +11749,7 @@
         <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>27</v>
@@ -11698,15 +11758,15 @@
         <v>214</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A27" s="30" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B27" s="28"/>
       <c r="C27" s="29" t="s">
@@ -11723,16 +11783,16 @@
     </row>
     <row r="28" spans="1:11" ht="211.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>9</v>
@@ -11741,7 +11801,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H28" s="16" t="s">
         <v>27</v>
@@ -11750,15 +11810,15 @@
         <v>214</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="29" t="s">
@@ -11808,7 +11868,7 @@
     </row>
     <row r="31" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="29" t="s">
@@ -11858,7 +11918,7 @@
     </row>
     <row r="33" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B33" s="28"/>
       <c r="C33" s="29" t="s">
@@ -11908,7 +11968,7 @@
     </row>
     <row r="35" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A35" s="30" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="B35" s="28"/>
       <c r="C35" s="29" t="s">
@@ -11924,41 +11984,43 @@
       <c r="K35" s="29"/>
     </row>
     <row r="36" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="B36" s="11" t="s">
+      <c r="A36" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C36" s="17" t="s">
-        <v>412</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="E36" s="17" t="s">
+      <c r="C36" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E36" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="16">
         <v>2</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17" t="s">
+      <c r="H36" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="K36" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A37" s="30" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="29" t="s">
@@ -11973,42 +12035,44 @@
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
     </row>
-    <row r="38" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>416</v>
-      </c>
-      <c r="B38" s="11" t="s">
+    <row r="38" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="B38" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="E38" s="17" t="s">
+      <c r="C38" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E38" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="16">
         <v>3</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G38" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H38" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I38" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17" t="s">
+      <c r="H38" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="K38" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B39" s="28"/>
       <c r="C39" s="29" t="s">
@@ -12025,16 +12089,16 @@
     </row>
     <row r="40" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>163</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>9</v>
@@ -12058,7 +12122,7 @@
     </row>
     <row r="41" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A41" s="30" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B41" s="28"/>
       <c r="C41" s="29" t="s">
@@ -12075,16 +12139,16 @@
     </row>
     <row r="42" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>151</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>9</v>
@@ -12103,12 +12167,12 @@
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A43" s="30" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="29" t="s">
@@ -12125,16 +12189,16 @@
     </row>
     <row r="44" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>158</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>9</v>
@@ -12153,7 +12217,7 @@
       </c>
       <c r="J44" s="17"/>
       <c r="K44" s="17" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -12162,7 +12226,7 @@
       </c>
       <c r="B45" s="24"/>
       <c r="C45" s="27" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
@@ -12175,7 +12239,7 @@
     </row>
     <row r="46" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A46" s="30" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B46" s="28"/>
       <c r="C46" s="29" t="s">
@@ -12192,16 +12256,16 @@
     </row>
     <row r="47" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>10</v>
@@ -12210,7 +12274,7 @@
         <v>5</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H47" s="16" t="s">
         <v>27</v>
@@ -12219,7 +12283,7 @@
         <v>214</v>
       </c>
       <c r="J47" s="16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K47" s="16" t="s">
         <v>203</v>
@@ -12227,16 +12291,16 @@
     </row>
     <row r="48" spans="1:11" ht="172.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>10</v>
@@ -12245,7 +12309,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H48" s="16" t="s">
         <v>27</v>
@@ -12254,7 +12318,7 @@
         <v>214</v>
       </c>
       <c r="J48" s="16" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>203</v>
@@ -12262,7 +12326,7 @@
     </row>
     <row r="49" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A49" s="30" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B49" s="28"/>
       <c r="C49" s="29" t="s">
@@ -12279,16 +12343,16 @@
     </row>
     <row r="50" spans="1:11" ht="277.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="E50" s="16" t="s">
         <v>10</v>
@@ -12297,7 +12361,7 @@
         <v>2</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>27</v>
@@ -12306,7 +12370,7 @@
         <v>214</v>
       </c>
       <c r="J50" s="16" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>203</v>
@@ -12314,7 +12378,7 @@
     </row>
     <row r="51" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A51" s="30" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B51" s="28"/>
       <c r="C51" s="29" t="s">
@@ -12331,16 +12395,16 @@
     </row>
     <row r="52" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>175</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>10</v>
@@ -12364,7 +12428,7 @@
     </row>
     <row r="53" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A53" s="30" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B53" s="28"/>
       <c r="C53" s="29" t="s">
@@ -12380,41 +12444,43 @@
       <c r="K53" s="29"/>
     </row>
     <row r="54" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="B54" s="11" t="s">
+      <c r="A54" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="C54" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="E54" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54" s="16">
         <v>3</v>
       </c>
-      <c r="G54" s="17" t="s">
+      <c r="G54" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H54" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I54" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17" t="s">
+      <c r="H54" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J54" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K54" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A55" s="30" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B55" s="28"/>
       <c r="C55" s="29" t="s">
@@ -12431,16 +12497,16 @@
     </row>
     <row r="56" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>10</v>
@@ -12464,7 +12530,7 @@
     </row>
     <row r="57" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A57" s="30" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B57" s="28"/>
       <c r="C57" s="29" t="s">
@@ -12481,16 +12547,16 @@
     </row>
     <row r="58" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>10</v>
@@ -12514,7 +12580,7 @@
     </row>
     <row r="59" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A59" s="30" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B59" s="28"/>
       <c r="C59" s="29" t="s">
@@ -12531,16 +12597,16 @@
     </row>
     <row r="60" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>10</v>
@@ -12564,7 +12630,7 @@
     </row>
     <row r="61" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A61" s="30" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B61" s="28"/>
       <c r="C61" s="29" t="s">
@@ -12581,16 +12647,16 @@
     </row>
     <row r="62" spans="1:11" ht="198.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B62" s="13" t="s">
         <v>172</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="E62" s="16" t="s">
         <v>10</v>
@@ -12599,7 +12665,7 @@
         <v>4</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="H62" s="16" t="s">
         <v>27</v>
@@ -12608,7 +12674,7 @@
         <v>214</v>
       </c>
       <c r="J62" s="16" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="K62" s="16" t="s">
         <v>203</v>
@@ -12616,7 +12682,7 @@
     </row>
     <row r="63" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A63" s="30" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B63" s="28"/>
       <c r="C63" s="29" t="s">
@@ -12633,16 +12699,16 @@
     </row>
     <row r="64" spans="1:11" ht="172.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>10</v>
@@ -12651,7 +12717,7 @@
         <v>4</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H64" s="16" t="s">
         <v>27</v>
@@ -12660,7 +12726,7 @@
         <v>214</v>
       </c>
       <c r="J64" s="16" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K64" s="16" t="s">
         <v>203</v>
@@ -12668,7 +12734,7 @@
     </row>
     <row r="65" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A65" s="30" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B65" s="28"/>
       <c r="C65" s="29" t="s">
@@ -12685,16 +12751,16 @@
     </row>
     <row r="66" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E66" s="16" t="s">
         <v>10</v>
@@ -12703,7 +12769,7 @@
         <v>3</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H66" s="16" t="s">
         <v>27</v>
@@ -12712,7 +12778,7 @@
         <v>214</v>
       </c>
       <c r="J66" s="16" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K66" s="16" t="s">
         <v>203</v>
@@ -12720,7 +12786,7 @@
     </row>
     <row r="67" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A67" s="30" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B67" s="28"/>
       <c r="C67" s="29" t="s">
@@ -12743,10 +12809,10 @@
         <v>136</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E68" s="16" t="s">
         <v>10</v>
@@ -12755,7 +12821,7 @@
         <v>3</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H68" s="16" t="s">
         <v>27</v>
@@ -12764,7 +12830,7 @@
         <v>214</v>
       </c>
       <c r="J68" s="16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K68" s="16" t="s">
         <v>203</v>
@@ -12772,7 +12838,7 @@
     </row>
     <row r="69" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A69" s="30" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="B69" s="28"/>
       <c r="C69" s="29" t="s">
@@ -12788,41 +12854,43 @@
       <c r="K69" s="29"/>
     </row>
     <row r="70" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="B70" s="11" t="s">
+      <c r="A70" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C70" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="D70" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="E70" s="17" t="s">
+      <c r="C70" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="E70" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F70" s="17">
+      <c r="F70" s="16">
         <v>2</v>
       </c>
-      <c r="G70" s="17" t="s">
+      <c r="G70" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H70" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I70" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17" t="s">
+      <c r="H70" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="K70" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A71" s="30" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B71" s="28"/>
       <c r="C71" s="29" t="s">
@@ -12839,16 +12907,16 @@
     </row>
     <row r="72" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>163</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>10</v>
@@ -12872,7 +12940,7 @@
     </row>
     <row r="73" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A73" s="30" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B73" s="28"/>
       <c r="C73" s="29" t="s">
@@ -12889,16 +12957,16 @@
     </row>
     <row r="74" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>158</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E74" s="16" t="s">
         <v>10</v>
@@ -12907,7 +12975,7 @@
         <v>6</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H74" s="16" t="s">
         <v>27</v>
@@ -12916,7 +12984,7 @@
         <v>214</v>
       </c>
       <c r="J74" s="16" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K74" s="16" t="s">
         <v>203</v>
@@ -12928,7 +12996,7 @@
       </c>
       <c r="B75" s="24"/>
       <c r="C75" s="27" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="D75" s="25"/>
       <c r="E75" s="25"/>
@@ -12941,7 +13009,7 @@
     </row>
     <row r="76" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A76" s="30" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B76" s="28"/>
       <c r="C76" s="29" t="s">
@@ -13098,11 +13166,11 @@
     </row>
     <row r="81" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A81" s="30" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B81" s="28"/>
       <c r="C81" s="29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D81" s="29"/>
       <c r="E81" s="29"/>
@@ -13115,16 +13183,16 @@
     </row>
     <row r="82" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E82" s="16" t="s">
         <v>11</v>
@@ -13150,16 +13218,16 @@
     </row>
     <row r="83" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B83" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E83" s="16" t="s">
         <v>11</v>
@@ -13185,7 +13253,7 @@
     </row>
     <row r="84" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B84" s="13" t="s">
         <v>151</v>
@@ -13194,7 +13262,7 @@
         <v>156</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E84" s="16" t="s">
         <v>11</v>
@@ -13220,11 +13288,11 @@
     </row>
     <row r="85" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A85" s="30" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B85" s="28"/>
       <c r="C85" s="29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D85" s="29"/>
       <c r="E85" s="29"/>
@@ -13237,16 +13305,16 @@
     </row>
     <row r="86" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A86" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B86" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E86" s="16" t="s">
         <v>11</v>
@@ -13272,16 +13340,16 @@
     </row>
     <row r="87" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B87" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E87" s="16" t="s">
         <v>11</v>
@@ -13307,16 +13375,16 @@
     </row>
     <row r="88" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B88" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E88" s="16" t="s">
         <v>11</v>
@@ -13342,7 +13410,7 @@
     </row>
     <row r="89" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A89" s="30" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B89" s="28"/>
       <c r="C89" s="29" t="s">
@@ -13359,16 +13427,16 @@
     </row>
     <row r="90" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="E90" s="17" t="s">
         <v>11</v>
@@ -13392,7 +13460,7 @@
     </row>
     <row r="91" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A91" s="30" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B91" s="28"/>
       <c r="C91" s="29" t="s">
@@ -13408,43 +13476,43 @@
       <c r="K91" s="29"/>
     </row>
     <row r="92" spans="1:11" ht="225" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A92" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="C92" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="E92" s="17" t="s">
+      <c r="A92" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="E92" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="17">
+      <c r="F92" s="16">
         <v>3</v>
       </c>
-      <c r="G92" s="17" t="s">
-        <v>461</v>
-      </c>
-      <c r="H92" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I92" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J92" s="17" t="s">
-        <v>462</v>
-      </c>
-      <c r="K92" s="17" t="s">
-        <v>463</v>
+      <c r="G92" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J92" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="K92" s="16" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="93" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A93" s="30" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B93" s="28"/>
       <c r="C93" s="29" t="s">
@@ -13496,7 +13564,7 @@
     </row>
     <row r="95" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A95" s="30" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B95" s="28"/>
       <c r="C95" s="29" t="s">
@@ -13552,7 +13620,7 @@
       </c>
       <c r="B97" s="24"/>
       <c r="C97" s="27" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="D97" s="25"/>
       <c r="E97" s="25"/>
@@ -13565,7 +13633,7 @@
     </row>
     <row r="98" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A98" s="30" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B98" s="28"/>
       <c r="C98" s="29" t="s">
@@ -13650,7 +13718,7 @@
     </row>
     <row r="101" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A101" s="30" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="B101" s="28"/>
       <c r="C101" s="29" t="s">
@@ -13667,16 +13735,16 @@
     </row>
     <row r="102" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E102" s="17" t="s">
         <v>12</v>
@@ -13700,7 +13768,7 @@
     </row>
     <row r="103" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A103" s="30" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B103" s="28"/>
       <c r="C103" s="29" t="s">
@@ -13717,16 +13785,16 @@
     </row>
     <row r="104" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="E104" s="17" t="s">
         <v>12</v>
@@ -13750,7 +13818,7 @@
     </row>
     <row r="105" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A105" s="30" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B105" s="28"/>
       <c r="C105" s="29" t="s">
@@ -13767,16 +13835,16 @@
     </row>
     <row r="106" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E106" s="17" t="s">
         <v>12</v>
@@ -13800,7 +13868,7 @@
     </row>
     <row r="107" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A107" s="30" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="B107" s="28"/>
       <c r="C107" s="29" t="s">
@@ -13817,16 +13885,16 @@
     </row>
     <row r="108" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="E108" s="17" t="s">
         <v>12</v>
@@ -13835,7 +13903,7 @@
         <v>2</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>26</v>
@@ -13850,7 +13918,7 @@
     </row>
     <row r="109" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A109" s="30" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B109" s="28"/>
       <c r="C109" s="29" t="s">
@@ -13867,16 +13935,16 @@
     </row>
     <row r="110" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B110" s="13" t="s">
         <v>141</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E110" s="16" t="s">
         <v>12</v>
@@ -13894,7 +13962,7 @@
         <v>214</v>
       </c>
       <c r="J110" s="16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K110" s="16" t="s">
         <v>203</v>
@@ -13902,7 +13970,7 @@
     </row>
     <row r="111" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A111" s="30" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B111" s="28"/>
       <c r="C111" s="29" t="s">
@@ -13954,7 +14022,7 @@
     </row>
     <row r="113" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A113" s="30" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B113" s="28"/>
       <c r="C113" s="29" t="s">
@@ -13970,41 +14038,43 @@
       <c r="K113" s="29"/>
     </row>
     <row r="114" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A114" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="B114" s="11" t="s">
+      <c r="A114" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B114" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C114" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="D114" s="17" t="s">
-        <v>436</v>
-      </c>
-      <c r="E114" s="17" t="s">
+      <c r="C114" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E114" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F114" s="17">
+      <c r="F114" s="16">
         <v>2</v>
       </c>
-      <c r="G114" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="H114" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I114" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J114" s="17"/>
-      <c r="K114" s="17" t="s">
+      <c r="G114" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="H114" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J114" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="K114" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="115" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A115" s="30" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="B115" s="28"/>
       <c r="C115" s="29" t="s">
@@ -14020,35 +14090,37 @@
       <c r="K115" s="29"/>
     </row>
     <row r="116" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A116" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="B116" s="11" t="s">
+      <c r="A116" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B116" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C116" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="D116" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="E116" s="17" t="s">
+      <c r="C116" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="D116" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="E116" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F116" s="17">
+      <c r="F116" s="16">
         <v>1</v>
       </c>
-      <c r="G116" s="17" t="s">
+      <c r="G116" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="H116" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I116" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J116" s="17"/>
-      <c r="K116" s="17" t="s">
+      <c r="H116" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I116" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="K116" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -14058,7 +14130,7 @@
       </c>
       <c r="B117" s="24"/>
       <c r="C117" s="27" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="D117" s="25"/>
       <c r="E117" s="25"/>
@@ -14071,7 +14143,7 @@
     </row>
     <row r="118" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A118" s="30" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="B118" s="28"/>
       <c r="C118" s="29" t="s">
@@ -14088,16 +14160,16 @@
     </row>
     <row r="119" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="E119" s="17" t="s">
         <v>13</v>
@@ -14121,7 +14193,7 @@
     </row>
     <row r="120" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A120" s="30" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="B120" s="28"/>
       <c r="C120" s="29" t="s">
@@ -14138,16 +14210,16 @@
     </row>
     <row r="121" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C121" s="17" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="E121" s="17" t="s">
         <v>13</v>
@@ -14171,7 +14243,7 @@
     </row>
     <row r="122" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A122" s="30" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B122" s="28"/>
       <c r="C122" s="29" t="s">
@@ -14188,16 +14260,16 @@
     </row>
     <row r="123" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E123" s="17" t="s">
         <v>13</v>
@@ -14221,7 +14293,7 @@
     </row>
     <row r="124" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A124" s="30" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B124" s="28"/>
       <c r="C124" s="29" t="s">
@@ -14271,7 +14343,7 @@
     </row>
     <row r="126" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A126" s="30" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B126" s="28"/>
       <c r="C126" s="29" t="s">
@@ -14287,35 +14359,37 @@
       <c r="K126" s="29"/>
     </row>
     <row r="127" spans="1:11" ht="172.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A127" s="11" t="s">
+      <c r="A127" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C127" s="17" t="s">
+      <c r="C127" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="D127" s="17" t="s">
+      <c r="D127" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="E127" s="17" t="s">
+      <c r="E127" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F127" s="17">
+      <c r="F127" s="16">
         <v>3</v>
       </c>
-      <c r="G127" s="17" t="s">
+      <c r="G127" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="H127" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I127" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J127" s="17"/>
-      <c r="K127" s="17" t="s">
+      <c r="H127" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I127" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J127" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="K127" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -14325,7 +14399,7 @@
       </c>
       <c r="B128" s="24"/>
       <c r="C128" s="27" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="D128" s="25"/>
       <c r="E128" s="25"/>
@@ -14338,7 +14412,7 @@
     </row>
     <row r="129" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A129" s="30" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B129" s="28"/>
       <c r="C129" s="29" t="s">
@@ -14355,16 +14429,16 @@
     </row>
     <row r="130" spans="1:11" ht="66.599999999999994" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>181</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="E130" s="17" t="s">
         <v>14</v>
@@ -14388,7 +14462,7 @@
     </row>
     <row r="131" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A131" s="30" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="B131" s="28"/>
       <c r="C131" s="29" t="s">
@@ -14405,16 +14479,16 @@
     </row>
     <row r="132" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A132" s="11" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E132" s="17" t="s">
         <v>14</v>
@@ -14438,7 +14512,7 @@
     </row>
     <row r="133" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A133" s="30" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B133" s="28"/>
       <c r="C133" s="29" t="s">
@@ -14488,7 +14562,7 @@
     </row>
     <row r="135" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A135" s="30" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="B135" s="28"/>
       <c r="C135" s="29" t="s">
@@ -14504,35 +14578,37 @@
       <c r="K135" s="29"/>
     </row>
     <row r="136" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A136" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="B136" s="11" t="s">
+      <c r="A136" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="B136" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C136" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="D136" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="E136" s="17" t="s">
+      <c r="C136" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="E136" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F136" s="17">
+      <c r="F136" s="16">
         <v>1</v>
       </c>
-      <c r="G136" s="17" t="s">
+      <c r="G136" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="H136" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I136" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J136" s="17"/>
-      <c r="K136" s="17" t="s">
+      <c r="H136" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I136" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J136" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="K136" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -14542,7 +14618,7 @@
       </c>
       <c r="B137" s="24"/>
       <c r="C137" s="27" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="D137" s="25"/>
       <c r="E137" s="25"/>
@@ -14555,7 +14631,7 @@
     </row>
     <row r="138" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A138" s="30" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B138" s="28"/>
       <c r="C138" s="29" t="s">
@@ -14571,41 +14647,43 @@
       <c r="K138" s="29"/>
     </row>
     <row r="139" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C139" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="D139" s="17" t="s">
+      <c r="C139" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="E139" s="17" t="s">
+      <c r="D139" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="E139" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F139" s="17">
+      <c r="F139" s="16">
         <v>2</v>
       </c>
-      <c r="G139" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="H139" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I139" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J139" s="17"/>
-      <c r="K139" s="17" t="s">
+      <c r="G139" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="H139" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I139" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J139" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="K139" s="16" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="140" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A140" s="30" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B140" s="28"/>
       <c r="C140" s="29" t="s">
@@ -14622,16 +14700,16 @@
     </row>
     <row r="141" spans="1:11" ht="93" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A141" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B141" s="13" t="s">
         <v>158</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>15</v>
@@ -14649,7 +14727,7 @@
         <v>214</v>
       </c>
       <c r="J141" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K141" s="16" t="s">
         <v>203</v>
@@ -14657,7 +14735,7 @@
     </row>
     <row r="142" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A142" s="30" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B142" s="28"/>
       <c r="C142" s="29" t="s">
@@ -14709,7 +14787,7 @@
     </row>
     <row r="144" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A144" s="30" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B144" s="28"/>
       <c r="C144" s="29" t="s">
@@ -14763,7 +14841,7 @@
       </c>
       <c r="B146" s="24"/>
       <c r="C146" s="27" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="D146" s="25"/>
       <c r="E146" s="25"/>
@@ -14776,7 +14854,7 @@
     </row>
     <row r="147" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A147" s="30" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B147" s="28"/>
       <c r="C147" s="29" t="s">
@@ -14792,41 +14870,43 @@
       <c r="K147" s="29"/>
     </row>
     <row r="148" spans="1:11" ht="79.8" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A148" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="B148" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="C148" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="D148" s="17" t="s">
-        <v>467</v>
-      </c>
-      <c r="E148" s="17" t="s">
+      <c r="A148" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="D148" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="E148" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F148" s="17">
+      <c r="F148" s="16">
         <v>3</v>
       </c>
-      <c r="G148" s="17" t="s">
+      <c r="G148" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="H148" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I148" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="J148" s="17"/>
-      <c r="K148" s="17" t="s">
-        <v>468</v>
+      <c r="H148" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I148" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J148" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="K148" s="16" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="149" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A149" s="30" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B149" s="28"/>
       <c r="C149" s="29" t="s">
@@ -14843,16 +14923,16 @@
     </row>
     <row r="150" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A150" s="11" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="E150" s="17" t="s">
         <v>16</v>
@@ -14876,7 +14956,7 @@
     </row>
     <row r="151" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A151" s="30" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B151" s="28"/>
       <c r="C151" s="29" t="s">
@@ -14928,7 +15008,7 @@
     </row>
     <row r="153" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A153" s="30" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B153" s="28"/>
       <c r="C153" s="29" t="s">
@@ -14945,16 +15025,16 @@
     </row>
     <row r="154" spans="1:11" ht="225" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E154" s="17" t="s">
         <v>16</v>
@@ -14963,7 +15043,7 @@
         <v>12</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>26</v>
@@ -14972,10 +15052,10 @@
         <v>201</v>
       </c>
       <c r="J154" s="17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K154" s="17" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
@@ -14984,7 +15064,7 @@
       </c>
       <c r="B155" s="24"/>
       <c r="C155" s="27" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="D155" s="25"/>
       <c r="E155" s="25"/>
@@ -14997,7 +15077,7 @@
     </row>
     <row r="156" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A156" s="30" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B156" s="28"/>
       <c r="C156" s="29" t="s">
@@ -15014,16 +15094,16 @@
     </row>
     <row r="157" spans="1:11" ht="106.2" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>158</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E157" s="17" t="s">
         <v>17</v>
@@ -15042,12 +15122,12 @@
       </c>
       <c r="J157" s="17"/>
       <c r="K157" s="17" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="158" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A158" s="30" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B158" s="28"/>
       <c r="C158" s="29" t="s">
@@ -15064,16 +15144,16 @@
     </row>
     <row r="159" spans="1:11" ht="132.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E159" s="16" t="s">
         <v>17</v>
@@ -15082,7 +15162,7 @@
         <v>6</v>
       </c>
       <c r="G159" s="16" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H159" s="16" t="s">
         <v>27</v>
@@ -15091,15 +15171,15 @@
         <v>214</v>
       </c>
       <c r="J159" s="16" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K159" s="16" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="160" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A160" s="30" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B160" s="28"/>
       <c r="C160" s="29" t="s">
@@ -15116,16 +15196,16 @@
     </row>
     <row r="161" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A161" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C161" s="17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D161" s="17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E161" s="17" t="s">
         <v>17</v>
@@ -15144,7 +15224,7 @@
       </c>
       <c r="J161" s="17"/>
       <c r="K161" s="17" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
@@ -15153,7 +15233,7 @@
       </c>
       <c r="B162" s="24"/>
       <c r="C162" s="27" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="D162" s="25"/>
       <c r="E162" s="25"/>
@@ -15166,7 +15246,7 @@
     </row>
     <row r="163" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A163" s="30" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B163" s="28"/>
       <c r="C163" s="29" t="s">
@@ -15183,16 +15263,16 @@
     </row>
     <row r="164" spans="1:11" ht="119.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A164" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>163</v>
       </c>
       <c r="C164" s="17" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E164" s="17" t="s">
         <v>18</v>
@@ -15201,7 +15281,7 @@
         <v>3</v>
       </c>
       <c r="G164" s="17" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>26</v>
@@ -15216,7 +15296,7 @@
     </row>
     <row r="165" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A165" s="30" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B165" s="28"/>
       <c r="C165" s="29" t="s">
@@ -15233,16 +15313,16 @@
     </row>
     <row r="166" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A166" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C166" s="17" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E166" s="17" t="s">
         <v>18</v>
@@ -15251,7 +15331,7 @@
         <v>3</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>26</v>
@@ -15260,7 +15340,7 @@
         <v>201</v>
       </c>
       <c r="J166" s="17" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K166" s="17" t="s">
         <v>203</v>
@@ -15272,7 +15352,7 @@
       </c>
       <c r="B167" s="24"/>
       <c r="C167" s="27" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="D167" s="25"/>
       <c r="E167" s="25"/>
@@ -15285,7 +15365,7 @@
     </row>
     <row r="168" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A168" s="30" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="B168" s="28"/>
       <c r="C168" s="29" t="s">
@@ -15302,16 +15382,16 @@
     </row>
     <row r="169" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A169" s="11" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C169" s="17" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="D169" s="17" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="E169" s="17" t="s">
         <v>19</v>
@@ -15335,7 +15415,7 @@
     </row>
     <row r="170" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A170" s="30" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="B170" s="28"/>
       <c r="C170" s="29" t="s">
@@ -15352,16 +15432,16 @@
     </row>
     <row r="171" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A171" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B171" s="13" t="s">
         <v>151</v>
       </c>
       <c r="C171" s="16" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D171" s="16" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E171" s="16" t="s">
         <v>19</v>
@@ -15391,7 +15471,7 @@
       </c>
       <c r="B172" s="24"/>
       <c r="C172" s="27" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="D172" s="25"/>
       <c r="E172" s="25"/>
@@ -15404,7 +15484,7 @@
     </row>
     <row r="173" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A173" s="30" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B173" s="28"/>
       <c r="C173" s="29" t="s">
@@ -15421,16 +15501,16 @@
     </row>
     <row r="174" spans="1:11" ht="132.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A174" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C174" s="17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D174" s="17" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E174" s="17" t="s">
         <v>20</v>
@@ -15439,7 +15519,7 @@
         <v>2</v>
       </c>
       <c r="G174" s="17" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>26</v>
@@ -15448,7 +15528,7 @@
         <v>201</v>
       </c>
       <c r="J174" s="17" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K174" s="17" t="s">
         <v>203</v>
@@ -15460,7 +15540,7 @@
       </c>
       <c r="B175" s="24"/>
       <c r="C175" s="27" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="D175" s="25"/>
       <c r="E175" s="25"/>
@@ -15473,7 +15553,7 @@
     </row>
     <row r="176" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A176" s="30" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B176" s="28"/>
       <c r="C176" s="29" t="s">
@@ -15529,7 +15609,7 @@
       </c>
       <c r="B178" s="24"/>
       <c r="C178" s="27" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="D178" s="25"/>
       <c r="E178" s="25"/>
@@ -15542,7 +15622,7 @@
     </row>
     <row r="179" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A179" s="30" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B179" s="28"/>
       <c r="C179" s="29" t="s">
@@ -15598,7 +15678,7 @@
       </c>
       <c r="B181" s="24"/>
       <c r="C181" s="27" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="D181" s="25"/>
       <c r="E181" s="25"/>
@@ -15611,7 +15691,7 @@
     </row>
     <row r="182" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A182" s="30" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B182" s="28"/>
       <c r="C182" s="29" t="s">
@@ -15667,7 +15747,7 @@
       </c>
       <c r="B184" s="24"/>
       <c r="C184" s="27" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="D184" s="25"/>
       <c r="E184" s="25"/>
@@ -15680,7 +15760,7 @@
     </row>
     <row r="185" spans="1:11" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A185" s="30" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B185" s="28"/>
       <c r="C185" s="29" t="s">
@@ -15697,16 +15777,16 @@
     </row>
     <row r="186" spans="1:11" ht="159" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A186" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C186" s="16" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D186" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E186" s="16" t="s">
         <v>24</v>
@@ -15724,14 +15804,14 @@
         <v>214</v>
       </c>
       <c r="J186" s="16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K186" s="16" t="s">
         <v>203</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{11F0FA64-2001-4638-8478-D9B38AC2BAC8}"/>
+  <autoFilter ref="A3:K3" xr:uid="{7B080FD3-BC29-448D-836E-817B0276C16E}"/>
   <mergeCells count="96">
     <mergeCell ref="C178:K178"/>
     <mergeCell ref="C179:K179"/>
@@ -15835,7 +15915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B949E3C-C5F3-4340-A693-9B586EBE4314}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF28FBC1-688B-416E-8F96-F8DF10FA9E68}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16101,7 +16181,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{8B949E3C-C5F3-4340-A693-9B586EBE4314}"/>
+  <autoFilter ref="A3:E3" xr:uid="{EF28FBC1-688B-416E-8F96-F8DF10FA9E68}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -16110,7 +16190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95CADAF-E3AA-4907-B3D0-E04401D2F848}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60B1C066-3C78-4B82-A351-839EFE37780B}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16316,7 +16396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C0D2A5-4B7B-4782-B406-15C573D635B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5823A546-157F-43D2-8BCC-0C0B0800E5F6}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16327,7 +16407,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -16340,106 +16420,106 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -16449,7 +16529,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -16457,7 +16537,7 @@
         <v>27</v>
       </c>
       <c r="B15" s="11">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -16465,7 +16545,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="11">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -16478,153 +16558,153 @@
     </row>
     <row r="28" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -16639,7 +16719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A916C533-855E-42F4-95FE-FFE68C6424CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E988BA-3F6F-4A96-9677-3E1B8BC490E3}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17167,7 +17247,7 @@
       <c r="G25" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{A916C533-855E-42F4-95FE-FFE68C6424CE}"/>
+  <autoFilter ref="A3:G3" xr:uid="{B4E988BA-3F6F-4A96-9677-3E1B8BC490E3}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A25:G25"/>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34DE7E2-F58C-47CF-BB92-77740D68307E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48911CB6-FB96-47A3-B146-47344F263130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{064D8D0D-B934-4A2C-A324-93FEC81DD467}"/>
+    <workbookView xWindow="5604" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{BD0C8803-00E2-4086-9BC0-5036026230F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -126,12 +126,12 @@
     <t>Statut</t>
   </si>
   <si>
+    <t>CONSTRUIT</t>
+  </si>
+  <si>
     <t>A CONSTRUIRE</t>
   </si>
   <si>
-    <t>CONSTRUIT</t>
-  </si>
-  <si>
     <t>HORS PERIMETRE</t>
   </si>
   <si>
@@ -1032,7 +1032,7 @@
     <t>Comptabilite</t>
   </si>
   <si>
-    <t>8 operation(s) - 5 construite(s) - 40 jobs estimes</t>
+    <t>8 operation(s) - 7 construite(s) - 40 jobs estimes</t>
   </si>
   <si>
     <t>CP</t>
@@ -1131,7 +1131,7 @@
     <t>Lineaire (generation - archivage)</t>
   </si>
   <si>
-    <t>Traitement lourd decale hors heures de pointe</t>
+    <t>ECFJDIFCP1 construit (session 2026-09-05 - releve texte reel - vrai rendu PDF QWeb a confirmer sur la VM)</t>
   </si>
   <si>
     <t xml:space="preserve">   INTRADAY</t>
@@ -1146,7 +1146,7 @@
     <t>Lineaire (10h-14h-16h - 3 executions independantes)</t>
   </si>
   <si>
-    <t>Analogue aux cycles de compensation SEPA a heures fixes</t>
+    <t>ECFJINTCP1 construit (session 2026-09-05 - 1 seul job continu pour les 3 creneaux - meme raisonnement que les autres consolidations)</t>
   </si>
   <si>
     <t>Achat</t>
@@ -1722,7 +1722,7 @@
     <t>Distinct du PURGE systeme global (ECFCPRG1) - specifique au module data_recycle</t>
   </si>
   <si>
-    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 42 operations deja CONSTRUITES ET VERIFIEES (vert), 0 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
+    <t>TOTAL : 88 operations reelles cataloguees, 233 jobs estimes au total (lineaires + paralleles cumules) - 44 operations deja CONSTRUITES ET VERIFIEES (vert), 0 en PRIORITE HAUTE a construire ensuite (jaune - operations quotidiennes/critiques des modules coeur), le reste sur le meme patron deja prouve. Ces chiffres sont des estimations architecturales raisonnees (jamais un decompte de jobs reellement ecrits pour les operations encore A CONSTRUIRE). Priorite : HAUTE = necessaire des le premier cycle d'exploitation reel (quotidien/critique sur un module coeur) - MOYENNE = utile mais differable - BASSE = illustratif/complementaire. Colonne 'Depend de' : chaine de dependance metier reelle (pas une IN_COND technique) - l'operation en amont qui doit exister avant que celle-ci ait un sens operationnel.</t>
   </si>
   <si>
     <t>Memes 88 operations, groupees par type de traitement (TFJ/EOM/ON_DEMAND/...) - pour repondre a 'combien d'operations TFJ au total ?'</t>
@@ -1857,7 +1857,7 @@
     <t>3 operations - 1 construite(s) - 13 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>2 operations - 0 construite(s) - 6 jobs estimes (deplier pour voir le detail)</t>
+    <t>2 operations - 1 construite(s) - 6 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t>2 operations - 1 construite(s) - 2 jobs estimes (deplier pour voir le detail)</t>
@@ -1866,7 +1866,7 @@
     <t xml:space="preserve">   Cantine</t>
   </si>
   <si>
-    <t>1 operation - 0 construite(s) - 2 jobs estimes (deplier pour voir le detail)</t>
+    <t>1 operation - 1 construite(s) - 2 jobs estimes (deplier pour voir le detail)</t>
   </si>
   <si>
     <t>1 operation - 0 construite(s) - 6 jobs estimes (deplier pour voir le detail)</t>
@@ -1938,7 +1938,7 @@
     <t>Couverture du catalogue d'operations</t>
   </si>
   <si>
-    <t>42 des 88 operations cataloguees deja construites</t>
+    <t>44 des 88 operations cataloguees deja construites</t>
   </si>
   <si>
     <t>233 jobs estimes au total sur l'ensemble du catalogue si tout etait construit - roadmap explicite, jamais presente comme deja fait.</t>
@@ -2209,13 +2209,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3C1E5A"/>
+        <fgColor rgb="FF9669EB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5A3C82"/>
+        <fgColor rgb="FF4078E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2402,7 +2402,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="4078E6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2525,7 +2525,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4674-4831-9E5B-616AD3D5F25B}"/>
+              <c16:uniqueId val="{00000000-A793-4FDF-AA78-0FB40EC304EF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2539,11 +2539,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1824259024"/>
-        <c:axId val="1824257360"/>
+        <c:axId val="2010807808"/>
+        <c:axId val="2010811968"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1824259024"/>
+        <c:axId val="2010807808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2586,7 +2586,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1824257360"/>
+        <c:crossAx val="2010811968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2594,7 +2594,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1824257360"/>
+        <c:axId val="2010811968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2645,7 +2645,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1824259024"/>
+        <c:crossAx val="2010807808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2793,7 +2793,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="9669EB"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2807,10 +2807,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>A CONSTRUIRE</c:v>
+                  <c:v>CONSTRUIT</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>CONSTRUIT</c:v>
+                  <c:v>A CONSTRUIRE</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>HORS PERIMETRE</c:v>
@@ -2838,7 +2838,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-99AB-439E-AA8C-37E6B2A70287}"/>
+              <c16:uniqueId val="{00000000-29CC-4F07-8A92-9B0664B51AEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2852,11 +2852,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1824258192"/>
-        <c:axId val="1824256528"/>
+        <c:axId val="2010814880"/>
+        <c:axId val="2010815296"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1824258192"/>
+        <c:axId val="2010814880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2899,7 +2899,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1824256528"/>
+        <c:crossAx val="2010815296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2907,7 +2907,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1824256528"/>
+        <c:axId val="2010815296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2958,7 +2958,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1824258192"/>
+        <c:crossAx val="2010814880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3190,14 +3190,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>42</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C2A8-4F80-A3C9-A4ACEDE64708}"/>
+              <c16:uniqueId val="{00000000-E7FB-48F4-81D1-8D27B5C3D9F5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3303,14 +3303,14 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>44</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C2A8-4F80-A3C9-A4ACEDE64708}"/>
+              <c16:uniqueId val="{00000002-E7FB-48F4-81D1-8D27B5C3D9F5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3423,7 +3423,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C2A8-4F80-A3C9-A4ACEDE64708}"/>
+              <c16:uniqueId val="{00000003-E7FB-48F4-81D1-8D27B5C3D9F5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5186,7 +5186,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{782E7328-3997-4BCD-AD86-E6ECF325ABB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC0F9029-D6AE-45B3-B432-93A6C2CDC232}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5222,7 +5222,7 @@
         <xdr:cNvPr id="3" name="Graphique 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F582DC55-42DF-40B5-8CF0-3B347CBABCD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A20D84A-F2E8-440D-A5CA-3752431BE5AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5263,7 +5263,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D461C39-1190-4EF7-B005-7CDCFCD8D12A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A94EFAF4-CCED-4E8E-829A-18682DC34207}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5580,7 +5580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FE69E7E-BE29-448B-8BB2-66444206E958}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EE4200F-0D73-4CC1-A486-5CF96E6BC6A8}">
   <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5935,7 +5935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFABEDA-7478-4F8D-8179-8796BA34DADB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{136913D7-A670-4F99-A276-1619907CCF39}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -6075,7 +6075,7 @@
         <v>200</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>201</v>
@@ -6179,7 +6179,7 @@
         <v>213</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>214</v>
@@ -6231,7 +6231,7 @@
         <v>219</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I12" s="16" t="s">
         <v>214</v>
@@ -6283,7 +6283,7 @@
         <v>224</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>214</v>
@@ -6352,7 +6352,7 @@
         <v>232</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I17" s="17" t="s">
         <v>233</v>
@@ -6404,7 +6404,7 @@
         <v>213</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I19" s="17" t="s">
         <v>233</v>
@@ -6454,7 +6454,7 @@
         <v>240</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I21" s="17" t="s">
         <v>201</v>
@@ -6506,7 +6506,7 @@
         <v>245</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I23" s="17" t="s">
         <v>201</v>
@@ -6573,7 +6573,7 @@
         <v>252</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I26" s="17" t="s">
         <v>201</v>
@@ -6608,7 +6608,7 @@
         <v>256</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="17" t="s">
         <v>233</v>
@@ -6658,7 +6658,7 @@
         <v>252</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I29" s="17" t="s">
         <v>233</v>
@@ -6708,7 +6708,7 @@
         <v>261</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I31" s="17" t="s">
         <v>233</v>
@@ -6775,7 +6775,7 @@
         <v>252</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>233</v>
@@ -6825,7 +6825,7 @@
         <v>270</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>233</v>
@@ -6944,7 +6944,7 @@
         <v>252</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I41" s="16" t="s">
         <v>214</v>
@@ -6979,7 +6979,7 @@
         <v>252</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I42" s="16" t="s">
         <v>214</v>
@@ -7014,7 +7014,7 @@
         <v>252</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I43" s="16" t="s">
         <v>214</v>
@@ -7049,7 +7049,7 @@
         <v>252</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I44" s="16" t="s">
         <v>214</v>
@@ -7101,7 +7101,7 @@
         <v>291</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I46" s="16" t="s">
         <v>214</v>
@@ -7153,7 +7153,7 @@
         <v>295</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I48" s="16" t="s">
         <v>214</v>
@@ -7205,7 +7205,7 @@
         <v>300</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I50" s="16" t="s">
         <v>214</v>
@@ -7274,7 +7274,7 @@
         <v>252</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I53" s="16" t="s">
         <v>214</v>
@@ -7309,7 +7309,7 @@
         <v>252</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I54" s="16" t="s">
         <v>214</v>
@@ -7344,7 +7344,7 @@
         <v>252</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I55" s="16" t="s">
         <v>214</v>
@@ -7396,7 +7396,7 @@
         <v>313</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I57" s="16" t="s">
         <v>214</v>
@@ -7448,7 +7448,7 @@
         <v>213</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I59" s="17" t="s">
         <v>201</v>
@@ -7498,7 +7498,7 @@
         <v>322</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I61" s="16" t="s">
         <v>214</v>
@@ -7550,7 +7550,7 @@
         <v>252</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I63" s="16" t="s">
         <v>214</v>
@@ -7619,7 +7619,7 @@
         <v>332</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I66" s="16" t="s">
         <v>214</v>
@@ -7654,7 +7654,7 @@
         <v>336</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I67" s="16" t="s">
         <v>214</v>
@@ -7706,7 +7706,7 @@
         <v>340</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I69" s="16" t="s">
         <v>214</v>
@@ -7758,7 +7758,7 @@
         <v>345</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I71" s="16" t="s">
         <v>214</v>
@@ -7810,7 +7810,7 @@
         <v>350</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I73" s="17" t="s">
         <v>201</v>
@@ -7862,7 +7862,7 @@
         <v>252</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I75" s="16" t="s">
         <v>214</v>
@@ -7892,37 +7892,37 @@
       <c r="K76" s="29"/>
     </row>
     <row r="77" spans="1:11" ht="132.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C77" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E77" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F77" s="17">
+      <c r="F77" s="16">
         <v>2</v>
       </c>
-      <c r="G77" s="17" t="s">
+      <c r="G77" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="H77" s="17" t="s">
+      <c r="H77" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I77" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J77" s="17" t="s">
+      <c r="I77" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J77" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="K77" s="17" t="s">
+      <c r="K77" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -7943,38 +7943,38 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A79" s="11" t="s">
+    <row r="79" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A79" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C79" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F79" s="17">
+      <c r="F79" s="16">
         <v>3</v>
       </c>
-      <c r="G79" s="17" t="s">
+      <c r="G79" s="16" t="s">
         <v>365</v>
       </c>
-      <c r="H79" s="17" t="s">
+      <c r="H79" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I79" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J79" s="17" t="s">
+      <c r="I79" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J79" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="K79" s="17" t="s">
+      <c r="K79" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
         <v>252</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I82" s="16" t="s">
         <v>214</v>
@@ -8070,7 +8070,7 @@
         <v>252</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I83" s="16" t="s">
         <v>214</v>
@@ -8105,7 +8105,7 @@
         <v>252</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I84" s="16" t="s">
         <v>214</v>
@@ -8157,7 +8157,7 @@
         <v>213</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I86" s="17" t="s">
         <v>201</v>
@@ -8207,7 +8207,7 @@
         <v>378</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I88" s="16" t="s">
         <v>214</v>
@@ -8259,7 +8259,7 @@
         <v>252</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I90" s="16" t="s">
         <v>214</v>
@@ -8328,7 +8328,7 @@
         <v>213</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I93" s="17" t="s">
         <v>201</v>
@@ -8378,7 +8378,7 @@
         <v>213</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I95" s="17" t="s">
         <v>201</v>
@@ -8428,7 +8428,7 @@
         <v>256</v>
       </c>
       <c r="H97" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I97" s="16" t="s">
         <v>214</v>
@@ -8480,7 +8480,7 @@
         <v>396</v>
       </c>
       <c r="H99" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I99" s="16" t="s">
         <v>214</v>
@@ -8549,7 +8549,7 @@
         <v>213</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>233</v>
@@ -8599,7 +8599,7 @@
         <v>213</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I104" s="17" t="s">
         <v>201</v>
@@ -8649,7 +8649,7 @@
         <v>406</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I106" s="17" t="s">
         <v>201</v>
@@ -8716,7 +8716,7 @@
         <v>213</v>
       </c>
       <c r="H109" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I109" s="16" t="s">
         <v>214</v>
@@ -8768,7 +8768,7 @@
         <v>252</v>
       </c>
       <c r="H111" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I111" s="16" t="s">
         <v>214</v>
@@ -8837,7 +8837,7 @@
         <v>213</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I114" s="16" t="s">
         <v>214</v>
@@ -8889,7 +8889,7 @@
         <v>252</v>
       </c>
       <c r="H116" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I116" s="16" t="s">
         <v>214</v>
@@ -8958,7 +8958,7 @@
         <v>213</v>
       </c>
       <c r="H119" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I119" s="16" t="s">
         <v>214</v>
@@ -9010,7 +9010,7 @@
         <v>429</v>
       </c>
       <c r="H121" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I121" s="16" t="s">
         <v>214</v>
@@ -9079,7 +9079,7 @@
         <v>213</v>
       </c>
       <c r="H124" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I124" s="17" t="s">
         <v>201</v>
@@ -9146,7 +9146,7 @@
         <v>213</v>
       </c>
       <c r="H127" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I127" s="17" t="s">
         <v>233</v>
@@ -9213,7 +9213,7 @@
         <v>336</v>
       </c>
       <c r="H130" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I130" s="16" t="s">
         <v>214</v>
@@ -9265,7 +9265,7 @@
         <v>213</v>
       </c>
       <c r="H132" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I132" s="16" t="s">
         <v>214</v>
@@ -9334,7 +9334,7 @@
         <v>213</v>
       </c>
       <c r="H135" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I135" s="17" t="s">
         <v>233</v>
@@ -9384,7 +9384,7 @@
         <v>252</v>
       </c>
       <c r="H137" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I137" s="17" t="s">
         <v>233</v>
@@ -9451,7 +9451,7 @@
         <v>213</v>
       </c>
       <c r="H140" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I140" s="17" t="s">
         <v>233</v>
@@ -9518,7 +9518,7 @@
         <v>252</v>
       </c>
       <c r="H143" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I143" s="17" t="s">
         <v>233</v>
@@ -9585,7 +9585,7 @@
         <v>467</v>
       </c>
       <c r="H146" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I146" s="16" t="s">
         <v>214</v>
@@ -9637,7 +9637,7 @@
         <v>471</v>
       </c>
       <c r="H148" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I148" s="16" t="s">
         <v>214</v>
@@ -9689,7 +9689,7 @@
         <v>213</v>
       </c>
       <c r="H150" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I150" s="16" t="s">
         <v>214</v>
@@ -9741,7 +9741,7 @@
         <v>213</v>
       </c>
       <c r="H152" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I152" s="16" t="s">
         <v>214</v>
@@ -9810,7 +9810,7 @@
         <v>486</v>
       </c>
       <c r="H155" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I155" s="16" t="s">
         <v>214</v>
@@ -9862,7 +9862,7 @@
         <v>213</v>
       </c>
       <c r="H157" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I157" s="17" t="s">
         <v>201</v>
@@ -9929,7 +9929,7 @@
         <v>213</v>
       </c>
       <c r="H160" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I160" s="17" t="s">
         <v>201</v>
@@ -9979,7 +9979,7 @@
         <v>252</v>
       </c>
       <c r="H162" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I162" s="17" t="s">
         <v>233</v>
@@ -10046,7 +10046,7 @@
         <v>213</v>
       </c>
       <c r="H165" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I165" s="17" t="s">
         <v>201</v>
@@ -10113,7 +10113,7 @@
         <v>252</v>
       </c>
       <c r="H168" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I168" s="17" t="s">
         <v>233</v>
@@ -10180,7 +10180,7 @@
         <v>213</v>
       </c>
       <c r="H171" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I171" s="17" t="s">
         <v>233</v>
@@ -10247,7 +10247,7 @@
         <v>213</v>
       </c>
       <c r="H174" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I174" s="16" t="s">
         <v>214</v>
@@ -10299,7 +10299,7 @@
         <v>213</v>
       </c>
       <c r="H176" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I176" s="17" t="s">
         <v>201</v>
@@ -10366,7 +10366,7 @@
         <v>252</v>
       </c>
       <c r="H179" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I179" s="17" t="s">
         <v>233</v>
@@ -10433,7 +10433,7 @@
         <v>213</v>
       </c>
       <c r="H182" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I182" s="17" t="s">
         <v>233</v>
@@ -10500,7 +10500,7 @@
         <v>252</v>
       </c>
       <c r="H185" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I185" s="17" t="s">
         <v>233</v>
@@ -10567,7 +10567,7 @@
         <v>252</v>
       </c>
       <c r="H188" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I188" s="17" t="s">
         <v>233</v>
@@ -10634,7 +10634,7 @@
         <v>252</v>
       </c>
       <c r="H191" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I191" s="17" t="s">
         <v>233</v>
@@ -10701,7 +10701,7 @@
         <v>213</v>
       </c>
       <c r="H194" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I194" s="17" t="s">
         <v>233</v>
@@ -10751,7 +10751,7 @@
         <v>544</v>
       </c>
       <c r="H196" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I196" s="17" t="s">
         <v>201</v>
@@ -10818,7 +10818,7 @@
         <v>213</v>
       </c>
       <c r="H199" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I199" s="17" t="s">
         <v>233</v>
@@ -10885,7 +10885,7 @@
         <v>252</v>
       </c>
       <c r="H202" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I202" s="17" t="s">
         <v>233</v>
@@ -10952,7 +10952,7 @@
         <v>213</v>
       </c>
       <c r="H205" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I205" s="17" t="s">
         <v>233</v>
@@ -10980,7 +10980,7 @@
       <c r="K207" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{DCFABEDA-7478-4F8D-8179-8796BA34DADB}"/>
+  <autoFilter ref="A3:K3" xr:uid="{136913D7-A670-4F99-A276-1619907CCF39}"/>
   <mergeCells count="116">
     <mergeCell ref="C204:K204"/>
     <mergeCell ref="A207:K207"/>
@@ -11104,7 +11104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B080FD3-BC29-448D-836E-817B0276C16E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17923E9F-F5AD-493C-9E46-EC3DC91F3F17}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
@@ -11244,7 +11244,7 @@
         <v>486</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>214</v>
@@ -11296,7 +11296,7 @@
         <v>213</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>201</v>
@@ -11346,7 +11346,7 @@
         <v>213</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>214</v>
@@ -11398,7 +11398,7 @@
         <v>213</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>233</v>
@@ -11448,7 +11448,7 @@
         <v>213</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I14" s="17" t="s">
         <v>233</v>
@@ -11498,7 +11498,7 @@
         <v>213</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>233</v>
@@ -11548,7 +11548,7 @@
         <v>213</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>233</v>
@@ -11600,7 +11600,7 @@
         <v>213</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>233</v>
@@ -11650,7 +11650,7 @@
         <v>213</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>233</v>
@@ -11700,7 +11700,7 @@
         <v>213</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I24" s="16" t="s">
         <v>214</v>
@@ -11752,7 +11752,7 @@
         <v>313</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I26" s="16" t="s">
         <v>214</v>
@@ -11804,7 +11804,7 @@
         <v>340</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>214</v>
@@ -11856,7 +11856,7 @@
         <v>252</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>233</v>
@@ -11906,7 +11906,7 @@
         <v>245</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I32" s="17" t="s">
         <v>201</v>
@@ -11956,7 +11956,7 @@
         <v>252</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>233</v>
@@ -12006,7 +12006,7 @@
         <v>213</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I36" s="16" t="s">
         <v>214</v>
@@ -12058,7 +12058,7 @@
         <v>213</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I38" s="16" t="s">
         <v>214</v>
@@ -12110,7 +12110,7 @@
         <v>213</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>233</v>
@@ -12160,7 +12160,7 @@
         <v>213</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I42" s="17" t="s">
         <v>201</v>
@@ -12210,7 +12210,7 @@
         <v>213</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>201</v>
@@ -12277,7 +12277,7 @@
         <v>332</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I47" s="16" t="s">
         <v>214</v>
@@ -12312,7 +12312,7 @@
         <v>336</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I48" s="16" t="s">
         <v>214</v>
@@ -12364,7 +12364,7 @@
         <v>467</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I50" s="16" t="s">
         <v>214</v>
@@ -12416,7 +12416,7 @@
         <v>213</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I52" s="17" t="s">
         <v>201</v>
@@ -12466,7 +12466,7 @@
         <v>213</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I54" s="16" t="s">
         <v>214</v>
@@ -12518,7 +12518,7 @@
         <v>213</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I56" s="17" t="s">
         <v>201</v>
@@ -12568,7 +12568,7 @@
         <v>252</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I58" s="17" t="s">
         <v>233</v>
@@ -12618,7 +12618,7 @@
         <v>213</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I60" s="17" t="s">
         <v>201</v>
@@ -12668,7 +12668,7 @@
         <v>429</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I62" s="16" t="s">
         <v>214</v>
@@ -12720,7 +12720,7 @@
         <v>378</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I64" s="16" t="s">
         <v>214</v>
@@ -12772,7 +12772,7 @@
         <v>322</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I66" s="16" t="s">
         <v>214</v>
@@ -12824,7 +12824,7 @@
         <v>300</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I68" s="16" t="s">
         <v>214</v>
@@ -12876,7 +12876,7 @@
         <v>213</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I70" s="16" t="s">
         <v>214</v>
@@ -12928,7 +12928,7 @@
         <v>213</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I72" s="17" t="s">
         <v>201</v>
@@ -12978,7 +12978,7 @@
         <v>396</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I74" s="16" t="s">
         <v>214</v>
@@ -13047,7 +13047,7 @@
         <v>252</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I77" s="16" t="s">
         <v>214</v>
@@ -13082,7 +13082,7 @@
         <v>252</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I78" s="16" t="s">
         <v>214</v>
@@ -13117,7 +13117,7 @@
         <v>252</v>
       </c>
       <c r="H79" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I79" s="16" t="s">
         <v>214</v>
@@ -13152,7 +13152,7 @@
         <v>252</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I80" s="16" t="s">
         <v>214</v>
@@ -13204,7 +13204,7 @@
         <v>252</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I82" s="16" t="s">
         <v>214</v>
@@ -13239,7 +13239,7 @@
         <v>252</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I83" s="16" t="s">
         <v>214</v>
@@ -13274,7 +13274,7 @@
         <v>252</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I84" s="16" t="s">
         <v>214</v>
@@ -13326,7 +13326,7 @@
         <v>252</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I86" s="16" t="s">
         <v>214</v>
@@ -13361,7 +13361,7 @@
         <v>252</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I87" s="16" t="s">
         <v>214</v>
@@ -13396,7 +13396,7 @@
         <v>252</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I88" s="16" t="s">
         <v>214</v>
@@ -13448,7 +13448,7 @@
         <v>252</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I90" s="17" t="s">
         <v>233</v>
@@ -13498,7 +13498,7 @@
         <v>471</v>
       </c>
       <c r="H92" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I92" s="16" t="s">
         <v>214</v>
@@ -13550,7 +13550,7 @@
         <v>240</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>201</v>
@@ -13602,7 +13602,7 @@
         <v>219</v>
       </c>
       <c r="H96" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I96" s="16" t="s">
         <v>214</v>
@@ -13671,7 +13671,7 @@
         <v>252</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I99" s="17" t="s">
         <v>201</v>
@@ -13706,7 +13706,7 @@
         <v>256</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I100" s="17" t="s">
         <v>233</v>
@@ -13756,7 +13756,7 @@
         <v>252</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>233</v>
@@ -13806,7 +13806,7 @@
         <v>252</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I104" s="17" t="s">
         <v>233</v>
@@ -13856,7 +13856,7 @@
         <v>213</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I106" s="17" t="s">
         <v>233</v>
@@ -13906,7 +13906,7 @@
         <v>544</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I108" s="17" t="s">
         <v>201</v>
@@ -13956,7 +13956,7 @@
         <v>252</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I110" s="16" t="s">
         <v>214</v>
@@ -14008,7 +14008,7 @@
         <v>224</v>
       </c>
       <c r="H112" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I112" s="16" t="s">
         <v>214</v>
@@ -14060,7 +14060,7 @@
         <v>336</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I114" s="16" t="s">
         <v>214</v>
@@ -14112,7 +14112,7 @@
         <v>252</v>
       </c>
       <c r="H116" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I116" s="16" t="s">
         <v>214</v>
@@ -14181,7 +14181,7 @@
         <v>252</v>
       </c>
       <c r="H119" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I119" s="17" t="s">
         <v>233</v>
@@ -14231,7 +14231,7 @@
         <v>252</v>
       </c>
       <c r="H121" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I121" s="17" t="s">
         <v>233</v>
@@ -14281,7 +14281,7 @@
         <v>213</v>
       </c>
       <c r="H123" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I123" s="17" t="s">
         <v>233</v>
@@ -14331,7 +14331,7 @@
         <v>213</v>
       </c>
       <c r="H125" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I125" s="17" t="s">
         <v>233</v>
@@ -14381,7 +14381,7 @@
         <v>291</v>
       </c>
       <c r="H127" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I127" s="16" t="s">
         <v>214</v>
@@ -14450,7 +14450,7 @@
         <v>252</v>
       </c>
       <c r="H130" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I130" s="17" t="s">
         <v>233</v>
@@ -14500,7 +14500,7 @@
         <v>252</v>
       </c>
       <c r="H132" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I132" s="17" t="s">
         <v>233</v>
@@ -14550,7 +14550,7 @@
         <v>270</v>
       </c>
       <c r="H134" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I134" s="17" t="s">
         <v>233</v>
@@ -14600,7 +14600,7 @@
         <v>252</v>
       </c>
       <c r="H136" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I136" s="16" t="s">
         <v>214</v>
@@ -14669,7 +14669,7 @@
         <v>295</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>214</v>
@@ -14721,7 +14721,7 @@
         <v>256</v>
       </c>
       <c r="H141" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I141" s="16" t="s">
         <v>214</v>
@@ -14773,7 +14773,7 @@
         <v>232</v>
       </c>
       <c r="H143" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I143" s="17" t="s">
         <v>233</v>
@@ -14825,7 +14825,7 @@
         <v>261</v>
       </c>
       <c r="H145" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I145" s="17" t="s">
         <v>233</v>
@@ -14892,7 +14892,7 @@
         <v>213</v>
       </c>
       <c r="H148" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I148" s="16" t="s">
         <v>214</v>
@@ -14944,7 +14944,7 @@
         <v>213</v>
       </c>
       <c r="H150" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I150" s="17" t="s">
         <v>201</v>
@@ -14994,7 +14994,7 @@
         <v>200</v>
       </c>
       <c r="H152" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I152" s="17" t="s">
         <v>201</v>
@@ -15046,7 +15046,7 @@
         <v>350</v>
       </c>
       <c r="H154" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I154" s="17" t="s">
         <v>201</v>
@@ -15115,7 +15115,7 @@
         <v>213</v>
       </c>
       <c r="H157" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I157" s="17" t="s">
         <v>201</v>
@@ -15165,7 +15165,7 @@
         <v>345</v>
       </c>
       <c r="H159" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I159" s="16" t="s">
         <v>214</v>
@@ -15217,7 +15217,7 @@
         <v>213</v>
       </c>
       <c r="H161" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I161" s="17" t="s">
         <v>201</v>
@@ -15284,7 +15284,7 @@
         <v>406</v>
       </c>
       <c r="H164" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I164" s="17" t="s">
         <v>201</v>
@@ -15311,38 +15311,38 @@
       <c r="J165" s="29"/>
       <c r="K165" s="29"/>
     </row>
-    <row r="166" spans="1:11" ht="145.80000000000001" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A166" s="11" t="s">
+    <row r="166" spans="1:11" ht="185.4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A166" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C166" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="D166" s="17" t="s">
+      <c r="D166" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="E166" s="17" t="s">
+      <c r="E166" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F166" s="17">
+      <c r="F166" s="16">
         <v>3</v>
       </c>
-      <c r="G166" s="17" t="s">
+      <c r="G166" s="16" t="s">
         <v>365</v>
       </c>
-      <c r="H166" s="17" t="s">
+      <c r="H166" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I166" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J166" s="17" t="s">
+      <c r="I166" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J166" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="K166" s="17" t="s">
+      <c r="K166" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -15403,7 +15403,7 @@
         <v>252</v>
       </c>
       <c r="H169" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I169" s="17" t="s">
         <v>233</v>
@@ -15453,7 +15453,7 @@
         <v>252</v>
       </c>
       <c r="H171" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I171" s="16" t="s">
         <v>214</v>
@@ -15500,37 +15500,37 @@
       <c r="K173" s="29"/>
     </row>
     <row r="174" spans="1:11" ht="132.6" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A174" s="11" t="s">
+      <c r="A174" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B174" s="11" t="s">
+      <c r="B174" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="C174" s="17" t="s">
+      <c r="C174" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="D174" s="17" t="s">
+      <c r="D174" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="E174" s="17" t="s">
+      <c r="E174" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F174" s="17">
+      <c r="F174" s="16">
         <v>2</v>
       </c>
-      <c r="G174" s="17" t="s">
+      <c r="G174" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="H174" s="17" t="s">
+      <c r="H174" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I174" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="J174" s="17" t="s">
+      <c r="I174" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J174" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="K174" s="17" t="s">
+      <c r="K174" s="16" t="s">
         <v>203</v>
       </c>
     </row>
@@ -15729,7 +15729,7 @@
         <v>213</v>
       </c>
       <c r="H183" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I183" s="16" t="s">
         <v>214</v>
@@ -15798,7 +15798,7 @@
         <v>252</v>
       </c>
       <c r="H186" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I186" s="16" t="s">
         <v>214</v>
@@ -15811,7 +15811,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{7B080FD3-BC29-448D-836E-817B0276C16E}"/>
+  <autoFilter ref="A3:K3" xr:uid="{17923E9F-F5AD-493C-9E46-EC3DC91F3F17}"/>
   <mergeCells count="96">
     <mergeCell ref="C178:K178"/>
     <mergeCell ref="C179:K179"/>
@@ -15915,7 +15915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF28FBC1-688B-416E-8F96-F8DF10FA9E68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FFD022-774A-41BC-981C-169AA18F83AE}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16181,7 +16181,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{EF28FBC1-688B-416E-8F96-F8DF10FA9E68}"/>
+  <autoFilter ref="A3:E3" xr:uid="{A9FFD022-774A-41BC-981C-169AA18F83AE}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -16190,7 +16190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60B1C066-3C78-4B82-A351-839EFE37780B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E902C4F4-D52B-4046-91BA-F34A09EF4B35}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16396,7 +16396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5823A546-157F-43D2-8BCC-0C0B0800E5F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E44981-54FF-44C7-98FE-224CDCE4CA85}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16534,18 +16534,18 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="11">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="11">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -16719,7 +16719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E988BA-3F6F-4A96-9677-3E1B8BC490E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399D64FB-4066-4AEE-BBED-3E2CFF858D83}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17247,7 +17247,7 @@
       <c r="G25" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G3" xr:uid="{B4E988BA-3F6F-4A96-9677-3E1B8BC490E3}"/>
+  <autoFilter ref="A3:G3" xr:uid="{399D64FB-4066-4AEE-BBED-3E2CFF858D83}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A25:G25"/>

--- a/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
+++ b/docs/TABLEAU_DE_BORD_CYCLES_OPERATOIRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2560248D-D2A9-458C-B265-10A0393A616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{153E191B-B8E2-49BE-858C-E1CC63F6BBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{E09F606B-E046-4148-BA95-22ABFB1EBCBB}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{C2472AE7-6CAB-40CD-9B94-AB21B548B09E}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue d'ensemble" sheetId="1" r:id="rId1"/>
@@ -2223,7 +2223,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9669EB"/>
+        <fgColor rgb="FFD35400"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2530,7 +2530,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ADDE-4417-AC5D-3F57B65D3925}"/>
+              <c16:uniqueId val="{00000000-DB24-4953-B9B9-15E194AEFBDC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2544,11 +2544,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1785867344"/>
-        <c:axId val="1785867760"/>
+        <c:axId val="2069388463"/>
+        <c:axId val="2069387215"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1785867344"/>
+        <c:axId val="2069388463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2591,7 +2591,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1785867760"/>
+        <c:crossAx val="2069387215"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2599,7 +2599,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1785867760"/>
+        <c:axId val="2069387215"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2650,7 +2650,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1785867344"/>
+        <c:crossAx val="2069388463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2843,7 +2843,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-97C7-49C2-B3C0-09E36D8C3E9F}"/>
+              <c16:uniqueId val="{00000000-1174-4B4A-A960-34F7CC7E5473}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2857,11 +2857,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1785559024"/>
-        <c:axId val="1785556528"/>
+        <c:axId val="2068553663"/>
+        <c:axId val="2068552831"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1785559024"/>
+        <c:axId val="2068553663"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2904,7 +2904,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1785556528"/>
+        <c:crossAx val="2068552831"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2912,7 +2912,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1785556528"/>
+        <c:axId val="2068552831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2963,7 +2963,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1785559024"/>
+        <c:crossAx val="2068553663"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3156,7 +3156,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-73F6-4018-AF74-308855BF62E7}"/>
+              <c16:uniqueId val="{00000000-734A-4E72-9D44-59EC2AA4AE04}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3170,11 +3170,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1785557360"/>
-        <c:axId val="1785558192"/>
+        <c:axId val="2068554079"/>
+        <c:axId val="2075548943"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1785557360"/>
+        <c:axId val="2068554079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3217,7 +3217,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1785558192"/>
+        <c:crossAx val="2075548943"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3225,7 +3225,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1785558192"/>
+        <c:axId val="2075548943"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3276,7 +3276,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1785557360"/>
+        <c:crossAx val="2068554079"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4981,7 +4981,7 @@
         <xdr:cNvPr id="2" name="Graphique 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A0FAA03-1139-41F4-A737-33959AF893EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99E946E0-3F61-43E2-A7BB-F607865A7A74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5017,7 +5017,7 @@
         <xdr:cNvPr id="3" name="Graphique 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4D97826-9BFE-4C10-9182-C8BBB51FF4BA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F182CA2A-BBE3-4AAB-A366-D4CAB81216F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5053,7 +5053,7 @@
         <xdr:cNvPr id="4" name="Graphique 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{005DD656-E5E5-47CF-8B65-00CFD550A166}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95EF91AD-C294-4C31-8FA4-5FF07C68CCB4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5370,7 +5370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02AFC813-531F-47F7-9A04-AD2B1ACA9F4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA13E66-5D04-48B6-942D-A0F760086802}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6084,7 +6084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CCBAE8F-E035-4AE3-8970-3D51C274872D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2AC4EA-B1F4-43B5-BAD7-AECDE85A1C8D}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -11130,7 +11130,7 @@
       <c r="K207" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{9CCBAE8F-E035-4AE3-8970-3D51C274872D}"/>
+  <autoFilter ref="A3:K3" xr:uid="{BC2AC4EA-B1F4-43B5-BAD7-AECDE85A1C8D}"/>
   <mergeCells count="116">
     <mergeCell ref="C204:K204"/>
     <mergeCell ref="A207:K207"/>
@@ -11259,7 +11259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820B2158-1DD6-4E0C-8253-43B5ADE6C936}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59DCB98-77AB-4E7F-B6AD-63F660DC255D}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -15967,7 +15967,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K3" xr:uid="{820B2158-1DD6-4E0C-8253-43B5ADE6C936}"/>
+  <autoFilter ref="A3:K3" xr:uid="{E59DCB98-77AB-4E7F-B6AD-63F660DC255D}"/>
   <mergeCells count="96">
     <mergeCell ref="C178:K178"/>
     <mergeCell ref="C179:K179"/>
@@ -16076,7 +16076,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2AC5A60-FCA0-497A-8D38-7B02C0556156}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A3FE25-E1E5-4056-8D2A-8619D3D76F5A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -16345,7 +16345,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{D2AC5A60-FCA0-497A-8D38-7B02C0556156}"/>
+  <autoFilter ref="A3:E3" xr:uid="{A4A3FE25-E1E5-4056-8D2A-8619D3D76F5A}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -16359,7 +16359,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D90C4B-B4EC-49B3-9652-472E03347E2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96108087-59EE-46C6-8E9E-E6A492F1DADD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -16644,7 +16644,7 @@
       <c r="E18" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E3" xr:uid="{15D90C4B-B4EC-49B3-9652-472E03347E2B}"/>
+  <autoFilter ref="A3:E3" xr:uid="{96108087-59EE-46C6-8E9E-E6A492F1DADD}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:E18"/>
@@ -16659,7 +16659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B2C743-A3FF-4910-B4E1-1C25D36216C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8273634-A57A-4E5A-BEDF-925E584BE8A8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
